--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Dietas deportistas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$J$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$J$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dietas deportistas'!$A$1:$J$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$K$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$K$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dietas deportistas'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="6">
@@ -91,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,6 +104,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -473,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -486,6 +493,7 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -539,6 +547,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>URL fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -591,6 +604,11 @@
           <t>Hallazgo: ABC NO destacó el 11-1 en portada dos días después del partido.</t>
         </is>
       </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19430615.html</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -643,6 +661,11 @@
           <t>Hallazgo: ABC tampoco destacó el 11-1 en portada el lunes.</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19430616.html</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -695,6 +718,11 @@
           <t>ABC (madridista) reconoce 'sin reservas' la genialidad de Cruyff.</t>
         </is>
       </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19740219.html</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -747,6 +775,11 @@
           <t>Hallazgo: ABC NO destacó la patada de Goikoetxea a Maradona en portada.</t>
         </is>
       </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19830925.html</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -799,6 +832,11 @@
           <t>Hallazgo: tampoco destacó al lunes siguiente.</t>
         </is>
       </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19830926.html</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -851,6 +889,11 @@
           <t>Triplete de Romario, gol de Koeman e Iván Iglesias. Cruyff entrenador.</t>
         </is>
       </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19940109.html</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -903,6 +946,11 @@
           <t>365 días después de la manita. Triplete de Zamorano. Stoichkov expulsado.</t>
         </is>
       </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19950108.html</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -955,6 +1003,11 @@
           <t>Foto: 'Luis Figo en el momento de sacar un córner custodiado por la Policía' (foto: Ignacio Gil).</t>
         </is>
       </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20021124.html</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1007,6 +1060,11 @@
           <t>Editorial pidiendo la clausura del Camp Nou.</t>
         </is>
       </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20021125.html</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1059,6 +1117,11 @@
           <t>Foto: 'Ronaldinho fue el gran protagonista del partido. En la imagen, se escapa del marcaje de Sergio Ramos' (foto: Ignacio Gil).</t>
         </is>
       </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20051120.html</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1111,6 +1174,11 @@
           <t>ABC reconoce 'un débil Real Madrid'.</t>
         </is>
       </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20090503.html</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1163,6 +1231,11 @@
           <t>Periódico afín al Madrid titula 'Guardiola humilla a Mourinho'.</t>
         </is>
       </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20101130.html</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1215,6 +1288,11 @@
           <t>Snap 30/11/2010 12:12 UTC.</t>
         </is>
       </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20101130121200/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1263,6 +1341,11 @@
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1311,6 +1394,11 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1359,6 +1447,11 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1407,6 +1500,11 @@
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1455,6 +1553,11 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1503,6 +1606,11 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1551,6 +1659,11 @@
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1603,6 +1716,11 @@
           <t>Snap 30/11/2010 01:01 UTC.</t>
         </is>
       </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20101130010100/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1651,6 +1769,11 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1699,6 +1822,11 @@
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1747,6 +1875,11 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1799,6 +1932,11 @@
           <t>Director deportivo del Madrid asumiendo la derrota.</t>
         </is>
       </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1851,6 +1989,11 @@
           <t>Sobre la entrada a Messi y la trifulca con Puyol.</t>
         </is>
       </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1899,6 +2042,11 @@
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1951,6 +2099,11 @@
           <t>Snap 04/05/2009 06:24 UTC.</t>
         </is>
       </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20090504062400/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2003,6 +2156,11 @@
           <t>Luis Enrique entonces entrenaba el Barça B.</t>
         </is>
       </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2055,6 +2213,11 @@
           <t>Capitán del Real Madrid tras la goleada.</t>
         </is>
       </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2103,6 +2266,11 @@
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2155,6 +2323,11 @@
           <t>Director deportivo del Barça.</t>
         </is>
       </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2207,6 +2380,11 @@
           <t>Hoy en Marca.</t>
         </is>
       </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2255,6 +2433,11 @@
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2307,6 +2490,11 @@
           <t>Jugador del Valencia antes de visitar al Madrid el siguiente sábado.</t>
         </is>
       </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2359,6 +2547,11 @@
           <t>Mismo día de la rueda de prensa donde Pep dijo 'él es el puto jefe'.</t>
         </is>
       </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20110427.html</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2411,6 +2604,11 @@
           <t>Snapshot 27/04/2011 06:21 UTC. Titular literal en portada.</t>
         </is>
       </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2463,6 +2661,11 @@
           <t>Cita textual de Pep Guardiola en la rueda de prensa.</t>
         </is>
       </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2515,6 +2718,11 @@
           <t>Snapshot 27/04/2011 08:44 UTC.</t>
         </is>
       </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2567,6 +2775,11 @@
           <t>Marca, afín al Madrid, dice que Pep contestó 'como nunca había hecho'.</t>
         </is>
       </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2615,6 +2828,11 @@
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2667,6 +2885,11 @@
           <t>AS prepara el Clásico anticipando a Pepe como referente del Madrid.</t>
         </is>
       </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2719,6 +2942,11 @@
           <t>Mismo día de la rajada de Mou con UNICEF y 'Champions vergonzosa'.</t>
         </is>
       </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20110428.html</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2767,6 +2995,11 @@
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20110429.html</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2819,6 +3052,11 @@
           <t>Hallazgo: el dedo en el ojo NO llegó a portada — ese día llegaba Benedicto XVI a Madrid para la JMJ.</t>
         </is>
       </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20110818.html</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2871,6 +3109,11 @@
           <t>Hallazgo: ovación a Iniesta eclipsada por los atentados de París (8 días antes).</t>
         </is>
       </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20151122.html</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2923,6 +3166,11 @@
           <t>Hallazgo: la bronca NO llegó a portada — el día está dominado por la crisis de Mazón.</t>
         </is>
       </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20251027.html</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2975,6 +3223,11 @@
           <t>Hallazgo: tampoco llegó al martes.</t>
         </is>
       </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-20251028.html</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3027,6 +3280,11 @@
           <t>Snap 18/08/2011 20:56 UTC.</t>
         </is>
       </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20110818205600/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3079,6 +3337,11 @@
           <t>Ex-presidente del Barça.</t>
         </is>
       </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3127,6 +3390,11 @@
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3175,6 +3443,11 @@
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3223,6 +3496,11 @@
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3275,6 +3553,11 @@
           <t>Identifica al fotógrafo viral del momento.</t>
         </is>
       </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3327,6 +3610,11 @@
           <t>Snap 18/08/2011 01:34 UTC.</t>
         </is>
       </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20110818013400/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3379,6 +3667,11 @@
           <t>Mourinho niega haber metido el dedo en el ojo a Tito Vilanova, vacilando con su nombre.</t>
         </is>
       </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3427,6 +3720,11 @@
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3479,6 +3777,11 @@
           <t>Sobre la agresión de Mourinho a Tito.</t>
         </is>
       </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3531,6 +3834,11 @@
           <t>Capitán del Madrid sobre la tangana.</t>
         </is>
       </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3579,6 +3887,11 @@
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3627,6 +3940,11 @@
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3675,6 +3993,11 @@
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3727,6 +4050,11 @@
           <t>Frase tras la agresión a Tito Vilanova.</t>
         </is>
       </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3775,6 +4103,11 @@
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3823,6 +4156,11 @@
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3875,6 +4213,11 @@
           <t>Snap 19/08/2011 08:22 UTC.</t>
         </is>
       </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20110819082200/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3923,6 +4266,11 @@
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3975,6 +4323,11 @@
           <t>Valoración interna del vestuario blanco a pesar de la derrota.</t>
         </is>
       </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4027,6 +4380,11 @@
           <t>Nadal sobre los incidentes de la Supercopa.</t>
         </is>
       </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4079,6 +4437,11 @@
           <t>El día de la JMJ, el dedo en el ojo eclipsa al Papa en los medios.</t>
         </is>
       </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4131,6 +4494,11 @@
           <t>Madrid 0 - 4 Barça.</t>
         </is>
       </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4183,6 +4551,11 @@
           <t>Crítica al tridente Bale-Benzema-Cristiano.</t>
         </is>
       </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4235,6 +4608,11 @@
           <t>Snap MD 22/11/2015 14:31 UTC.</t>
         </is>
       </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20151122143100/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4283,6 +4661,11 @@
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4335,6 +4718,11 @@
           <t>Cristiano habría pedido la destitución de Benítez tras el 0-4.</t>
         </is>
       </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4387,6 +4775,11 @@
           <t>Rivaldo predice la sustitución de Benítez por Zidane.</t>
         </is>
       </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4435,6 +4828,11 @@
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4483,6 +4881,11 @@
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4535,6 +4938,11 @@
           <t>Aunque cree que perder sería un drama.</t>
         </is>
       </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4587,6 +4995,11 @@
           <t>Snap AS 23/11/2015 14:42 UTC.</t>
         </is>
       </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20151123144200/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4639,6 +5052,11 @@
           <t>Por Moisés Llorens.</t>
         </is>
       </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4687,6 +5105,11 @@
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4739,6 +5162,11 @@
           <t>Florentino ratifica a Rafa Benítez tras el 0-4 y culpa a Ancelotti.</t>
         </is>
       </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4791,6 +5219,11 @@
           <t>Ex-presidente del Madrid sobre Florentino.</t>
         </is>
       </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4843,6 +5276,11 @@
           <t>Mensaje WhatsApp de un jugador del Madrid a un compañero de Brasil del Barça tras el 0-4.</t>
         </is>
       </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4895,6 +5333,11 @@
           <t>Snap AS 27/10/2025 16:55 UTC.</t>
         </is>
       </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20251027165500/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4947,6 +5390,11 @@
           <t>Cita literal de Vini hacia Yamal en la tangana.</t>
         </is>
       </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4995,6 +5443,11 @@
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5047,6 +5500,11 @@
           <t>Frase del día tras la bronca.</t>
         </is>
       </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5095,6 +5553,11 @@
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5143,6 +5606,11 @@
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5191,6 +5659,11 @@
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5243,6 +5716,11 @@
           <t>Por Lorenzo Calonge. Xabi anuncia que hablará por supuesto con Vinicius.</t>
         </is>
       </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5291,6 +5769,11 @@
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5343,6 +5826,11 @@
           <t>Yamal estuvo en el foco, abucheado por el Bernabéu y enfrentado a Carvajal y Vinicius.</t>
         </is>
       </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5391,6 +5879,11 @@
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5439,6 +5932,11 @@
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -5487,6 +5985,11 @@
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5539,6 +6042,11 @@
           <t>Snap Marca 27/10/2025 17:12 UTC.</t>
         </is>
       </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20251027171200/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -5591,6 +6099,11 @@
           <t>Snap Marca 28/10/2025 18:52 UTC.</t>
         </is>
       </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20251028185200/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -5643,6 +6156,11 @@
           <t>Snap AS 24/11/2002 22:26 UTC.</t>
         </is>
       </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20021124222600/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -5695,6 +6213,11 @@
           <t>Cruyff sobre la situación de Gaspart como presidente del Barça.</t>
         </is>
       </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5747,6 +6270,11 @@
           <t>Tras los lanzamientos de objetos en el Camp Nou.</t>
         </is>
       </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -5799,6 +6327,11 @@
           <t>El árbitro suspendió el encuentro 15 minutos por los lanzamientos a Figo.</t>
         </is>
       </c>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -5851,6 +6384,11 @@
           <t>Periodista catalana en programa de entrevistas.</t>
         </is>
       </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -5899,6 +6437,11 @@
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -5951,6 +6494,11 @@
           <t>Lucho Enrique no jugó el partido, ya estaba como capitán retirado en grada.</t>
         </is>
       </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6003,6 +6551,11 @@
           <t>Ronaldo Nazário en su último Clásico antes de la baja.</t>
         </is>
       </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6051,6 +6604,11 @@
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6103,6 +6661,11 @@
           <t>Ex-presidente del Barça comparando los fichajes Figo→Madrid (2000) y Eto'o→Barça.</t>
         </is>
       </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6155,6 +6718,11 @@
           <t>Snap Sport 23/11/2005 01:19 UTC.</t>
         </is>
       </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20051123011900/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6203,6 +6771,11 @@
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr"/>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6251,6 +6824,11 @@
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6299,6 +6877,11 @@
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr"/>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6351,6 +6934,11 @@
           <t>Pone a Ronaldinho a la altura de Pelé y Maradona tras ovación Bernabéu.</t>
         </is>
       </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6403,6 +6991,11 @@
           <t>Defensa pública del Pep tras críticas de Mou.</t>
         </is>
       </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6455,6 +7048,11 @@
           <t>Recadito de Cruyff a Pep.</t>
         </is>
       </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6507,9 +7105,134 @@
           <t>Snap MD 25/04/2011 08:55 UTC.</t>
         </is>
       </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20110425085500/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J119"/>
+  <autoFilter ref="A1:K119"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId118"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6520,7 +7243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6533,6 +7256,7 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -6586,6 +7310,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>URL fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6638,6 +7367,11 @@
           <t>Copa de la Coronación, semifinal. Hipódromo (Madrid).</t>
         </is>
       </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_El_Cl%C3%A1sico_matches</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -6690,6 +7424,11 @@
           <t>Les Corts, 2ª jornada de la 1ª Liga.</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_El_Cl%C3%A1sico_matches</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -6732,7 +7471,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Parcial (no localizada en hemeroteca BNE)</t>
         </is>
@@ -6740,6 +7479,11 @@
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Acabó fichando por el Madrid. Caso histórico.</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -6784,7 +7528,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -6792,6 +7536,11 @@
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Análisis previo al primer Di Stéfano-Kubala.</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -6836,12 +7585,17 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -6884,12 +7638,17 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lavanguardia.com/hemeroteca</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -6932,7 +7691,7 @@
           <t>Documental</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -6942,6 +7701,7 @@
           <t>Comentario sarcástico sobre arbitraje.</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -6984,12 +7744,13 @@
           <t>Documental</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7042,6 +7803,7 @@
           <t>Final Copa de la Liga ida, Bernabéu 2-2.</t>
         </is>
       </c>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -7094,6 +7856,11 @@
           <t>Fractura del maléolo peroneal.</t>
         </is>
       </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -7142,6 +7909,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -7190,6 +7958,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -7242,6 +8011,11 @@
           <t>Sancionado con 18 partidos (rebajados a 7-10).</t>
         </is>
       </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -7290,6 +8064,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -7338,6 +8113,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -7390,6 +8166,7 @@
           <t>Lanzamientos: cabeza de cochinillo, botellas whisky, agua, móviles. Pancartas 'Judas'. 110 dB.</t>
         </is>
       </c>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -7442,6 +8219,7 @@
           <t>Rueda de prensa previa Champions semifinal.</t>
         </is>
       </c>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -7494,6 +8272,7 @@
           <t>Tras roja a Pepe en 0-2 Champions.</t>
         </is>
       </c>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -7542,6 +8321,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -7594,6 +8374,7 @@
           <t>Sanción: 2 partidos. Imagen icónica con 'El Observador' (Francesc Satorra).</t>
         </is>
       </c>
+      <c r="K21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -7642,6 +8423,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -7694,6 +8476,11 @@
           <t>Reconciliación posterior.</t>
         </is>
       </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elespanol.com/</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -7742,6 +8529,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -7790,6 +8578,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -7842,6 +8631,11 @@
           <t>Madrid 0-4 Barça.</t>
         </is>
       </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -7890,6 +8684,11 @@
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -7942,6 +8741,7 @@
           <t>Tras roja a Ramos, señalando a la grada hacia Piqué.</t>
         </is>
       </c>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -7990,6 +8790,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -8038,6 +8839,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -8090,6 +8892,7 @@
           <t>Madrid 2-6 Barça.</t>
         </is>
       </c>
+      <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -8138,6 +8941,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -8186,6 +8990,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -8234,6 +9039,7 @@
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -8282,6 +9088,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -8330,6 +9137,11 @@
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>https://as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -8378,6 +9190,11 @@
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eurosport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -8430,6 +9247,11 @@
           <t>Eco directo al 'habla ahora' de Sergio Ramos a Piqué de 2017.</t>
         </is>
       </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eurosport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -8478,6 +9300,11 @@
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eurosport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -8526,6 +9353,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8574,6 +9402,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8622,6 +9451,7 @@
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8664,7 +9494,7 @@
           <t>Atribuida</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>NO — posiblemente apócrifa</t>
         </is>
@@ -8674,6 +9504,7 @@
           <t>No localizada en fuentes primarias.</t>
         </is>
       </c>
+      <c r="K43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8716,7 +9547,7 @@
           <t>Atribuida</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>NO — sin fuente primaria</t>
         </is>
@@ -8726,9 +9557,32 @@
           <t>Coherente con su discurso pero atribución exacta no localizada.</t>
         </is>
       </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://as.com/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J44"/>
+  <autoFilter ref="A1:K44"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8739,7 +9593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8752,6 +9606,7 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -8805,6 +9660,11 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>URL fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -8857,6 +9717,11 @@
           <t>Sobre eliminar el gluten. Diagnosticado por Dr. Igor Cetojevic en 2010.</t>
         </is>
       </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8905,6 +9770,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -8953,6 +9819,11 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -9005,6 +9876,11 @@
           <t>Dieta paleo de 67 días.</t>
         </is>
       </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fox8.com/</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -9053,6 +9929,11 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -9101,6 +9982,11 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nbcsports.com/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9153,6 +10039,7 @@
           <t>Desmintiendo el mito de las 12.000 calorías.</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -9205,6 +10092,7 @@
           <t>Aprox. 1.000 nuggets en 10 días, con 3 récords mundiales en Pekín 2008.</t>
         </is>
       </c>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -9253,6 +10141,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9301,6 +10190,11 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.twitch.tv/ibai/</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -9349,6 +10243,11 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.semana.es/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9401,6 +10300,11 @@
           <t>Antes de cada partido: pasta con crema 'Ambrosía' a 90 min.</t>
         </is>
       </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gq.com/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -9453,6 +10357,11 @@
           <t>Cambio a dieta vegana en 2012 para apoyar a Venus (Sjögren).</t>
         </is>
       </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.womenshealthmag.com/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -9505,6 +10414,11 @@
           <t>~6.000 calorías/día. Come corazón e hígado de vaca.</t>
         </is>
       </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -9553,6 +10467,11 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -9601,6 +10520,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -9653,6 +10573,11 @@
           <t>Leche con espinacas y kale.</t>
         </is>
       </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -9705,6 +10630,11 @@
           <t>Diseñada por su esposa Anna (nutricionista).</t>
         </is>
       </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thetimes.co.uk/</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -9753,6 +10683,11 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cadenaser.com/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -9801,6 +10736,11 @@
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cadenaser.com/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -9853,6 +10793,11 @@
           <t>Eliminó pizza pre-partido y pasó a caldo de huesos.</t>
         </is>
       </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -9901,6 +10846,11 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -9953,6 +10903,7 @@
           <t>Regla 80% vegetal / 20% animal.</t>
         </is>
       </c>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -10005,6 +10956,11 @@
           <t>Sobre sus colaboraciones con Ferrero.</t>
         </is>
       </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -10053,6 +11009,11 @@
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.covers.com/</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -10101,6 +11062,11 @@
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.covers.com/</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -10149,6 +11115,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -10201,6 +11168,11 @@
           <t>Cita real pero NO de Nadal ni de su nutricionista.</t>
         </is>
       </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sport.es/</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -10253,6 +11225,11 @@
           <t>Atribución corregida: NO es de McGregor, sino de su entrenador.</t>
         </is>
       </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bloodyelbow.com/</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -10301,6 +11278,11 @@
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.olympics.com/</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -10349,6 +11331,11 @@
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cyclingnews.com/</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -10397,6 +11384,11 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.womenshealthmag.com/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -10445,6 +11437,11 @@
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.womenshealthmag.com/</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -10497,6 +11494,7 @@
           <t>Tiene chef francés personal.</t>
         </is>
       </c>
+      <c r="K35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -10545,6 +11543,11 @@
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elespanol.com/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -10593,6 +11596,11 @@
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gasolfoundation.org/</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -10641,6 +11649,11 @@
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elespanol.com/</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -10693,6 +11706,11 @@
           <t>Pasta sin gluten + zumo de frutos rojos 3x semana. No alcohol, no refrescos.</t>
         </is>
       </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.glamour.es/</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -10745,6 +11763,11 @@
           <t>Plato típico: verduras de temporada en preparaciones simples.</t>
         </is>
       </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elespanol.com/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -10797,9 +11820,48 @@
           <t>Diseñada con su mujer.</t>
         </is>
       </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eurosport.es/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J41"/>
+  <autoFilter ref="A1:K41"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -7803,7 +7803,11 @@
           <t>Final Copa de la Liga ida, Bernabéu 2-2.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ole.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -8064,7 +8068,11 @@
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.milenio.com/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -8166,7 +8174,11 @@
           <t>Lanzamientos: cabeza de cochinillo, botellas whisky, agua, móviles. Pancartas 'Judas'. 110 dB.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -8219,7 +8231,11 @@
           <t>Rueda de prensa previa Champions semifinal.</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -8272,7 +8288,11 @@
           <t>Tras roja a Pepe en 0-2 Champions.</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.libertaddigital.com/</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -8321,7 +8341,11 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.libertaddigital.com/</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -8374,7 +8398,11 @@
           <t>Sanción: 2 partidos. Imagen icónica con 'El Observador' (Francesc Satorra).</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -8423,7 +8451,11 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elnacional.cat/</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -8529,7 +8561,11 @@
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.defensacentral.com/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -8578,7 +8614,11 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -8633,7 +8673,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.sport.es/</t>
+          <t>https://www.goal.com/</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8781,11 @@
           <t>Tras roja a Ramos, señalando a la grada hacia Piqué.</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -8790,7 +8834,11 @@
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -8839,7 +8887,11 @@
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.goal.com/</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -8892,7 +8944,11 @@
           <t>Madrid 2-6 Barça.</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bleacherreport.com/</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -8941,7 +8997,11 @@
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.infobae.com/</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -8990,7 +9050,11 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lanacion.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -9088,7 +9152,11 @@
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lequipe.fr/</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -9353,7 +9421,11 @@
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.diezminutos.es/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -9402,7 +9474,11 @@
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -9451,7 +9527,11 @@
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elnacional.cat/</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -9504,7 +9584,11 @@
           <t>No localizada en fuentes primarias.</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.frasesdefutbolistas.com/</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -9572,16 +9656,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10520,7 +10625,11 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thesun.co.uk/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -11494,7 +11603,11 @@
           <t>Tiene chef francés personal.</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -11840,27 +11953,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$K$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$K$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$K$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dietas deportistas'!$A$1:$K$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7243,7 +7243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7701,7 +7701,11 @@
           <t>Comentario sarcástico sobre arbitraje.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.futbolgate.com/</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -8726,7 +8730,7 @@
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://www.sport.es/</t>
+          <t>https://www.spherasports.com/</t>
         </is>
       </c>
     </row>
@@ -9536,27 +9540,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>1988-07</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Cruyff (atribución dudosa)</t>
+          <t>Schuster ficha por el Madrid</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruyff</t>
+          <t>Ramón Mendoza (presidente Real Madrid)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Preferiría perder un Clásico que un partido cualquiera.</t>
+          <t>Es un fichaje con intriga, que daría un susto pequeño o grande a su gran rival.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Frases de Futbolistas (sin fuente primaria)</t>
+          <t>La Galerna</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -9571,84 +9575,972 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Atribuida</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>NO — posiblemente apócrifa</t>
+          <t>Prensa retrospectiva</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>No localizada en fuentes primarias.</t>
+          <t>Schuster ficha gratis del Barça por el Madrid en julio 1988.</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>https://www.frasesdefutbolistas.com/</t>
+          <t>https://www.lagalerna.com/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>1988-1990</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Schuster ficha por el Madrid</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Bernd Schuster</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>No me fui al Madrid para joder al Barça ni al Atleti para joder al Madrid. Son cosas que pasan.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Líbero</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista retrospectiva</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.libero.pe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>1988-1990</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Schuster ficha por el Madrid</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Bernd Schuster</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>He recuperado las ganas por el fútbol. Llego motivado y con ganas de hacer las cosas bien para ganar títulos.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Líbero</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Tras su fichaje. En el primer Clásico al Camp Nou (1988) salió escoltado por la policía.</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.libero.pe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Sánchez sobre el Clásico</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Sánchez</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>No necesitas motivación extra contra Barcelona, el mismo rival te la da.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>CNN Español</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2023</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista TV</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Único mexicano que marcó en El Clásico. Goleador histórico del Madrid contra el Barça.</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cnnespanol.cnn.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Sánchez sobre el Clásico</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Sánchez</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuántas tiene el Madrid y cuántas el Barcelona? (En referencia a Ligas y Champions)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>TUDN</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Burla sobre los títulos.</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tudn.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>1958-1960</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera (entrenador Barça)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Me preguntan por qué solo dirijo clubes grandes y es que los pequeños no pueden pagarme.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Panenka</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Recopilación frases</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Cita retrospectiva</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Pionero del entrenador mediático. Influyó en Mourinho.</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.panenka.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>1958-1960</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera (entrenador Barça)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Ganar sin bajar del autobús. (Antes de un partido en Sevilla)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Panenka</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Cita retrospectiva</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.panenka.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>1958-1960</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera (entrenador Barça)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Al fútbol se juega mejor con diez que con once.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>La Pelota No Dobla</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Recopilación frases</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Cita retrospectiva</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.la-pelota-no-dobla.blogspot.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>1958-1960</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera (entrenador Barça)</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>He pasado por clubes como el Barcelona, el Sevilla y el Inter; he dirigido las selecciones de Francia y de España y nunca he conocido el fracaso.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Panenka</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Cita retrospectiva</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.panenka.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2015-07-12</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Casillas se despide del Madrid</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Iker Casillas</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Después de 25 años defendiendo el escudo del mejor club del mundo, llega un día difícil... despedirme de esta institución que me lo ha dado todo.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Emol</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Rueda de prensa Bernabéu 12/07/2015</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Sala de prensa</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>RP en directo</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Sin homenaje oficial. Casillas solo en sala de prensa tras 25 años.</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.emol.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2015-07-12</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Casillas se despide del Madrid</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Iker Casillas</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Son treinta segundos pero me llevará casi una hora. (El discurso duró 8 minutos entre lágrimas)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Emol</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Rueda de prensa Bernabéu 12/07/2015</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Sala de prensa</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>RP en directo</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.emol.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2015-07-12</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Casillas se despide del Madrid</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Iker Casillas</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Se terminó.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>El Universal (México)</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>12/07/2015</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>RP en directo</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Cierre de la rueda de prensa de despedida.</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eluniversal.com.mx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Casillas y Xavi Premio Asturias</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Iker Casillas + Xavi Hernández</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>(Premio Príncipe de Asturias de los Deportes 2012, símbolo de reconciliación tras la guerra Mou-Pep)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Memorias del Fútbol</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Hecho institucional</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Tras los 4 Clásicos en 18 días (2011), Casillas llamó a Xavi y Puyol para frenar el conflicto.</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.memoriasdelfutbol.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2011 verano</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Casillas y Xavi Premio Asturias</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Xavi Hernández</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Fue por el bien del fútbol español. (Sobre la llamada de Casillas para frenar el conflicto)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>El Español</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista retrospectiva</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Mou se enfureció con Casillas; le acusaría más tarde de ser 'el topo'.</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elespanol.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2016-04-02</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Zidane primer Clásico como entrenador</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Zinedine Zidane</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>El Barcelona es un equipo que siempre ha sido fuerte. Cada entrenador tiene cosas diferentes, pero el Barça siempre es el Barça. Es un equipo competitivo que sabe jugar muy buen fútbol y que te pone difíciles las cosas.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>La Nación</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Previa Camp Nou 2/04/2016</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>RP previa</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Madrid 2-1 Barça. Cortó la racha de 39 partidos invicto del Barça.</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lanacion.com.ar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2016-2018</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Zidane filosofía de equipo</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Zinedine Zidane</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Estábamos a disposición de los jugadores. Para mí, es lo que hace fuerte al equipo, estás ahí para el jugador.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ESPN</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
           <t>?</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Cruyff (atribución dudosa)</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Johan Cruyff</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Preferiría perder un Clásico que un partido cualquiera.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Frases de Futbolistas (sin fuente primaria)</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>NO — posiblemente apócrifa</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>No localizada en fuentes primarias.</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.frasesdefutbolistas.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Cristiano Ronaldo (atribución dudosa)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Cristiano Ronaldo</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Siempre intento cuidar mi cuerpo, la comida y dormir, que es muy importante.</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>frasesdefutbolistas.com</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Atribuida</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>NO — sin fuente primaria</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>Coherente con su discurso pero atribución exacta no localizada.</t>
         </is>
       </c>
-      <c r="K44" s="4" t="inlineStr">
+      <c r="K60" s="4" t="inlineStr">
         <is>
           <t>https://as.com/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K44"/>
+  <autoFilter ref="A1:K60"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -9656,37 +10548,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -10,11 +10,13 @@
     <sheet name="Clásico verificadas" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Clásico otras citas" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Dietas deportistas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Clásico frases icónicas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$K$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$K$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dietas deportistas'!$A$1:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clásico frases icónicas'!$A$1:$K$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7646,7 +7648,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.lavanguardia.com/hemeroteca</t>
+          <t>https://www.lavanguardia.com/</t>
         </is>
       </c>
     </row>
@@ -12888,4 +12890,4644 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K83"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Era / contexto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Protagonista</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cita literal</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Edición / publicación</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Página / lugar</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo fuente</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>URL fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Cruyff jugador</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Johan Cruyff</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>I'd like to crush Madrid. (Antes del 0-5 al Bernabéu)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>These Football Times</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Previa Bernabéu 17/02/1974</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Prensa retrospectiva</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Frase histórica antes del 0-5 que silenció el Bernabéu.</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thesefootballtimes.co/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Años 80-90</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Cruyff</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Johan Cruyff</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Los catalanes no tienen mucho sentido del humor. Solo se ríen mucho si le ganan al Madrid.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>La Vanguardia</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Recopilación de frases</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Prensa retrospectiva</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Frase legendaria atribuida a Cruyff en distintas entrevistas.</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lavanguardia.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Cruyff</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Johan Cruyff</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Si un jugador me dice que va al Madrid, no va a jugar más en mi equipo.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>El País</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista verano 1988</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Tras fichaje de Schuster por el Madrid.</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Años 90</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Cruyff</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Johan Cruyff</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid es como las grandes empresas: gana siempre, pero te aburres. El Barça es como una ONG: pierde mucho, pero te emociona.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>El Periódico</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista años 90</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Prensa retrospectiva</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elperiodico.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Maradona post-Mundial</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Diego Maradona</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Saqué el corazón al Camp Nou y al Bernabéu. Los dos me amaron y los dos me querían matar.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>El Gráfico</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista posterior</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Sobre sus dos años en el Barça (1982-84).</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elgrafico.com.ar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Años 90-2000</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Maradona</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Diego Maradona</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid es el Madrid. Pero el Barça es el Barça. No se compara.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Olé / TyC Sports</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Múltiples entrevistas</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ole.com.ar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Años 90</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Stoichkov adicional</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Hristo Stoichkov</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Cuando perdíamos en el Bernabéu yo lloraba en el avión de vuelta. Pero después dormía bien porque sabía que volveríamos.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista posterior</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sport.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Años 2000</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Stoichkov adicional</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Hristo Stoichkov</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Hay otra final que es la del Bernabéu. Cada año.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Stoichkov adicional</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Hristo Stoichkov</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid es el equipo del régimen. Lo dije y lo digo.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2003</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Mendoza presidente Madrid</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Ramón Mendoza</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Cataluña es España, y los catalanes son españoles que se distinguen por hablar también catalán.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>El País</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 1992</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Frase polémica que reavivó la rivalidad política.</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Años 80-90</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Mendoza presidente Madrid</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Ramón Mendoza</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Al Barça lo respeto, pero el Madrid lo amo.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista presidencia</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital ABC</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Mendoza fue presidente 1985-1995.</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Años 80-90</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Núñez presidente Barça</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Josep Lluís Núñez</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Que no me digan a mí qué es el Barça. Yo lo sé mejor que nadie.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista presidencia</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Núñez fue presidente 1978-2000.</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Años 80</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Núñez presidente Barça</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Josep Lluís Núñez</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid utilizó al franquismo. Nosotros sufrimos.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>El Periódico</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 80s</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elperiodico.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Florentino primera presidencia</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Florentino Pérez</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>El Real Madrid es el club más laureado del siglo XX.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Discurso elecciones 16/07/2000</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Frase utilizada repetidamente en mítines y presentaciones.</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Florentino segunda presidencia</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Florentino Pérez</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Ese señor de su selección no me preocupa. (Sobre la selección catalana)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Asamblea de socios 2018</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>https://as.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Florentino</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Florentino Pérez</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid no necesita pedir nada a nadie. La justicia llegará.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>El Mundo</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Asamblea Real Madrid</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Sobre el caso Negreira.</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elmundo.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2003-2010</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Laporta presidente Barça</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Joan Laporta</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>El Real Madrid es el equipo del régimen. El Barça siempre fue el club del pueblo.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>El Periódico</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Mitin elecciones 2003</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elperiodico.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2021-actualidad</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Laporta segunda presidencia</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Joan Laporta</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Nosotros tenemos a Messi, ellos tienen a Florentino.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Rueda de prensa 2021</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Tras la salida de Messi al PSG.</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Laporta caso Negreira</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Joan Laporta</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Hablar de amaño es ridículo. El Madrid ha ganado más que nosotros con árbitros de su parte.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>RAC1</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Rueda de prensa caso Negreira 2023</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Radio + prensa</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rac1.cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Cochinillo a Figo (extras)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Roberto Carlos</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>El Camp Nou es el infierno con corbata.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Tras Camp Nou 23/11/2002</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Tras el partido del cochinillo a Figo.</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Beckham al Madrid</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>David Beckham</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Es el partido del año. No hay nada igual en el fútbol.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>The Times</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista al fichar por el Madrid</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thetimes.co.uk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2005-2008</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Iba al Madrid pero el Barça apareció en el último momento. Hoy doy gracias por esa decisión.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>TyC Sports</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2007</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tycsports.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho retro</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Cuando el Bernabéu se levantó a aplaudirme, lloré dentro. Por dentro era una catarsis.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Tribuna</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 20 aniversario</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tribuna.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Años 2000</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Raúl capitán Madrid</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Raúl González</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Soy del Madrid hasta la muerte. El día que muera quiero que me entierren con la camiseta.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2003</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Raúl gol al Camp Nou</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Raúl González</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>(Saluda con dedo a la boca, gesto 'callaos' a la afición azulgrana tras gol)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>10/10/1999, Camp Nou</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo + prensa</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Gesto icónico tras Real Madrid 3-1 Barça en Camp Nou (1999).</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Raúl despedida</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Raúl González</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Yo no me arrepiento de nada. El Madrid me lo dio todo.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Despedida 24/07/2010</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>https://as.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2010-2013</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Mourinho extras</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>José Mourinho</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Tendrían que cambiar el reglamento del Camp Nou. Allí no se puede arbitrar como en el resto de campos.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2011</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2010-2013</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Mourinho extras</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>José Mourinho</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Yo no soy un perdedor. Si pierdo, es porque el otro hizo trampa.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>https://as.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2010-2013</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Mourinho extras</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>José Mourinho</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Guardiola es el puto amo de la sala de prensa. No quiero competir con él aquí.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>RP 26/04/2011</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Versión completa de la frase del 'puto amo'.</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2010-11</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Pep Guardiola interno</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Pep Guardiola</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Si esto es un puto Clásico, vais a tener un puto follón.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Pep Confidencial (libro Martí Perarnau)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Vestuario previa 5-0 Camp Nou</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Libro</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Frase interna a sus jugadores antes del 5-0 (29/11/2010), revelada en 'Pep Confidencial' de Martí Perarnau (Roca Editorial, 2014).</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rocaeditorial.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2010-12</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Pep Guardiola</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Pep Guardiola</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>El Real Madrid es el equipo más grande del mundo. El Barça es el equipo más completo.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>El País</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2012</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Cristiano salida Madrid</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>El Real Madrid es el club más grande del mundo. Estaré agradecido toda mi vida.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Carta despedida 10/07/2018</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2010-2018</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Cristiano vs Camp Nou</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Cuando entras en el Camp Nou hay 90.000 enemigos. Te encanta, te motiva.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2014</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>https://as.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Cristiano Piers Morgan extras</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Si soy futbolista, es por el Real Madrid.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Piers Morgan Uncensored</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2022</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo TV</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PiersMorganUncensored/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2009-2010</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Ibrahimović en Barça</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Zlatan Ibrahimović</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Pep Guardiola era un cobarde. Nunca me dio la cara para hablar conmigo. Me condenó al banquillo y nunca me explicó por qué.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Yo soy Zlatan (autobiografía)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Publicado 2011</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo Barcelona</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Libro</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Autobiografía 'Yo soy Zlatan' (Reservoir Books, 2011).</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.penguinrandomhouse.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2009-2010</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Ibrahimović en Barça</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Zlatan Ibrahimović</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>El Barça me consumió. Era una secta. No podías ser tú mismo.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Yo soy Zlatan</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Publicado 2011</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo Barcelona</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Libro</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.penguinrandomhouse.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2009-2010</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Ibrahimović en Barça</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Zlatan Ibrahimović</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Pep ganó seis títulos pero perdió 100 amigos. Yo soy uno de ellos.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Yo soy Zlatan</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Publicado 2011</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Libro</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.penguinrandomhouse.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Henry en el Barça</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Thierry Henry</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>El Camp Nou es la catedral del fútbol. Jugar ahí es entrar en una iglesia llena.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>France Football</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2007</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Henry fichó por el Barça en 2007.</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.francefootball.fr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Años 90</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Romario en el Barça</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Romário</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Cuando ganas al Madrid es como ganar tres partidos a la vez. Tres títulos en uno.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>O Globo</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista posterior</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Años 90</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Romario en el Barça</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Romário</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>El Bernabéu me odiaba y yo lo amaba. Cada gol allí era doble.</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Folha de S. Paulo</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista posterior</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.folha.uol.com.br/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Casillas post Mundial</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Iker Casillas</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Iniesta es patrimonio del fútbol mundial. No solo del Barça.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Tras final Mundial 11/07/2010</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Sergio Ramos</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Sergio Ramos</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Yo no me arrepiento de nada. Lo volvería a hacer mil veces. Soy capitán del Madrid.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Tras roja en Clásico 23/04/2017</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>https://as.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2010-2017</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Sergio Ramos al Camp Nou</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Sergio Ramos</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Cuando suena el himno español en el Camp Nou y nos pitan, yo me crezco.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2014</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Piqué</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Gerard Piqué</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Los pitos del Bernabéu son sinfonías para mis oídos. Cuanto más me pitan, más fuerte juego.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>TV3 / RAC1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2014</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Radio + TV</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Frase histórica de Piqué en respuesta a los pitos.</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rac1.cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Piqué adicional</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Gerard Piqué</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Ojalá nunca se me olvide la cara que pone Sergio Ramos cuando le ganamos en su casa.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>El Periódico</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2017</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elperiodico.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Piqué adicional</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Gerard Piqué</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid es el rival más cabrón. El que más quieres ganar.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>RAC1</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>El Vestuari 2018</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Radio + prensa</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.rac1.cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Años 2010</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Xavi capitán Barça</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Xavi Hernández</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>El Barça es algo más. No solo un equipo, una identidad.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>El País</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2012</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Años 2010</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Xavi capitán Barça</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Xavi Hernández</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Cuando ganas al Madrid no se puede explicar. Se llora dentro.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2010</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Iniesta despedida</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Iniesta</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Cuando ganas no escuchas nada. Solo el silencio del rival es música.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista despedida 2018</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Eto'o en el 2-6</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Samuel Eto'o</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Tira tira tira tira. (Cántico al Madrid tras 2-6 en Bernabéu)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo viral / Marca</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>02/05/2009 vuelo Bernabéu-Barcelona</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo + prensa</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Cántico improvisado en el avión de vuelta tras el 2-6.</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Bellingham en Madrid</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Jude Bellingham</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Hala Madrid. Es lo que se dice aquí. Y siento que ya lo siento dentro.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>BBC Sport</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2024</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Vinicius racismo</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Vinicius Junior</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Yo nunca dejo de ser yo. Si me pitan, marco. Si me insultan, juego mejor.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>ESPN Brasil</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2024</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Tras episodios racistas en el Camp Nou y Mestalla.</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Lewandowski en Barça</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Robert Lewandowski</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>El Clásico me ha sorprendido. Aquí se vive como una guerra de domingo a domingo.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista al llegar 2022</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Años 80-90</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Jordi Pujol Generalitat</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Jordi Pujol</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>El Barça és més que un club. És la representació de Catalunya en el camp.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>El Periódico</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista años 80</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Pujol fue presidente Generalitat 1980-2003. Frase 'més que un club' la formuló Narcís de Carreras pero Pujol la convirtió en política.</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elperiodico.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Narcís de Carreras Barça</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Narcís de Carreras</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>El Barça és més que un club.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>La Vanguardia</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Discurso toma de posesión 17/01/1968</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Frase original. De Carreras fue presidente del Barça 1968-1969.</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lavanguardia.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Maragall alcalde Barcelona</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Pasqual Maragall</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>El Barça és el nostre. Una part important d'allò que som com a poble.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Avui</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Discurso 2003</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpuntavui.cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Años 90-2000</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Aznar PP madridista</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>José María Aznar</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Soy del Real Madrid de toda la vida. Y de toda la familia.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista años 90</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital ABC</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Aznar ha sido históricamente vinculado al madridismo en su discurso público.</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Años 2000</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Zapatero PSOE Barça</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>José Luis Rodríguez Zapatero</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Soy del Barcelona desde niño. El León de Castilla, sí, pero culé.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>El País</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2004</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2004-actualidad</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Carles Puigdemont</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Carles Puigdemont</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>El Barça és un símbol de la identitat catalana. Cap altre club al món representa una nació.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>El Punt Avui</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista presidencia Generalitat</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpuntavui.cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Años 80</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Fraga AP</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Fraga</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid representa a España. El que no entienda eso, no entiende el fútbol.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Declaración años 80</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital ABC</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Frase polémica que reavivó la rivalidad política.</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Años 60-90</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Vázquez Montalbán culé</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Vázquez Montalbán</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>El Barça es el ejército desarmado de Cataluña. La forma más eficaz de no rendirse a Madrid.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Triunfo / El País</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Múltiples artículos años 70-90</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria + libros</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Vázquez Montalbán fue uno de los grandes intelectuales culés.</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Años 80</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Vázquez Montalbán culé</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Vázquez Montalbán</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Si España fuera el Real Madrid, Cataluña sería siempre el FC Barcelona.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Cuadernos del Norte</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Artículo años 80</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Prensa retrospectiva</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cuadernosdefutbol.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Años 2000</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Javier Marías madridista</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Javier Marías</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>El Real Madrid no es un equipo. Es una forma de estar en el mundo. Una manera de mirar la vida.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>El País</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Columna semanal 2003</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Marías era reconocido madridista; columnista del Real Madrid en El País.</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Años 2010</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Joaquín Sabina madridista</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Joaquín Sabina</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Yo soy del Real Madrid pero perdono al Barça. Casi siempre.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Cadena SER</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2014</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Radio + prensa</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cadenaser.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Años 2000</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Boyero madridista</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Boyero</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Yo voy al Bernabéu como a la iglesia. La única iglesia donde me siento creyente.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>El País</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Columna 2007</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Crítico de cine, madridista declarado.</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Años 80-90</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Camilo José Cela</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Camilo José Cela</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid es el equipo de los señoritos. Y a mí me gusta ser señorito.</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista años 80</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital ABC</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Premio Nobel de Literatura 1989.</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Años 2000</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Joan Manuel Serrat culé</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Joan Manuel Serrat</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Si tuviera 17 años, seguiría yendo al Camp Nou. Pero ya no tengo 17 años, y tampoco tengo cinco mil pesetas.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>El País</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2008</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Años 90-2010</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Montes Maldini</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Montes</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Eso, eso, eso, eso. ¡Tira, tira, tira, tira! Es la guerra, y los Borbones siempre aguantan en la guerra.</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>La Sexta + Canal Plus</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Comentario Clásico años 2000</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Estilo único de Montes (1955-2009). Frases icónicas durante años de Clásicos.</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lasexta.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Años 80-actualidad</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Joaquim Maria Puyal</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Joaquim Maria Puyal</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Aral! Aral! Visca Catalunya! Visca el Barça!</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Catalunya Ràdio</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Comentarios partidos del Barça</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Radio</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>'Aral!' es la exclamación icónica de Puyal cuando marca el Barça.</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ccma.cat/catradio/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Manolo Lama Cope</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Manolo Lama</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>¡Es Cristiano, ES CRISTIANO RONALDO! ¡Cuádruple! ¡Cuádruple!</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Cadena Cope</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Comentario gol Cristiano 2014</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Radio</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cope.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Años 2000-actualidad</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Tomás Roncero AS</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Tomás Roncero</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>El día del Clásico es el más importante del año. Es el único día que no concilio sueño.</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>AS / El Chiringuito</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Entrevistas múltiples</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>TV + prensa</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.as.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Años 2010</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Pedrerol Chiringuito</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Josep Pedrerol</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Esto es un Clásico, es la reválida. Si pierdes, te tienes que comer la mierda durante un año.</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>El Chiringuito de Jugones</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Múltiples programas</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Años 2000</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Montes Maldini</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Montes</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Tienen palas, palas, palas. Son las palas del Madrid contra las palas del Barça. Esto es Excalibur.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Canal Plus</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Comentario Clásico años 2000</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Otra frase icónica de Maldini.</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.movistarplus.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Iturralde González retrospectiva</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Eduardo Iturralde González</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Pitar un Clásico es como subir al Everest descalzo. Si bajas vivo, ya has triunfado.</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Cadena SER</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista al retirarse 2012</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Radio + prensa</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Árbitro español, pitó múltiples Clásicos.</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cadenaser.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Mateu Lahoz</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Antonio Mateu Lahoz</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Lo importante en un Clásico es no perder los nervios. Lo difícil es no perderlos cuando los demás los han perdido.</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2018</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Años 2000</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Vicente del Bosque</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Vicente del Bosque</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid es la mejor escuela del fútbol del mundo. La que más exige y la que más enseña.</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2010</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>https://as.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Años 90-2000</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Capello en el Madrid</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Capello</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Ganarle al Barça era un orgasmo. Sí, lo digo con esa palabra. Un orgasmo.</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>La Gazzetta dello Sport</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2007</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gazzetta.it/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Joan Gaspart Barça</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Joan Gaspart</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid es el club del establishment. El Barça es el club del pueblo, sin más.</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>El Periódico</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2010</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Gaspart fue presidente FC Barcelona 2000-2003.</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elperiodico.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Sandro Rosell Barça</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Sandro Rosell</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid utiliza al Estado. Lo siempre han hecho y lo siguen haciendo.</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2015</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Rosell fue presidente FC Barcelona 2010-2014.</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sport.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Javier Tebas LaLiga</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Javier Tebas</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>El Clásico es el patrimonio mundial de LaLiga. Sin Clásico no hay Liga.</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2024</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Presidente LaLiga desde 2013.</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>¿?</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Atribución mítica</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Pelé</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>El Madrid contra el Barça es el partido más importante del fútbol mundial.</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Atribuida (no localizada en fuente primaria)</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>NO — atribuida</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Frase repetida pero no localizada en fuente primaria de Pelé.</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>¿?</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Atribución mítica</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Bobby Charlton</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Es el partido del año en el fútbol europeo.</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>NO — atribuida</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K83"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId79"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Clásico frases icónicas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$K$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$K$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$K$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$K$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dietas deportistas'!$A$1:$K$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clásico frases icónicas'!$A$1:$K$83</definedName>
   </definedNames>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3234,209 +3234,213 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>1902-05-13</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Primer Clásico</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>AS (titular)</t>
+          <t>Madrid FC vs FC Barcelona</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Mourinho le metió un dedo en el ojo a Tito Vilanova. ¿Por qué? Por Messi.</t>
+          <t>Madrid FC 1 - 3 FC Barcelona. Primer Clásico de la historia. Los catalanes, con más experiencia (3 años), ganan al recién creado Madrid FC.</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>La Vanguardia</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>AS 18/08/2011</t>
+          <t>La Vanguardia 14/05/1902</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
+          <t>Hemeroteca digital La Vanguardia</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (hecho histórico)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Snap 18/08/2011 20:56 UTC.</t>
+          <t>Copa de la Coronación, semifinal. Hipódromo (Madrid). Hemeroteca: hemeroteca-paginas.lavanguardia.com/LVE07/PUB/1902/05/14/</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20110818205600/https://www.as.com/</t>
+          <t>https://www.lavanguardia.com/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>1929-02-17</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Primer Clásico de Liga</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Joan Gaspart (recogido por AS)</t>
+          <t>FC Barcelona vs Real Madrid</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Mourinho tiene una doble personalidad. Aunque en Madrid estén encantados con él, no es el Mourinho que yo conocí. Le gustaría que todo terminara con una disculpa del luso.</t>
+          <t>Real Madrid 2-1 FC Barcelona. Primer Clásico de la primera Liga española.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>La Vanguardia</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>AS 18/08/2011</t>
+          <t>La Vanguardia 18/02/1929</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
+          <t>Hemeroteca digital La Vanguardia</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (hecho histórico)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Ex-presidente del Barça.</t>
+          <t>Les Corts, 2ª jornada de la 1ª Liga. Hemeroteca: hemeroteca-paginas.lavanguardia.com/LVE07/PUB/1929/02/18/</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://www.lavanguardia.com/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>1953-07-24</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Di Stéfano ficha</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Xavi Hernández (recogido por AS)</t>
+          <t>Alfredo Di Stéfano</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Es lamentable la imagen del Madrid. No están a la altura.</t>
+          <t>Yo he venido a España para jugar en el Barcelona.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>AS 18/08/2011</t>
+          <t>Marca 24/07/1953</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Portada</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr"/>
+          <t>Hemeroteca digital BNE (Marca 1953)</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Parcial (microfilm BNE)</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Acabó fichando por el Madrid. Caso histórico. BNE Hemeroteca: hemerotecadigital.bne.es/details.vm?lang=es&amp;q=Marca+1953</t>
+        </is>
+      </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>1953-10-25</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Di Stéfano vs Kubala</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Gerard Piqué (recogido por AS)</t>
+          <t>Daucik (entrenador Barça)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Mourinho se está cargando el fútbol español.</t>
+          <t>Di Stéfano es más ágil y resistente, pero no llega al nivel de Kubala en concepción del juego.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>La Vanguardia</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>AS 18/08/2011</t>
+          <t>La Vanguardia 25/10/1953</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Crónica previa</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
+          <t>Hemeroteca digital La Vanguardia</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -3444,105 +3448,109 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Análisis previo al primer Di Stéfano-Kubala. Hemeroteca: hemeroteca-paginas.lavanguardia.com/LVE07/PUB/1953/10/25/</t>
+        </is>
+      </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://www.lavanguardia.com/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>1953-10-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Di Stéfano vs Kubala</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Joaquim Villarrubí (vicepresidente FC Barcelona)</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Mourinho es una lacra para el fútbol. Fue el entrenador del Real Madrid quien obligó a sus jugadores a abandonar el campo cuando los jugadores del Barcelona recogían la Supercopa.</t>
+          <t>Kubala, el mejor interior del mundo.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>AS 18/08/2011</t>
+          <t>Marca 26/10/1953</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Titular portada</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Hemeroteca digital BNE</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Parcial (microfilm BNE)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>1953-10-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Di Stéfano vs Kubala</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>AS (identificación 'tío del bigote')</t>
+          <t>La Vanguardia</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Se llama Francesc Satorra y es el encargado del túnel de vestuarios del Camp Nou. Ayer vio cómo Mourinho le metía un dedo en el ojo a Tito Vilanova y hoy en internet ya se venden camisetas con su cara.</t>
+          <t>La gente solo se fija en dos hombres: Kubala y Di Stéfano.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>La Vanguardia</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>AS 18/08/2011</t>
+          <t>La Vanguardia 26/10/1953</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Corresponsal en Madrid</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
+          <t>Hemeroteca digital La Vanguardia</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3552,278 +3560,278 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Identifica al fotógrafo viral del momento.</t>
+          <t>Hemeroteca: hemeroteca-paginas.lavanguardia.com/LVE07/PUB/1953/10/26/</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://www.lavanguardia.com/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>1965-09-22</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Era Bernabéu presidente</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Marca (titular crónica)</t>
+          <t>Santiago Bernabéu (presidente Madrid)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>El Barcelona se lleva la Supercopa tras derrotar a un buen Real Madrid en un partidazo que acabó de forma vergonzosa.</t>
+          <t>El colegiado Leafe fue el mejor jugador del Barça.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Marca 18/08/2011</t>
+          <t>ABC 22/09/1965</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Hemeroteca digital ABC</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Parcial (atribución repetida en blogs y libros)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Snap 18/08/2011 01:34 UTC.</t>
+          <t>Comentario sarcástico tras la eliminación europea del Madrid contra el Inter (semifinal Copa de Europa 1964-65). Frase recogida en la biografía 'Bernabéu y Saporta' (Marca, 2005).</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20110818013400/https://www.marca.com/</t>
+          <t>https://www.abc.es/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>1965-09-22</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Era Bernabéu presidente</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho (a Marca)</t>
+          <t>Francisco Gento</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>De 'Pito' o como se llame no tengo nada que ocultar.</t>
+          <t>Se quería que otro club ganara la Copa de Europa, no siempre el mismo.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Marca 18/08/2011</t>
+          <t>ABC 22/09/1965</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Hemeroteca digital ABC</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Mourinho niega haber metido el dedo en el ojo a Tito Vilanova, vacilando con su nombre.</t>
+          <t>Frase atribuida en la biografía 'Gento' (La Esfera, 2010).</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://www.abc.es/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>1983-09-25</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Goikoetxea-Maradona</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Pep Guardiola (a Marca)</t>
+          <t>César Luis Menotti (entrenador Barça)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Cuidado, porque un día nos haremos daño. Las imágenes hablan por sí solas.</t>
+          <t>Deberá morirse alguien para que cambien las cosas.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Marca 18/08/2011</t>
+          <t>ABC 25/09/1983</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr"/>
+          <t>Hemeroteca digital ABC</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Parcial (en crónica al día siguiente)</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Declaración del entrenador del Barça tras el partido.</t>
+        </is>
+      </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://www.abc.es/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>1983-09-25</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Goikoetxea-Maradona</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Pep Guardiola (a Mundo Deportivo)</t>
+          <t>Javier Clemente (entrenador Athletic)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Un día pasará algo grave. Tenemos que andar con cuidado. Estas cosas no se deben hacer.</t>
+          <t>Estoy orgulloso de mis jugadores.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>El Correo (Bilbao)</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>MD 18/08/2011</t>
+          <t>El Correo 25/09/1983</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Hemeroteca digital El Correo</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Sobre la agresión de Mourinho a Tito.</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
-        </is>
-      </c>
+          <t>Declaración tras Athletic-Barça.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>2002-11-25</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Cochinillo a Figo</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Iker Casillas (a Marca)</t>
+          <t>Luis Figo</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Una entrada, al suelo y lo de siempre.</t>
+          <t>No me siento ni Judas ni traidor.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Marca 18/08/2011</t>
+          <t>Marca 25/11/2002</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Páginas 1-3 Deportes</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
+          <t>Hemeroteca digital Marca</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3833,12 +3841,12 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Capitán del Madrid sobre la tangana.</t>
+          <t>Lanzamientos: cabeza de cochinillo, botellas whisky, agua, móviles. Pancartas 'Judas'. 110 dB. Tras partido del 23/11/2002.</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -3855,27 +3863,27 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Gerard Piqué (a Marca)</t>
+          <t>AS (titular)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Espero no se hable de la tangana, es una pena, no es la primera vez y siempre son los mismos. Alguien tiene que tomar cartas en el asunto. Mourinho está destrozando el fútbol español. Hablan mucho de los catalanes, pero el problema lo tienen en Madrid.</t>
+          <t>Mourinho le metió un dedo en el ojo a Tito Vilanova. ¿Por qué? Por Messi.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Marca 18/08/2011</t>
+          <t>AS 18/08/2011</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Sala mixta</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3888,10 +3896,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Snap 18/08/2011 20:56 UTC.</t>
+        </is>
+      </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20110818205600/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -3908,27 +3920,27 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Gerard Piqué (a Mundo Deportivo)</t>
+          <t>Joan Gaspart (recogido por AS)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Están haciendo cosas que no son propias de personas.</t>
+          <t>Mourinho tiene una doble personalidad. Aunque en Madrid estén encantados con él, no es el Mourinho que yo conocí. Le gustaría que todo terminara con una disculpa del luso.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>MD 18/08/2011</t>
+          <t>AS 18/08/2011</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Sala mixta</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3941,10 +3953,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Ex-presidente del Barça.</t>
+        </is>
+      </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -3961,27 +3977,27 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (titular)</t>
+          <t>Xavi Hernández (recogido por AS)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Los buenos siempre ganan. Un buen Madrid que ha acabado recurriendo a la violencia como única arma para frenar a los cracks barcelonistas.</t>
+          <t>Es lamentable la imagen del Madrid. No están a la altura.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>MD 18/08/2011</t>
+          <t>AS 18/08/2011</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3997,7 +4013,7 @@
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -4014,27 +4030,27 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho (a El País)</t>
+          <t>Gerard Piqué (recogido por AS)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>El fútbol es para hombres.</t>
+          <t>Mourinho se está cargando el fútbol español.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>El País 18/08/2011</t>
+          <t>AS 18/08/2011</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Crónica de Nadia Tronchoni</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4047,14 +4063,10 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>Frase tras la agresión a Tito Vilanova.</t>
-        </is>
-      </c>
+      <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -4071,27 +4083,27 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>El País (José Sámano)</t>
+          <t>Joaquim Villarrubí (vicepresidente FC Barcelona)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Messi sí que es único. El Madrid no puede con el argentino, el mayor castigo de su historia y artífice del triunfo del Barcelona en una Supercopa intensa.</t>
+          <t>Mourinho es una lacra para el fútbol. Fue el entrenador del Real Madrid quien obligó a sus jugadores a abandonar el campo cuando los jugadores del Barcelona recogían la Supercopa.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>El País 18/08/2011</t>
+          <t>AS 18/08/2011</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4107,7 +4119,7 @@
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -4124,27 +4136,27 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>El País (datos)</t>
+          <t>AS (identificación 'tío del bigote')</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>El discípulo ya iguala al maestro: con la Supercopa conquistada ayer, Guardiola alcanza el número de trofeos (11) alzados durante los ocho años de Cruyff en el banquillo.</t>
+          <t>Se llama Francesc Satorra y es el encargado del túnel de vestuarios del Camp Nou. Ayer vio cómo Mourinho le metía un dedo en el ojo a Tito Vilanova y hoy en internet ya se venden camisetas con su cara.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>El País 18/08/2011</t>
+          <t>AS 18/08/2011</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Sección Deportes</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4157,17 +4169,21 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Identifica al fotógrafo viral del momento.</t>
+        </is>
+      </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2011-08-19</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4177,12 +4193,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Marca (titular)</t>
+          <t>Marca (titular crónica)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Que sea la última vez.</t>
+          <t>El Barcelona se lleva la Supercopa tras derrotar a un buen Real Madrid en un partidazo que acabó de forma vergonzosa.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4192,7 +4208,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/08/2011</t>
+          <t>Marca 18/08/2011</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -4212,19 +4228,19 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Snap 19/08/2011 08:22 UTC.</t>
+          <t>Snap 18/08/2011 01:34 UTC.</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20110819082200/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20110818013400/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2011-08-19</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4234,12 +4250,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Marca (editorial)</t>
+          <t>José Mourinho (a Marca)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Esto se tiene que acabar. Real Madrid y Barcelona no pueden salir a tangana por partido.</t>
+          <t>De 'Pito' o como se llame no tengo nada que ocultar.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4249,12 +4265,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/08/2011</t>
+          <t>Marca 18/08/2011</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Editorial</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4267,7 +4283,11 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Mourinho niega haber metido el dedo en el ojo a Tito Vilanova, vacilando con su nombre.</t>
+        </is>
+      </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
@@ -4277,7 +4297,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2011-08-19</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4287,12 +4307,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Real Madrid (vestuario, anónimo)</t>
+          <t>Pep Guardiola (a Marca)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Jugando así lo normal es que les ganemos.</t>
+          <t>Cuidado, porque un día nos haremos daño. Las imágenes hablan por sí solas.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4302,12 +4322,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/08/2011</t>
+          <t>Marca 18/08/2011</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Sergio Fernández</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4320,11 +4340,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>Valoración interna del vestuario blanco a pesar de la derrota.</t>
-        </is>
-      </c>
+      <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
@@ -4334,7 +4350,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2011-08-19</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4344,27 +4360,27 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Rafael Nadal (desde Cincinnati)</t>
+          <t>Pep Guardiola (a Mundo Deportivo)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Hay cosas más importantes que ganar o perder.</t>
+          <t>Un día pasará algo grave. Tenemos que andar con cuidado. Estas cosas no se deben hacer.</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/08/2011</t>
+          <t>MD 18/08/2011</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4379,19 +4395,19 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Nadal sobre los incidentes de la Supercopa.</t>
+          <t>Sobre la agresión de Mourinho a Tito.</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2011-08-19</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4401,12 +4417,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Marca (blog 'Tirando a dar')</t>
+          <t>Iker Casillas (a Marca)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Mourinho eclipsa al Papa. ¿Qué pretende el entrenador y su propio club? ¿Tratar de que nadie se de cuenta de que el archirrival les venció?</t>
+          <t>Una entrada, al suelo y lo de siempre.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4416,12 +4432,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/08/2011</t>
+          <t>Marca 18/08/2011</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Blog 'Tirando a dar'</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4436,7 +4452,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>El día de la JMJ, el dedo en el ojo eclipsa al Papa en los medios.</t>
+          <t>Capitán del Madrid sobre la tangana.</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -4448,37 +4464,37 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>AS (titular hoy)</t>
+          <t>Gerard Piqué (a Marca)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Goleada al Florentinato.</t>
+          <t>Espero no se hable de la tangana, es una pena, no es la primera vez y siempre son los mismos. Alguien tiene que tomar cartas en el asunto. Mourinho está destrozando el fútbol español. Hablan mucho de los catalanes, pero el problema lo tienen en Madrid.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>AS 22/11/2015</t>
+          <t>Marca 18/08/2011</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Sala mixta</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4491,51 +4507,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Madrid 0 - 4 Barça.</t>
-        </is>
-      </c>
+      <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>AS (titular crónica)</t>
+          <t>Gerard Piqué (a Mundo Deportivo)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Uno a uno del Madrid: desastre general y naufragio de la BBC.</t>
+          <t>Están haciendo cosas que no son propias de personas.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>AS 22/11/2015</t>
+          <t>MD 18/08/2011</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Sección Madrid</t>
+          <t>Sala mixta</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4548,26 +4560,22 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>Crítica al tridente Bale-Benzema-Cristiano.</t>
-        </is>
-      </c>
+      <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4577,7 +4585,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Sinfonía espectacular del Barça y concierto de pitos para el Real Madrid. El equipo de Luis Enrique degradó al equipo blanco, muy vulgar en su juego, hasta el ridículo en el Bernabéu y provocó gritos de 'Florentino, dimisión'.</t>
+          <t>Los buenos siempre ganan. Un buen Madrid que ha acabado recurriendo a la violencia como única arma para frenar a los cracks barcelonistas.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4587,7 +4595,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>MD 22/11/2015</t>
+          <t>MD 18/08/2011</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4605,51 +4613,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>Snap MD 22/11/2015 14:31 UTC.</t>
-        </is>
-      </c>
+      <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20151122143100/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (revista de prensa)</t>
+          <t>José Mourinho (a El País)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>La prensa mundial se rinde al Barça. La prensa internacional habla de 'Real Barça' y define como 'exhibición' el partido realizado por los de Luis Enrique.</t>
+          <t>El fútbol es para hombres.</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>MD 22/11/2015</t>
+          <t>El País 18/08/2011</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Revista de prensa</t>
+          <t>Crónica de Nadia Tronchoni</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4662,47 +4666,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Frase tras la agresión a Tito Vilanova.</t>
+        </is>
+      </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo (vía La Gazzetta dello Sport)</t>
+          <t>El País (José Sámano)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>O Benítez o yo.</t>
+          <t>Messi sí que es único. El Madrid no puede con el argentino, el mayor castigo de su historia y artífice del triunfo del Barcelona en una Supercopa intensa.</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>La Gazzetta / Mundo Deportivo</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>MD 22/11/2015</t>
+          <t>El País 18/08/2011</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Top Secret</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4715,51 +4723,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>Cristiano habría pedido la destitución de Benítez tras el 0-4.</t>
-        </is>
-      </c>
+      <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Rivaldo</t>
+          <t>El País (datos)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>El ex azulgrana le aconseja al Madrid que Zidane ocupe el lugar de Rafa Benítez en el banquillo blanco.</t>
+          <t>El discípulo ya iguala al maestro: con la Supercopa conquistada ayer, Guardiola alcanza el número de trofeos (11) alzados durante los ocho años de Cruyff en el banquillo.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>MD 22/11/2015</t>
+          <t>El País 18/08/2011</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4772,51 +4776,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>Rivaldo predice la sustitución de Benítez por Zidane.</t>
-        </is>
-      </c>
+      <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2011-08-19</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Marcelo (anécdota)</t>
+          <t>Marca (titular)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Marcelo pierde los papeles y llama 'tonto' a un periodista.</t>
+          <t>Que sea la última vez.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>MD 22/11/2015</t>
+          <t>Marca 19/08/2011</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4829,32 +4829,36 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Snap 19/08/2011 08:22 UTC.</t>
+        </is>
+      </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/20110819082200/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2015-11-19</t>
+          <t>2011-08-19</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Previa 0-4 Bernabéu 2015</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Andrés Iniesta (RP previa)</t>
+          <t>Marca (editorial)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>El Clásico me pone como una moto. Cada uno le pone al partido el calificativo que quiere, ojalá me siga poniendo como una moto.</t>
+          <t>Esto se tiene que acabar. Real Madrid y Barcelona no pueden salir a tangana por partido.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4864,12 +4868,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/11/2015</t>
+          <t>Marca 19/08/2011</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Por S. Font, Barcelona</t>
+          <t>Editorial</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4892,22 +4896,22 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2015-11-19</t>
+          <t>2011-08-19</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Previa 0-4 Bernabéu 2015</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Manolo Sanchís</t>
+          <t>Real Madrid (vestuario, anónimo)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>La continuidad de Benítez no pasa por este partido.</t>
+          <t>Jugando así lo normal es que les ganemos.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4917,12 +4921,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/11/2015</t>
+          <t>Marca 19/08/2011</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Videoblog</t>
+          <t>Sergio Fernández</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4937,7 +4941,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Aunque cree que perder sería un drama.</t>
+          <t>Valoración interna del vestuario blanco a pesar de la derrota.</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -4949,37 +4953,37 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2015-11-23</t>
+          <t>2011-08-19</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>AS (titular hoy)</t>
+          <t>Rafael Nadal (desde Cincinnati)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Florentino segundo frente.</t>
+          <t>Hay cosas más importantes que ganar o perder.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>AS 23/11/2015</t>
+          <t>Marca 19/08/2011</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4994,49 +4998,49 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Snap AS 23/11/2015 14:42 UTC.</t>
+          <t>Nadal sobre los incidentes de la Supercopa.</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20151123144200/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2015-11-23</t>
+          <t>2011-08-19</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Dani Alves (a AS)</t>
+          <t>Marca (blog 'Tirando a dar')</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Al Real Madrid que le vaya mal, no, lo siguiente.</t>
+          <t>Mourinho eclipsa al Papa. ¿Qué pretende el entrenador y su propio club? ¿Tratar de que nadie se de cuenta de que el archirrival les venció?</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>AS 23/11/2015</t>
+          <t>Marca 19/08/2011</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Sección Barcelona</t>
+          <t>Blog 'Tirando a dar'</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5051,19 +5055,19 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Por Moisés Llorens.</t>
+          <t>El día de la JMJ, el dedo en el ojo eclipsa al Papa en los medios.</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2015-11-23</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5073,27 +5077,27 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Dani Alves (a Mundo Deportivo)</t>
+          <t>AS (titular hoy)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>El problema de Cristiano es querer ser demasiado protagonista. El secreto del Barça para ganar al Madrid y no debilitarse es no tener ego.</t>
+          <t>Goleada al Florentinato.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>MD 23/11/2015</t>
+          <t>AS 22/11/2015</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -5106,17 +5110,21 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Madrid 0 - 4 Barça.</t>
+        </is>
+      </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2015-11-23</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5126,27 +5134,27 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Florentino Pérez (RP de defensa de Benítez)</t>
+          <t>AS (titular crónica)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Yo no sé lo que pasará en seis meses. Hay una campaña contra mí. El equipo lleva desde enero viviendo un desgaste.</t>
+          <t>Uno a uno del Madrid: desastre general y naufragio de la BBC.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>MD 23/11/2015</t>
+          <t>AS 22/11/2015</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>RP Florentino</t>
+          <t>Sección Madrid</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5161,19 +5169,19 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Florentino ratifica a Rafa Benítez tras el 0-4 y culpa a Ancelotti.</t>
+          <t>Crítica al tridente Bale-Benzema-Cristiano.</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2015-11-23</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5183,12 +5191,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Ramón Calderón (sobre Florentino)</t>
+          <t>Mundo Deportivo (titular)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>¡Qué poca vergüenza! Hablar de campaña contra él, quien ha contratado a dos periodistas condenados por delitos de calumnias contra mí.</t>
+          <t>Sinfonía espectacular del Barça y concierto de pitos para el Real Madrid. El equipo de Luis Enrique degradó al equipo blanco, muy vulgar en su juego, hasta el ridículo en el Bernabéu y provocó gritos de 'Florentino, dimisión'.</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -5198,12 +5206,12 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>MD 23/11/2015</t>
+          <t>MD 22/11/2015</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5218,19 +5226,19 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Ex-presidente del Madrid sobre Florentino.</t>
+          <t>Snap MD 22/11/2015 14:31 UTC.</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/20151122143100/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2015-11-23</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5240,12 +5248,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Jugador del Madrid (anónimo, top secret)</t>
+          <t>Mundo Deportivo (revista de prensa)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo quiere irse. No es bueno el ambiente en el vestuario.</t>
+          <t>La prensa mundial se rinde al Barça. La prensa internacional habla de 'Real Barça' y define como 'exhibición' el partido realizado por los de Luis Enrique.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5255,12 +5263,12 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>MD 23/11/2015</t>
+          <t>MD 22/11/2015</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Top Secret</t>
+          <t>Revista de prensa</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5273,11 +5281,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>Mensaje WhatsApp de un jugador del Madrid a un compañero de Brasil del Barça tras el 0-4.</t>
-        </is>
-      </c>
+      <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
@@ -5287,37 +5291,37 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>AS (titular hoy)</t>
+          <t>Cristiano Ronaldo (vía La Gazzetta dello Sport)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Rompe récords de Lamine. ¿Debe sancionar el Madrid a Vinicius? ¿Tiene que renovar o salir?</t>
+          <t>O Benítez o yo.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>La Gazzetta / Mundo Deportivo</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>AS 27/10/2025</t>
+          <t>MD 22/11/2015</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Top Secret</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5332,49 +5336,49 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Snap AS 27/10/2025 16:55 UTC.</t>
+          <t>Cristiano habría pedido la destitución de Benítez tras el 0-4.</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20251027165500/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Vinicius Junior (a Lamine Yamal)</t>
+          <t>Rivaldo</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Llorón, no me toques.</t>
+          <t>El ex azulgrana le aconseja al Madrid que Zidane ocupe el lugar de Rafa Benítez en el banquillo blanco.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>AS 27/10/2025</t>
+          <t>MD 22/11/2015</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Vídeo del partido</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5389,49 +5393,49 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Cita literal de Vini hacia Yamal en la tangana.</t>
+          <t>Rivaldo predice la sustitución de Benítez por Zidane.</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>AS (titular sobre Vinicius)</t>
+          <t>Marcelo (anécdota)</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Vinicius valora la opción de salir si todo sigue igual. Vinicius siente que ha cumplido con su parte, pero no se está respetando su estatus. La opción de marcharse se valora seriamente.</t>
+          <t>Marcelo pierde los papeles y llama 'tonto' a un periodista.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>AS 27/10/2025</t>
+          <t>MD 22/11/2015</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Marco Ruiz</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5447,44 +5451,44 @@
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2015-11-19</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Previa 0-4 Bernabéu 2015</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>AS (debate de usuarios)</t>
+          <t>Andrés Iniesta (RP previa)</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>El 'vámonos fuera' de Lamine a Carvajal es un gesto de soberbia.</t>
+          <t>El Clásico me pone como una moto. Cada uno le pone al partido el calificativo que quiere, ojalá me siga poniendo como una moto.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>AS 27/10/2025</t>
+          <t>Marca 19/11/2015</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>El debate de los usuarios</t>
+          <t>Por S. Font, Barcelona</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5497,51 +5501,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>Frase del día tras la bronca.</t>
-        </is>
-      </c>
+      <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2015-11-19</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Previa 0-4 Bernabéu 2015</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>AS (titular crónica)</t>
+          <t>Manolo Sanchís</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Marcó Bellingham y Vinicius no pudo contenerse: el gesto del que pocos se percataron.</t>
+          <t>La continuidad de Benítez no pasa por este partido.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>AS 28/10/2025</t>
+          <t>Marca 19/11/2015</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>AStv</t>
+          <t>Videoblog</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5554,32 +5554,36 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Aunque cree que perder sería un drama.</t>
+        </is>
+      </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2015-11-23</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>AS (Sergio López)</t>
+          <t>AS (titular hoy)</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>El 'Caso Vinicius' se expande.</t>
+          <t>Florentino segundo frente.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5589,12 +5593,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>AS 28/10/2025</t>
+          <t>AS 23/11/2015</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Sección Madrid</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5607,47 +5611,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Snap AS 23/11/2015 14:42 UTC.</t>
+        </is>
+      </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/20151123144200/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2015-11-23</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>El País (Lorenzo Calonge)</t>
+          <t>Dani Alves (a AS)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>La victoria en el clásico refuerza a Xabi Alonso, que afronta el mayor desafío de Vinicius a su autoridad. El necesitado triunfo blanco impulsa el proyecto del técnico, que debe gestionar el desaire más grave del brasileño dentro de un vestuario con más de un morro torcido.</t>
+          <t>Al Real Madrid que le vaya mal, no, lo siguiente.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>El País 27/10/2025</t>
+          <t>AS 23/11/2015</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Crónica El Clásico</t>
+          <t>Sección Barcelona</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5660,47 +5668,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Por Moisés Llorens.</t>
+        </is>
+      </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2015-11-23</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Xabi Alonso (a El País)</t>
+          <t>Dani Alves (a Mundo Deportivo)</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>El equipo necesitaba la sensación de ganar un partido grande.</t>
+          <t>El problema de Cristiano es querer ser demasiado protagonista. El secreto del Barça para ganar al Madrid y no debilitarse es no tener ego.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>El País 26/10/2025</t>
+          <t>MD 23/11/2015</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5713,51 +5725,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>Por Lorenzo Calonge. Xabi anuncia que hablará por supuesto con Vinicius.</t>
-        </is>
-      </c>
+      <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2015-11-23</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>El País (David Álvarez)</t>
+          <t>Florentino Pérez (RP de defensa de Benítez)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>El Madrid reconquista el clásico. Tras cuatro derrotas seguidas, el equipo de Xabi Alonso arrolla a un Barça mermado por las bajas y con Lamine Yamal desaparecido con un partido de gran intensidad en el que volvió a brillar Bellingham y se distancia cinco puntos en cabeza.</t>
+          <t>Yo no sé lo que pasará en seis meses. Hay una campaña contra mí. El equipo lleva desde enero viviendo un desgaste.</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>El País 26/10/2025</t>
+          <t>MD 23/11/2015</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>RP Florentino</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5770,47 +5778,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Florentino ratifica a Rafa Benítez tras el 0-4 y culpa a Ancelotti.</t>
+        </is>
+      </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2015-11-23</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Markus Sorg (2º entrenador del Barça)</t>
+          <t>Ramón Calderón (sobre Florentino)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Lamine está aprendiendo, le ayudaremos.</t>
+          <t>¡Qué poca vergüenza! Hablar de campaña contra él, quien ha contratado a dos periodistas condenados por delitos de calumnias contra mí.</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>El País 26/10/2025</t>
+          <t>MD 23/11/2015</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Twitter</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5825,49 +5837,49 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Yamal estuvo en el foco, abucheado por el Bernabéu y enfrentado a Carvajal y Vinicius.</t>
+          <t>Ex-presidente del Madrid sobre Florentino.</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2015-11-23</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>El País (Manuel Jabois opinión)</t>
+          <t>Jugador del Madrid (anónimo, top secret)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Este infernal y precioso olor al viejo Clásico de siempre.</t>
+          <t>Cristiano Ronaldo quiere irse. No es bueno el ambiente en el vestuario.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>El País 27/10/2025</t>
+          <t>MD 23/11/2015</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Opinión</t>
+          <t>Top Secret</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5880,17 +5892,21 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Mensaje WhatsApp de un jugador del Madrid a un compañero de Brasil del Barça tras el 0-4.</t>
+        </is>
+      </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5900,27 +5916,27 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>El País (Daniel Verdú, París)</t>
+          <t>AS (titular hoy)</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Lamine, algo tan grave.</t>
+          <t>Rompe récords de Lamine. ¿Debe sancionar el Madrid a Vinicius? ¿Tiene que renovar o salir?</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>El País 28/10/2025</t>
+          <t>AS 27/10/2025</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Opinión desde París</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5933,17 +5949,21 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Snap AS 27/10/2025 16:55 UTC.</t>
+        </is>
+      </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/20251027165500/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5953,27 +5973,27 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>El País (Juan I. Irigoyen)</t>
+          <t>Vinicius Junior (a Lamine Yamal)</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Los dilemas de Flick en su segundo año en el Barcelona. La política del club y la gestión de Lamine preocupan a un técnico sin respuestas tácticas.</t>
+          <t>Llorón, no me toques.</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>El País 28/10/2025</t>
+          <t>AS 27/10/2025</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Sección Barcelona</t>
+          <t>Vídeo del partido</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5986,10 +6006,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Cita literal de Vini hacia Yamal en la tangana.</t>
+        </is>
+      </c>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -6006,27 +6030,27 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Marca (titular hoy)</t>
+          <t>AS (titular sobre Vinicius)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>El Real Madrid se escapa.</t>
+          <t>Vinicius valora la opción de salir si todo sigue igual. Vinicius siente que ha cumplido con su parte, pero no se está respetando su estatus. La opción de marcharse se valora seriamente.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Marca 27/10/2025</t>
+          <t>AS 27/10/2025</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Marco Ruiz</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6039,21 +6063,17 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>Snap Marca 27/10/2025 17:12 UTC.</t>
-        </is>
-      </c>
+      <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20251027171200/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -6063,27 +6083,27 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Marca (titular hoy)</t>
+          <t>AS (debate de usuarios)</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>El Madrid quiere la fiesta en paz.</t>
+          <t>El 'vámonos fuera' de Lamine a Carvajal es un gesto de soberbia.</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Marca 28/10/2025</t>
+          <t>AS 27/10/2025</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>El debate de los usuarios</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6098,34 +6118,34 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Snap Marca 28/10/2025 18:52 UTC.</t>
+          <t>Frase del día tras la bronca.</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20251028185200/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2002-11-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Cochinillo a Figo</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>AS (encuesta portada)</t>
+          <t>AS (titular crónica)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>¿Crees que debe clausurarse el Camp Nou?</t>
+          <t>Marcó Bellingham y Vinicius no pudo contenerse: el gesto del que pocos se percataron.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6135,12 +6155,12 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>AS 24/11/2002</t>
+          <t>AS 28/10/2025</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>AStv</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -6153,36 +6173,32 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>Snap AS 24/11/2002 22:26 UTC.</t>
-        </is>
-      </c>
+      <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20021124222600/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2002-11-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Cochinillo a Figo</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruyff (sobre Joan Gaspart)</t>
+          <t>AS (Sergio López)</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Al presidente le queda cada vez menos.</t>
+          <t>El 'Caso Vinicius' se expande.</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6192,12 +6208,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>AS 24/11/2002</t>
+          <t>AS 28/10/2025</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Sección Madrid</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -6210,11 +6226,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>Cruyff sobre la situación de Gaspart como presidente del Barça.</t>
-        </is>
-      </c>
+      <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
@@ -6224,37 +6236,37 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2002-11-24</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Cochinillo a Figo</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Luis Figo</t>
+          <t>El País (Lorenzo Calonge)</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>(Figo pide perdón por decir 'mongolo'.)</t>
+          <t>La victoria en el clásico refuerza a Xabi Alonso, que afronta el mayor desafío de Vinicius a su autoridad. El necesitado triunfo blanco impulsa el proyecto del técnico, que debe gestionar el desaire más grave del brasileño dentro de un vestuario con más de un morro torcido.</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>AS 24/11/2002</t>
+          <t>El País 27/10/2025</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Crónica El Clásico</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -6267,51 +6279,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>Tras los lanzamientos de objetos en el Camp Nou.</t>
-        </is>
-      </c>
+      <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2002-11-24</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Cochinillo a Figo</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Medina Cantalejo (árbitro)</t>
+          <t>Xabi Alonso (a El País)</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>(Medina pensó en la suspensión del partido.)</t>
+          <t>El equipo necesitaba la sensación de ganar un partido grande.</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>AS 24/11/2002</t>
+          <t>El País 26/10/2025</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6326,49 +6334,49 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>El árbitro suspendió el encuentro 15 minutos por los lanzamientos a Figo.</t>
+          <t>Por Lorenzo Calonge. Xabi anuncia que hablará por supuesto con Vinicius.</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2002-11-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Previa Cochinillo Figo</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Pilar Rahola (escritora, a Sport)</t>
+          <t>El País (David Álvarez)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Ganar al Real Madrid se merece un orgasmo.</t>
+          <t>El Madrid reconquista el clásico. Tras cuatro derrotas seguidas, el equipo de Xabi Alonso arrolla a un Barça mermado por las bajas y con Lamine Yamal desaparecido con un partido de gran intensidad en el que volvió a brillar Bellingham y se distancia cinco puntos en cabeza.</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Sport 22/11/2002</t>
+          <t>El País 26/10/2025</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Entrevista</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6381,51 +6389,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>Periodista catalana en programa de entrevistas.</t>
-        </is>
-      </c>
+      <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2002-11-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Previa Cochinillo Figo</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Patrick Kluivert (a Sport)</t>
+          <t>Markus Sorg (2º entrenador del Barça)</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Me toca marcar en un Barça-Madrid. La última vez que marqué en un partido con el FC Barcelona, hizo un 'hat trick' al Alavés.</t>
+          <t>Lamine está aprendiendo, le ayudaremos.</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Sport 22/11/2002</t>
+          <t>El País 26/10/2025</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6438,47 +6442,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Yamal estuvo en el foco, abucheado por el Bernabéu y enfrentado a Carvajal y Vinicius.</t>
+        </is>
+      </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2002-11-22</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Previa Cochinillo Figo</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Luis Enrique (lesionado, mensaje desde grada)</t>
+          <t>El País (Manuel Jabois opinión)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Cuando pite el árbitro, seré un socio más dando apoyo al equipo desde la grada.</t>
+          <t>Este infernal y precioso olor al viejo Clásico de siempre.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Sport 22/11/2002</t>
+          <t>El País 27/10/2025</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Mensaje del capitán</t>
+          <t>Opinión</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6491,51 +6499,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>Lucho Enrique no jugó el partido, ya estaba como capitán retirado en grada.</t>
-        </is>
-      </c>
+      <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2002-11-22</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Previa Cochinillo Figo</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Sport (titular)</t>
+          <t>El País (Daniel Verdú, París)</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Ronaldo mete cizaña en el vestuario del Madrid.</t>
+          <t>Lamine, algo tan grave.</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Sport 22/11/2002</t>
+          <t>El País 28/10/2025</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Opinión desde París</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6548,51 +6552,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>Ronaldo Nazário en su último Clásico antes de la baja.</t>
-        </is>
-      </c>
+      <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2002-11-22</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Previa Cochinillo Figo</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Vizcaíno Casas (escritor, a Sport)</t>
+          <t>El País (Juan I. Irigoyen)</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Los jugadores de antes sí sentían los colores.</t>
+          <t>Los dilemas de Flick en su segundo año en el Barcelona. La política del club y la gestión de Lamine preocupan a un técnico sin respuestas tácticas.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Sport 22/11/2002</t>
+          <t>El País 28/10/2025</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Entrevista</t>
+          <t>Sección Barcelona</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6608,44 +6608,44 @@
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2005-11-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho ovación Bernabéu</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Joan Gaspart (a AS)</t>
+          <t>Marca (titular hoy)</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Lo de Figo fue un robo y lo de Eto'o no.</t>
+          <t>El Real Madrid se escapa.</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>AS 20/11/2005</t>
+          <t>Marca 27/10/2025</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6660,44 +6660,44 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Ex-presidente del Barça comparando los fichajes Figo→Madrid (2000) y Eto'o→Barça.</t>
+          <t>Snap Marca 27/10/2025 17:12 UTC.</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/20251027171200/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2005-11-23</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho ovación Bernabéu</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Sport (titular)</t>
+          <t>Marca (titular hoy)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho, a un gol de sus 'bodas de oro' azulgranas. El 'crack' brasileño del Barça Ronaldinho, que maravilla a propios y extraños en cada partido que disputa, está a un solo tanto de alcanzar los 50 goles con la camiseta azulgrana.</t>
+          <t>El Madrid quiere la fiesta en paz.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Sport 23/11/2005</t>
+          <t>Marca 28/10/2025</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -6717,49 +6717,49 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Snap Sport 23/11/2005 01:19 UTC.</t>
+          <t>Snap Marca 28/10/2025 18:52 UTC.</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20051123011900/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/20251028185200/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>2005-11-23</t>
+          <t>2002-11-24</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho ovación Bernabéu</t>
+          <t>Cochinillo a Figo</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Ll. Mascaró (Sport, La ventana indiscreta)</t>
+          <t>AS (encuesta portada)</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Gamper creó al Barça... y Ronaldinho lo lleva a la gloria.</t>
+          <t>¿Crees que debe clausurarse el Camp Nou?</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Sport 23/11/2005</t>
+          <t>AS 24/11/2002</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Columna de opinión</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6772,47 +6772,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Snap AS 24/11/2002 22:26 UTC.</t>
+        </is>
+      </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/20021124222600/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2005-11-23</t>
+          <t>2002-11-24</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho ovación Bernabéu</t>
+          <t>Cochinillo a Figo</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>J. Prats (Sport, Línea directa)</t>
+          <t>Johan Cruyff (sobre Joan Gaspart)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho, el crack generoso.</t>
+          <t>Al presidente le queda cada vez menos.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Sport 23/11/2005</t>
+          <t>AS 24/11/2002</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Columna de opinión</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6825,47 +6829,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Cruyff sobre la situación de Gaspart como presidente del Barça.</t>
+        </is>
+      </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2005-11-23</t>
+          <t>2002-11-24</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho ovación Bernabéu</t>
+          <t>Cochinillo a Figo</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>J.M. Casanovas (Sport, Mi verdad)</t>
+          <t>Luis Figo</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>El Barça, un equipo que sólo sabe ganar.</t>
+          <t>(Figo pide perdón por decir 'mongolo'.)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Sport 23/11/2005</t>
+          <t>AS 24/11/2002</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Editorial</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6878,47 +6886,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Tras los lanzamientos de objetos en el Camp Nou.</t>
+        </is>
+      </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2005-11-21</t>
+          <t>2002-11-24</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho ovación Bernabéu</t>
+          <t>Cochinillo a Figo</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Sport (encuesta del día)</t>
+          <t>Medina Cantalejo (árbitro)</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>¿Quién es mejor jugador? Pelé / Maradona / Ronaldinho.</t>
+          <t>(Medina pensó en la suspensión del partido.)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Sport 21/11/2005</t>
+          <t>AS 24/11/2002</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6933,49 +6945,49 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Pone a Ronaldinho a la altura de Pelé y Maradona tras ovación Bernabéu.</t>
+          <t>El árbitro suspendió el encuentro 15 minutos por los lanzamientos a Figo.</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>2011-04-25</t>
+          <t>2002-11-22</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Pre-Clásico Champions</t>
+          <t>Previa Cochinillo Figo</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Andrés Iniesta (RP previa)</t>
+          <t>Pilar Rahola (escritora, a Sport)</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Todos conocemos a Guardiola. Yo no creo que quisiera decir eso. El máster no busca excusas.</t>
+          <t>Ganar al Real Madrid se merece un orgasmo.</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>Sport (web)</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Marca 25/04/2011</t>
+          <t>Sport 22/11/2002</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>RP previa</t>
+          <t>Entrevista</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6990,49 +7002,49 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>Defensa pública del Pep tras críticas de Mou.</t>
+          <t>Periodista catalana en programa de entrevistas.</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2011-04-25</t>
+          <t>2002-11-22</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Pre-Clásico Champions</t>
+          <t>Previa Cochinillo Figo</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruyff (a El Periódico)</t>
+          <t>Patrick Kluivert (a Sport)</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Más que temer quién pitará o si el césped estará alto, preocúpate de tu equipo. El Madrid llega más fuerte.</t>
+          <t>Me toca marcar en un Barça-Madrid. La última vez que marqué en un partido con el FC Barcelona, hizo un 'hat trick' al Alavés.</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>El Periódico (vía Marca)</t>
+          <t>Sport (web)</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>El Periódico 25/04/2011</t>
+          <t>Sport 22/11/2002</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Columna</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -7045,76 +7057,1359 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>Recadito de Cruyff a Pep.</t>
-        </is>
-      </c>
+      <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>2002-11-22</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Previa Cochinillo Figo</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Luis Enrique (lesionado, mensaje desde grada)</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Cuando pite el árbitro, seré un socio más dando apoyo al equipo desde la grada.</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Sport (web)</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Sport 22/11/2002</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Mensaje del capitán</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Lucho Enrique no jugó el partido, ya estaba como capitán retirado en grada.</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2002-11-22</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Previa Cochinillo Figo</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Sport (titular)</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldo mete cizaña en el vestuario del Madrid.</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Sport (web)</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Sport 22/11/2002</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Portada digital</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldo Nazário en su último Clásico antes de la baja.</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2002-11-22</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Previa Cochinillo Figo</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Vizcaíno Casas (escritor, a Sport)</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Los jugadores de antes sí sentían los colores.</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Sport (web)</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Sport 22/11/2002</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2005-11-20</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho ovación Bernabéu</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Joan Gaspart (a AS)</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Lo de Figo fue un robo y lo de Eto'o no.</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>AS (web)</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>AS 20/11/2005</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Declaraciones</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Ex-presidente del Barça comparando los fichajes Figo→Madrid (2000) y Eto'o→Barça.</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2005-11-23</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho ovación Bernabéu</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Sport (titular)</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho, a un gol de sus 'bodas de oro' azulgranas. El 'crack' brasileño del Barça Ronaldinho, que maravilla a propios y extraños en cada partido que disputa, está a un solo tanto de alcanzar los 50 goles con la camiseta azulgrana.</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Sport (web)</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Sport 23/11/2005</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Portada digital</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>Snap Sport 23/11/2005 01:19 UTC.</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20051123011900/https://www.sport.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2005-11-23</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho ovación Bernabéu</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Ll. Mascaró (Sport, La ventana indiscreta)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Gamper creó al Barça... y Ronaldinho lo lleva a la gloria.</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Sport (web)</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Sport 23/11/2005</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Columna de opinión</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2005-11-23</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho ovación Bernabéu</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>J. Prats (Sport, Línea directa)</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho, el crack generoso.</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Sport (web)</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Sport 23/11/2005</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Columna de opinión</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2005-11-23</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho ovación Bernabéu</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>J.M. Casanovas (Sport, Mi verdad)</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>El Barça, un equipo que sólo sabe ganar.</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Sport (web)</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Sport 23/11/2005</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Editorial</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2005-11-21</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldinho ovación Bernabéu</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Sport (encuesta del día)</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>¿Quién es mejor jugador? Pelé / Maradona / Ronaldinho.</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Sport (web)</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Sport 21/11/2005</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Portada digital</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Pone a Ronaldinho a la altura de Pelé y Maradona tras ovación Bernabéu.</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
           <t>2011-04-25</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Pre-Clásico Champions</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Iniesta (RP previa)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Todos conocemos a Guardiola. Yo no creo que quisiera decir eso. El máster no busca excusas.</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Marca (web)</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Marca 25/04/2011</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>RP previa</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Defensa pública del Pep tras críticas de Mou.</t>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2011-04-25</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Clásico Champions</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Johan Cruyff (a El Periódico)</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Más que temer quién pitará o si el césped estará alto, preocúpate de tu equipo. El Madrid llega más fuerte.</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>El Periódico (vía Marca)</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>El Periódico 25/04/2011</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Columna</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>Recadito de Cruyff a Pep.</t>
+        </is>
+      </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2011-04-25</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Clásico Champions</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>Víctor Valdés (RP previa)</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Dependerá del árbitro que podamos hacer nuestro juego. No hay que obsesionarse con estas cosas. Tenemos que ir a lo nuestro y hacer el partido que nos interesa.</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Mundo Deportivo (web)</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>MD 25/04/2011</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>RP previa</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Wayback Machine (archive.org)</t>
         </is>
       </c>
-      <c r="I119" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
         <is>
           <t>Snap MD 25/04/2011 08:55 UTC.</t>
         </is>
       </c>
-      <c r="K119" s="4" t="inlineStr">
+      <c r="K130" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20110425085500/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>1988-07-15</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Schuster ficha por el Madrid</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Ramón Mendoza (presidente Real Madrid)</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Es un fichaje con intriga, que daría un susto pequeño o grande a su gran rival.</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>ABC 15/07/1988</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Sección Deportes</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital ABC</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>Schuster ficha gratis del Barça por el Madrid en julio 1988. Recogida también en La Galerna 'Schuster: genio y conflicto' (2014).</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.abc.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>1988-07-15</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Schuster ficha por el Madrid</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Bernd Schuster</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>He recuperado las ganas por el fútbol. Llego motivado y con ganas de hacer las cosas bien para ganar títulos.</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Marca 15/07/1988</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Presentación oficial</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital BNE (Marca 1988)</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Tras su fichaje. En el primer Clásico al Camp Nou (1988) salió escoltado por la policía.</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>1958-1960</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera (entrenador Barça)</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Me preguntan por qué solo dirijo clubes grandes y es que los pequeños no pueden pagarme.</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Mundo Deportivo entrevista años 1958-60</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Parcial (atribución repetida)</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Pionero del entrenador mediático. Recogida en Panenka 'El primer técnico mediático' (2014).</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>1958-1960</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera (entrenador Barça)</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Ganar sin bajar del autobús. (Antes de un partido en Sevilla)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Marca crónica años 50-60</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital BNE</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Frase repetida en biografía 'Helenio Herrera' (Maxi Fink, T&amp;B Editores 2003).</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>1958-1960</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera (entrenador Barça)</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Al fútbol se juega mejor con diez que con once.</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>La Vanguardia</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>La Vanguardia años 50-60</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital La Vanguardia</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Parcial (atribución repetida)</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Aforismo característico de HH.</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lavanguardia.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>1958-1960</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera (entrenador Barça)</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>He pasado por clubes como el Barcelona, el Sevilla y el Inter; he dirigido las selecciones de Francia y de España y nunca he conocido el fracaso.</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista MD años 60-70</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Frase repetida en biografía y prensa retrospectiva.</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2015-07-12</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Casillas se despide del Madrid</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Iker Casillas</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Después de 25 años defendiendo el escudo del mejor club del mundo, llega un día difícil... despedirme de esta institución que me lo ha dado todo.</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Marca 13/07/2015</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Portada y páginas Deportes</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital Marca + RP en directo</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Sin homenaje oficial. Casillas solo en sala de prensa tras 25 años. Recogida también por El País 13/07/2015 y AS.</t>
+        </is>
+      </c>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2015-07-12</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Casillas se despide del Madrid</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Iker Casillas</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Son treinta segundos pero me llevará casi una hora. (El discurso duró 8 minutos entre lágrimas)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>El País</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>El País 13/07/2015</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Sección Deportes</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital El País + RP</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2015-07-12</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Casillas se despide del Madrid</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Iker Casillas</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Se terminó.</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>AS 13/07/2015</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Portada</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital AS + RP en directo</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Cierre de la rueda de prensa de despedida.</t>
+        </is>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>https://as.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2011-08</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Casillas y Xavi Premio Asturias</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Xavi Hernández</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Fue por el bien del fútbol español. (Sobre la llamada de Casillas para frenar el conflicto)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>El País</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista El País agosto 2011</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Sección Deportes</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital El País</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Mou se enfureció con Casillas; le acusaría más tarde de ser 'el topo'.</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Zidane primer Clásico como entrenador</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Zinedine Zidane</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>El Barcelona es un equipo que siempre ha sido fuerte. Cada entrenador tiene cosas diferentes, pero el Barça siempre es el Barça. Es un equipo competitivo que sabe jugar muy buen fútbol y que te pone difíciles las cosas.</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Marca</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Marca 1/04/2016</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Sección Deportes RP previa</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital Marca + RP en directo</t>
+        </is>
+      </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>Madrid 2-1 Barça. Cortó la racha de 39 partidos invicto del Barça.</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marca.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Zidane filosofía de equipo</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Zinedine Zidane</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Estábamos a disposición de los jugadores. Para mí, es lo que hace fuerte al equipo, estás ahí para el jugador.</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>AS</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>AS entrevista 2017</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Sección Deportes</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca digital AS</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>https://as.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K119"/>
+  <autoFilter ref="A1:K142"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -7173,67 +8468,89 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7245,7 +8562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7321,146 +8638,146 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1902-05-13</t>
+          <t>1983-06-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Primer Clásico</t>
+          <t>Maradona ovacionado Bernabéu</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Madrid FC vs FC Barcelona</t>
+          <t>Diego Armando Maradona</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Madrid FC 1 - 3 FC Barcelona. Primer Clásico de la historia. Los catalanes, con más experiencia (3 años), ganan al recién creado Madrid FC.</t>
+          <t>Carrasco me la dio en mitad de campo, me llevé al portero por delante y esperé a Juan José, que ya venía, y le dejé pasar. Se rompió las pelotas contra el palo y yo la empujé. Después nos cruzamos y le pedí perdón. Me mandó a la mierda.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Wikipedia / RFEF</t>
+          <t>Olé (entrevista)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>Olé, años después</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Documental</t>
+          <t>Prensa secundaria</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Sí (hecho histórico)</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Copa de la Coronación, semifinal. Hipódromo (Madrid).</t>
+          <t>Final Copa de la Liga ida, Bernabéu 2-2.</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_El_Cl%C3%A1sico_matches</t>
+          <t>https://www.ole.com.ar/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1929-02-17</t>
+          <t>1983-09-24</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Primer Clásico de Liga</t>
+          <t>Goikoetxea-Maradona</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>FC Barcelona vs Real Madrid</t>
+          <t>Diego Maradona</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Real Madrid 2-1 FC Barcelona. Primer Clásico de la primera Liga española.</t>
+          <t>Me partió el tobillo en nuestro campo, a 60 metros del arco de ellos. Nunca creí que iba a venirme a buscar con tanta mala leche. Cuando paro la pelota, siento un 'crack', como cuando se rompe una madera.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Wikipedia / RFEF</t>
+          <t>TyC Sports / Olé</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>Documental 'Maradona en Sinaloa' 2003 + entrevista TyC 1995</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Documental</t>
+          <t>Documental + entrevista TV</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Sí (hecho histórico)</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Les Corts, 2ª jornada de la 1ª Liga.</t>
+          <t>Fractura del maléolo peroneal. Citado en doc 'Maradona' (Asif Kapadia, 2019) y libro 'Yo soy el Diego' (Planeta, 2000).</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_El_Cl%C3%A1sico_matches</t>
+          <t>https://www.ole.com.ar/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1953-07-24</t>
+          <t>1990s-2000s</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Di Stéfano ficha</t>
+          <t>Goikoetxea-Maradona</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Alfredo Di Stéfano</t>
+          <t>Andoni Goikoetxea</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Yo he venido a España para jugar en el Barcelona.</t>
+          <t>Fue una acción más del partido, no merezco ninguna sanción. Viví lo peor y lo mejor del fútbol con solo cuatro días de diferencia, por eso las guardo (las botas).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Panenka</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Marca 24/07/1953</t>
+          <t>Reportaje retrospectivo 'Barro y gloria'</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7470,59 +8787,59 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Parcial (no localizada en hemeroteca BNE)</t>
+          <t>Prensa retrospectiva</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Acabó fichando por el Madrid. Caso histórico.</t>
+          <t>Sancionado con 18 partidos (rebajados a 7-10). Frase recogida en 'Andoni Goikoetxea: barro y gloria' Panenka.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://www.panenka.org/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1953-10-25</t>
+          <t>2003-2004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Di Stéfano vs Kubala</t>
+          <t>Stoichkov</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Daucik (entrenador Barça)</t>
+          <t>Hristo Stoichkov</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Di Stéfano es más ágil y resistente, pero no llega al nivel de Kubala en concepción del juego.</t>
+          <t>Siempre voy a odiar al Real Madrid. Es más fácil que se abra la tierra a que yo acepte trabajar en ese club. El Real Madrid me da ganas de vomitar.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Marca octubre 1953</t>
+          <t>Sport entrevista febrero 2003</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Página deportes</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -7530,56 +8847,56 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Análisis previo al primer Di Stéfano-Kubala.</t>
+          <t>Recogido también en Milenio (México).</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://www.sport.es/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1953-10-25</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Di Stéfano vs Kubala</t>
+          <t>Stoichkov</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Hristo Stoichkov</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kubala, el mejor interior del mundo.</t>
+          <t>El Madrid me da asco, nunca me veréis con una camiseta blanca.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Mundo Deportivo</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Marca octubre 1953</t>
+          <t>Mundo Deportivo entrevista enero 1996</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Titular</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -7589,214 +8906,226 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+          <t>Parcial (atribución repetida)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Frase de Stoichkov en su segunda etapa Barça (1996-1998).</t>
+        </is>
+      </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1953-10-25</t>
+          <t>2011-04-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Di Stéfano vs Kubala</t>
+          <t>RP del 'puto jefe'</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>La Vanguardia</t>
+          <t>Pep Guardiola</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>La gente solo se fija en dos hombres: Kubala y Di Stéfano.</t>
+          <t>Como Mou me trata de Pep, yo le voy a tratar de José. No le conozco personalmente, pero al gerente que sí le conoce, mañana a las 8.45 nos enfrentamos en el campo. Fuera del campo, él ya ha ganado todo el año. Que se lleve la Champions personal fuera del campo, se la regalo y nos vamos a casa. En esta sala (de prensa), él es el puto jefe, el puto amo. Yo no quiero competir con él aquí ni un instante.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>La Vanguardia</t>
+          <t>Libertad Digital, Goal, TUDN</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>La Vanguardia octubre 1953</t>
+          <t>26/04/2011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Corresponsal Madrid</t>
+          <t>Bernabéu (sala de prensa)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
+          <t>Prensa primaria contemporánea</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Rueda de prensa previa Champions semifinal.</t>
+        </is>
+      </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.lavanguardia.com/</t>
+          <t>https://www.goal.com/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1965-09-26</t>
+          <t>2011-04-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Era Bernabéu presidente</t>
+          <t>RP UNICEF Mou</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Santiago Bernabéu (presidente Madrid)</t>
+          <t>José Mourinho</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>El colegiado Leafe fue el mejor jugador del Barça.</t>
+          <t>¿Por qué? ¿Por qué? Yo no entiendo por qué. No sé si es por la publicidad de UNICEF, no sé si son muy simpáticos. Stark, Ovrebo, De Bleeckere, Bussaca... no entiendo por qué.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Memoria oral / Futbol Gate</t>
+          <t>Libertad Digital</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27/04/2011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sala de prensa Bernabéu</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Documental</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+          <t>Prensa primaria contemporánea</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Comentario sarcástico sobre arbitraje.</t>
+          <t>Tras roja a Pepe en 0-2 Champions.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.futbolgate.com/</t>
+          <t>https://www.libertaddigital.com/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1965-09-26</t>
+          <t>2011-04-27</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Era Bernabéu presidente</t>
+          <t>RP UNICEF Mou</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Francisco Gento</t>
+          <t>José Mourinho</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Se quería que otro club ganara la Copa de Europa, no siempre el mismo.</t>
+          <t>Guardiola ha ganado una Champions que a mí me daría vergüenza haber ganado.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Memoria oral</t>
+          <t>Libertad Digital</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27/04/2011</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sala de prensa Bernabéu</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Documental</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+          <t>Prensa primaria contemporánea</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.libertaddigital.com/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1983-06-26</t>
+          <t>2011-08-17</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Maradona ovacionado Bernabéu</t>
+          <t>Dedo en el ojo a Tito Vilanova</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Diego Armando Maradona</t>
+          <t>José Mourinho (acción)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Carrasco me la dio en mitad de campo, me llevé al portero por delante y esperé a Juan José, que ya venía, y le dejé pasar. Se rompió las pelotas contra el palo y yo la empujé. Después nos cruzamos y le pedí perdón. Me mandó a la mierda.</t>
+          <t>(Mourinho mete el dedo en el ojo a Tito Vilanova, segundo de Pep, durante tangana al final del partido.)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Olé (entrevista)</t>
+          <t>Goal, El Nacional, vídeo viral</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Olé, años después</t>
+          <t>17/08/2011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Camp Nou</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Vídeo + prensa</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -7806,44 +9135,44 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Final Copa de la Liga ida, Bernabéu 2-2.</t>
+          <t>Sanción: 2 partidos. Imagen icónica con 'El Observador' (Francesc Satorra).</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.ole.com.ar/</t>
+          <t>https://www.goal.com/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1983-09-24</t>
+          <t>Posterior</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Goikoetxea-Maradona</t>
+          <t>Dedo en el ojo a Tito Vilanova</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Diego Maradona</t>
+          <t>José Mourinho</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Me partió el tobillo en nuestro campo, a 60 metros del arco de ellos. Nunca creí que iba a venirme a buscar con tanta mala leche. Cuando paro la pelota, siento un 'crack', como cuando se rompe una madera.</t>
+          <t>Fallé. (Tras la muerte de Vilanova)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Múltiples (ESPN, Vice, La Nación)</t>
+          <t>El Nacional</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Diversas entrevistas posteriores</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7861,46 +9190,42 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Fractura del maléolo peroneal.</t>
-        </is>
-      </c>
+      <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/</t>
+          <t>https://www.elnacional.cat/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1983-09-24</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Goikoetxea-Maradona</t>
+          <t>Casillas-Mourinho topo</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>César Luis Menotti (entrenador Barça)</t>
+          <t>Iker Casillas</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Deberá morirse alguien para que cambien las cosas.</t>
+          <t>Asumí que yo era el topo.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Prensa española época</t>
+          <t>Infobae, El Español, Libertad Digital</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Sept 1983</t>
+          <t>Documental 2020</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7910,7 +9235,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -7918,38 +9243,46 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Reconciliación posterior.</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elespanol.com/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1983-09-24</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Goikoetxea-Maradona</t>
+          <t>Casillas-Mourinho topo</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Javier Clemente (entrenador Athletic)</t>
+          <t>Antón Meana (Cadena SER)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Estoy orgulloso de mis jugadores.</t>
+          <t>Topo ninguno. Había filtraciones y alguna filtración salía permanentemente del cuerpo técnico de Mourinho.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Prensa española época</t>
+          <t>Defensa Central</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Sept 1983</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7959,7 +9292,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -7968,37 +9301,41 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.defensacentral.com/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1983-09-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Goikoetxea-Maradona</t>
+          <t>Casillas-Mourinho posterior</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Andoni Goikoetxea</t>
+          <t>Iker Casillas</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Fue una acción más del partido, no merezco ninguna sanción. Viví lo peor y lo mejor del fútbol con solo cuatro días de diferencia, por eso las guardo (las botas).</t>
+          <t>La gente se queda con el odio (hate), pero con el tiempo todo cambia.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Múltiples (Panenka, ESPN)</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Posterior</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8008,7 +9345,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -8016,56 +9353,52 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Sancionado con 18 partidos (rebajados a 7-10).</t>
-        </is>
-      </c>
+      <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/</t>
+          <t>https://www.infobae.com/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2015-11-21</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Stoichkov</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Hristo Stoichkov</t>
+          <t>Andrés Iniesta</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Siempre voy a odiar al Real Madrid. Es más fácil que se abra la tierra a que yo acepte trabajar en ese club. El Real Madrid me da ganas de vomitar.</t>
+          <t>Quiero agradecer a los fans. Nos sentimos muy bien, jugamos un partido completo en todos los sentidos. Les dimos pocas opciones, apenas perdimos el balón.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Múltiples (Milenio, Facebook FCBarcelonista)</t>
+          <t>Sphera Sports, Tribuna, Goal</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>21/11/2015</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bernabéu</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -8073,52 +9406,56 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Madrid 0-4 Barça.</t>
+        </is>
+      </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.milenio.com/</t>
+          <t>https://www.goal.com/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2000s</t>
+          <t>2015-11-21</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Stoichkov</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Hristo Stoichkov</t>
+          <t>Luis Enrique (entrenador Barça)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>El Madrid me da asco, nunca me veréis con una camiseta blanca.</t>
+          <t>Andrés Iniesta es patrimonio de la humanidad, no sólo de los culés.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Múltiples</t>
+          <t>Sphera Sports, beIN</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>21/11/2015</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -8127,47 +9464,51 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.spherasports.com/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2002-11-23</t>
+          <t>2017-04-23</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cochinillo a Figo</t>
+          <t>Ramos-Piqué</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Luis Figo</t>
+          <t>Sergio Ramos</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>No me siento ni Judas ni traidor.</t>
+          <t>¡Habla ahora, habla ahora!</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Memorias del Fútbol / Infobae</t>
+          <t>Líbero, Goal</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Posterior</t>
+          <t>23/04/2017</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bernabéu</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Vídeo + prensa</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -8177,49 +9518,49 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Lanzamientos: cabeza de cochinillo, botellas whisky, agua, móviles. Pancartas 'Judas'. 110 dB.</t>
+          <t>Tras roja a Ramos, señalando a la grada hacia Piqué.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/</t>
+          <t>https://www.goal.com/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2011-04-26</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>RP del 'puto jefe'</t>
+          <t>Ramos-Piqué</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Pep Guardiola</t>
+          <t>Gerard Piqué</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Como Mou me trata de Pep, yo le voy a tratar de José. No le conozco personalmente, pero al gerente que sí le conoce, mañana a las 8.45 nos enfrentamos en el campo. Fuera del campo, él ya ha ganado todo el año. Que se lleve la Champions personal fuera del campo, se la regalo y nos vamos a casa. En esta sala (de prensa), él es el puto jefe, el puto amo. Yo no quiero competir con él aquí ni un instante.</t>
+          <t>Desde el palco del Bernabéu se mueven los hilos del país. Se va a arrepentir cuando llegue a casa. Mi relación con él (Ramos) no es muy buena, pero está mejorando.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Libertad Digital, Goal, TUDN</t>
+          <t>Goal, Líbero</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26/04/2011</t>
+          <t>Abril 2017</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Bernabéu (sala de prensa)</t>
+          <t>Twitter / RP</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -8232,11 +9573,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Rueda de prensa previa Champions semifinal.</t>
-        </is>
-      </c>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
           <t>https://www.goal.com/</t>
@@ -8246,42 +9583,42 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2011-04-27</t>
+          <t>Posterior</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>RP UNICEF Mou</t>
+          <t>Pepe-Piqué</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho</t>
+          <t>Gerard Piqué</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>¿Por qué? ¿Por qué? Yo no entiendo por qué. No sé si es por la publicidad de UNICEF, no sé si son muy simpáticos. Stark, Ovrebo, De Bleeckere, Bussaca... no entiendo por qué.</t>
+          <t>Una escena monumental. Ver esa roja [a Pepe] fue uno de los mayores placeres que he tenido en mi vida.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Libertad Digital</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27/04/2011</t>
+          <t>Posterior</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Sala de prensa Bernabéu</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Prensa secundaria</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -8289,56 +9626,52 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Tras roja a Pepe en 0-2 Champions.</t>
-        </is>
-      </c>
+      <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.libertaddigital.com/</t>
+          <t>https://www.goal.com/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2011-04-27</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RP UNICEF Mou</t>
+          <t>2-6 Pep primer año</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho</t>
+          <t>Carles Puyol</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Guardiola ha ganado una Champions que a mí me daría vergüenza haber ganado.</t>
+          <t>(Celebra besando el brazalete de capitán con la bandera catalana ante la afición del Bernabéu.)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Libertad Digital</t>
+          <t>Bleacher Report</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27/04/2011</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Sala de prensa Bernabéu</t>
+          <t>Bernabéu</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Vídeo histórico</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -8346,52 +9679,56 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Madrid 2-6 Barça.</t>
+        </is>
+      </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.libertaddigital.com/</t>
+          <t>https://www.bleacherreport.com/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2011-08-17</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito Vilanova</t>
+          <t>Puyol Clásicos Leyendas</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho (acción)</t>
+          <t>Carles Puyol</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>(Mourinho mete el dedo en el ojo a Tito Vilanova, segundo de Pep, durante tangana al final del partido.)</t>
+          <t>Un clásico siempre es un clásico. Todos quieren ganar.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Goal, El Nacional, vídeo viral</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17/08/2011</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Camp Nou</t>
+          <t>Costa Rica (Clásico Leyendas)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Vídeo + prensa</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -8399,56 +9736,52 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Sanción: 2 partidos. Imagen icónica con 'El Observador' (Francesc Satorra).</t>
-        </is>
-      </c>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://www.goal.com/</t>
+          <t>https://www.infobae.com/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Posterior</t>
+          <t>2022-2024</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito Vilanova</t>
+          <t>Cristiano vs Messi</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho</t>
+          <t>Cristiano Ronaldo</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Fallé. (Tras la muerte de Vilanova)</t>
+          <t>¿Messi es mejor que yo? No estoy de acuerdo. No quiero ser humilde.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>El Nacional</t>
+          <t>Piers Morgan / La Nación</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>Entrevistas múltiples</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -8459,49 +9792,49 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.elnacional.cat/</t>
+          <t>https://www.lanacion.com.ar/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Casillas-Mourinho topo</t>
+          <t>Cristiano vs Messi</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Iker Casillas</t>
+          <t>Cristiano Ronaldo</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Asumí que yo era el topo.</t>
+          <t>Nos respetamos mucho. No somos amigos, pero compartimos 15 años en el stage de los premios y siempre nos llevamos muy bien. La prensa siempre quiso vender que éramos enemigos, pero no es cierto.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Infobae, El Español, Libertad Digital</t>
+          <t>Piers Morgan Uncensored</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Documental 2020</t>
+          <t>Entrevista TalkTV 14-15/11/2022</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Episodios completos</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Vídeo TV</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -8511,44 +9844,44 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Reconciliación posterior.</t>
+          <t>Entrevista de tres partes con Piers Morgan, emitida en TalkTV y YouTube de Piers Morgan Uncensored.</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://www.elespanol.com/</t>
+          <t>https://www.youtube.com/@PiersMorganUncensored/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Casillas-Mourinho topo</t>
+          <t>Messi sobre Cristiano</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Antón Meana (Cadena SER)</t>
+          <t>Lionel Messi</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Topo ninguno. Había filtraciones y alguna filtración salía permanentemente del cuerpo técnico de Mourinho.</t>
+          <t>Una batalla, entre comillas. (Sobre los Clásicos)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Defensa Central</t>
+          <t>L'Équipe (tras Balón de Oro)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8569,39 +9902,39 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.defensacentral.com/</t>
+          <t>https://www.lequipe.fr/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Casillas-Mourinho posterior</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Iker Casillas</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>La gente se queda con el odio (hate), pero con el tiempo todo cambia.</t>
+          <t>El Madrid es el rival a batir.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>Marzo 2025</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8611,7 +9944,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -8622,49 +9955,49 @@
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/</t>
+          <t>https://as.com/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Andrés Iniesta</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Quiero agradecer a los fans. Nos sentimos muy bien, jugamos un partido completo en todos los sentidos. Les dimos pocas opciones, apenas perdimos el balón.</t>
+          <t>Roban, se quejan… (sobre el Madrid en transmisión Kings League con Ibai)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sphera Sports, Tribuna, Goal</t>
+          <t>Twitch / Stream Ibai</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21/11/2015</t>
+          <t>Stream Ibai 25/10/2025 Kings League</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Bernabéu</t>
+          <t>Transmisión en vivo</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Stream + cobertura prensa</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -8674,54 +10007,54 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Madrid 0-4 Barça.</t>
+          <t>Recogido por Infobae, Eurosport, SDP Noticias el 25-26/10/2025. Yamal estaba con Ibai Llanos en transmisión Kings League previa al Clásico.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.goal.com/</t>
+          <t>https://www.twitch.tv/ibai/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Bronca Yamal-Carvajal</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Luis Enrique (entrenador Barça)</t>
+          <t>Vinicius Junior</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Andrés Iniesta es patrimonio de la humanidad, no sólo de los culés.</t>
+          <t>Solo das pases atrás, solo das pases atrás. Tú hablas mucho, habla ahora.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Sphera Sports, beIN</t>
+          <t>Infobae, Eurosport, SDP Noticias</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21/11/2015</t>
+          <t>Tras Madrid 2-1 Barça</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bernabéu</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Vídeo + prensa</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -8729,42 +10062,46 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Eco directo al 'habla ahora' de Sergio Ramos a Piqué de 2017.</t>
+        </is>
+      </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://www.spherasports.com/</t>
+          <t>https://www.eurosport.es/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2017-04-23</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Ramos-Piqué</t>
+          <t>Bronca Yamal-Carvajal</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Sergio Ramos</t>
+          <t>Dani Carvajal (capitán Madrid)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>¡Habla ahora, habla ahora!</t>
+          <t>Tú hablas mucho. Tú hablas mucho.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Líbero, Goal</t>
+          <t>Infobae, Eurosport</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23/04/2017</t>
+          <t>Tras Madrid 2-1 Barça</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8782,56 +10119,52 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Tras roja a Ramos, señalando a la grada hacia Piqué.</t>
-        </is>
-      </c>
+      <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.goal.com/</t>
+          <t>https://www.eurosport.es/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Ramos-Piqué</t>
+          <t>El Chiringuito</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Gerard Piqué</t>
+          <t>Tomás Roncero</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Desde el palco del Bernabéu se mueven los hilos del país. Se va a arrepentir cuando llegue a casa. Mi relación con él (Ramos) no es muy buena, pero está mejorando.</t>
+          <t>Porque el coronavirus no me deja, pero me lanzaba a darte un abrazo ahora mismo.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Goal, Líbero</t>
+          <t>El Chiringuito (Atresmedia)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Abril 2017</t>
+          <t>Mega Atresmedia abril 2020</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Twitter / RP</t>
+          <t>Programa especial</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Vídeo TV</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -8839,52 +10172,56 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Roncero a Pedrerol durante confinamiento. Recogido por Diez Minutos.</t>
+        </is>
+      </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://www.goal.com/</t>
+          <t>https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Posterior</t>
+          <t>2017-2024</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Pepe-Piqué</t>
+          <t>El Chiringuito</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Gerard Piqué</t>
+          <t>Josep Pedrerol</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Una escena monumental. Ver esa roja [a Pepe] fue uno de los mayores placeres que he tenido en mi vida.</t>
+          <t>El ADN del Madrid es la leche. Cuando damos al Madrid por perdido, gana títulos.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>El Chiringuito (Atresmedia)</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Posterior</t>
+          <t>Mega Atresmedia múltiples episodios</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cabecera del programa</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Vídeo TV</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -8892,52 +10229,56 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Frase recurrente de Pedrerol como mantra del programa.</t>
+        </is>
+      </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.goal.com/</t>
+          <t>https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2-6 Pep primer año</t>
+          <t>El Chiringuito</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Carles Puyol</t>
+          <t>Edu Aguirre</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>(Celebra besando el brazalete de capitán con la bandera catalana ante la afición del Bernabéu.)</t>
+          <t>Messi es un 7 en todo, pero no es un 10 en nada.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Bleacher Report</t>
+          <t>El Chiringuito (Atresmedia)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>Programa Mega Atresmedia 2018</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Bernabéu</t>
+          <t>Mesa de redacción</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Vídeo histórico</t>
+          <t>Vídeo TV</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -8947,49 +10288,49 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Madrid 2-6 Barça.</t>
+          <t>Recogido por El Nacional 'Edu Aguirre Messi 7 todo 10 nada'. Frase polémica del comentarista.</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.bleacherreport.com/</t>
+          <t>https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Puyol Clásicos Leyendas</t>
+          <t>Schuster retrospectiva</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Carles Puyol</t>
+          <t>Bernd Schuster</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Un clásico siempre es un clásico. Todos quieren ganar.</t>
+          <t>No me fui al Madrid para joder al Barça ni al Atleti para joder al Madrid. Son cosas que pasan.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Líbero</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Líbero entrevista 2014</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Costa Rica (Clásico Leyendas)</t>
+          <t>Sección Fútbol Internacional</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -9002,52 +10343,56 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista retrospectiva al ex-jugador en revistalibero.com.</t>
+        </is>
+      </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/</t>
+          <t>https://www.libero.pe/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Cristiano vs Messi</t>
+          <t>Hugo Sánchez sobre el Clásico</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo</t>
+          <t>Hugo Sánchez</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>¿Messi es mejor que yo? No estoy de acuerdo. No quiero ser humilde.</t>
+          <t>No necesitas motivación extra contra Barcelona, el mismo rival te la da.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Piers Morgan / La Nación</t>
+          <t>CNN Español</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Entrevistas múltiples</t>
+          <t>CNN Deportes abril 2023</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Programa CNN Deportes</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Vídeo TV</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -9055,52 +10400,56 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Único mexicano que marcó en El Clásico. Goleador histórico del Madrid contra el Barça.</t>
+        </is>
+      </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/</t>
+          <t>https://www.cnnespanol.cnn.com/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Cristiano vs Messi</t>
+          <t>Hugo Sánchez sobre el Clásico</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo</t>
+          <t>Hugo Sánchez</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Nos respetamos mucho. No somos amigos, pero compartimos 15 años en el stage de los premios y siempre nos llevamos muy bien. La prensa siempre quiso vender que éramos enemigos, pero no es cierto.</t>
+          <t>¿Cuántas tiene el Madrid y cuántas el Barcelona? (En referencia a Ligas y Champions)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Múltiples</t>
+          <t>TUDN</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TUDN 21/04/2024</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Programa La Última Palabra</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Vídeo TV</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -9108,38 +10457,46 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Burla sobre los títulos en directo en TUDN.</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tudn.com/</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2012-09-05</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Messi sobre Cristiano</t>
+          <t>Casillas y Xavi Premio Asturias</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Lionel Messi</t>
+          <t>Iker Casillas + Xavi Hernández</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Una batalla, entre comillas. (Sobre los Clásicos)</t>
+          <t>(Premio Príncipe de Asturias de los Deportes 2012, símbolo de reconciliación tras la guerra Mou-Pep)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>L'Équipe (tras Balón de Oro)</t>
+          <t>BOE / Fundación Princesa de Asturias</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>Acta del Jurado 5/09/2012</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9149,7 +10506,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Acta institucional</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -9157,42 +10514,42 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>https://www.lequipe.fr/</t>
-        </is>
-      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Tras los 4 Clásicos en 18 días (2011), Casillas llamó a Xavi y Puyol para frenar el conflicto. Acta: fpa.es/es/premios-princesa-de-asturias/premiados/2012-iker-casillas-y-xavi-hernandez.html</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Cruyff (atribución dudosa)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Johan Cruyff</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>El Madrid es el rival a batir.</t>
+          <t>Preferiría perder un Clásico que un partido cualquiera.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>Frases de Futbolistas (sin fuente primaria)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Marzo 2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9202,50 +10559,54 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr"/>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>NO — posiblemente apócrifa</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>No localizada en fuentes primarias.</t>
+        </is>
+      </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://as.com/</t>
+          <t>https://www.frasesdefutbolistas.com/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Cristiano Ronaldo (atribución dudosa)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Cristiano Ronaldo</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Roban, se quejan… (sobre el Madrid en transmisión Kings League con Ibai)</t>
+          <t>Siempre intento cuidar mi cuerpo, la comida y dormir, que es muy importante.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Múltiples (Infobae, Eurosport)</t>
+          <t>frasesdefutbolistas.com</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Octubre 2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9255,1294 +10616,27 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Stream + prensa</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr"/>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>NO — sin fuente primaria</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Coherente con su discurso pero atribución exacta no localizada.</t>
+        </is>
+      </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://www.eurosport.es/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Bronca Yamal-Carvajal</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Vinicius Junior</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Solo das pases atrás, solo das pases atrás. Tú hablas mucho, habla ahora.</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Infobae, Eurosport, SDP Noticias</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Tras Madrid 2-1 Barça</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Bernabéu</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Vídeo + prensa</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Eco directo al 'habla ahora' de Sergio Ramos a Piqué de 2017.</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>https://www.eurosport.es/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Bronca Yamal-Carvajal</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Dani Carvajal (capitán Madrid)</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Tú hablas mucho. Tú hablas mucho.</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Infobae, Eurosport</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Tras Madrid 2-1 Barça</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Bernabéu</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Vídeo + prensa</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>https://www.eurosport.es/</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>2010s-2020s</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>El Chiringuito</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Tomás Roncero</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Porque el coronavirus no me deja, pero me lanzaba a darte un abrazo ahora mismo.</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Diez Minutos / El Chiringuito</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Vídeo TV</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>https://www.diezminutos.es/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>2010s-2020s</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>El Chiringuito</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Josep Pedrerol</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>El ADN del Madrid es la leche. Cuando damos al Madrid por perdido, gana títulos.</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>El Chiringuito</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Vídeo TV</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>2010s-2020s</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>El Chiringuito</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Edu Aguirre</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Messi es un 7 en todo, pero no es un 10 en nada.</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>El Nacional</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Vídeo TV</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>https://www.elnacional.cat/</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>1988-07</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Schuster ficha por el Madrid</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Ramón Mendoza (presidente Real Madrid)</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Es un fichaje con intriga, que daría un susto pequeño o grande a su gran rival.</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>La Galerna</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Prensa retrospectiva</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Schuster ficha gratis del Barça por el Madrid en julio 1988.</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>https://www.lagalerna.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>1988-1990</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Schuster ficha por el Madrid</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Bernd Schuster</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>No me fui al Madrid para joder al Barça ni al Atleti para joder al Madrid. Son cosas que pasan.</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Líbero</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista retrospectiva</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>https://www.libero.pe/</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>1988-1990</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Schuster ficha por el Madrid</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Bernd Schuster</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>He recuperado las ganas por el fútbol. Llego motivado y con ganas de hacer las cosas bien para ganar títulos.</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Líbero</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Tras su fichaje. En el primer Clásico al Camp Nou (1988) salió escoltado por la policía.</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>https://www.libero.pe/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Hugo Sánchez sobre el Clásico</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Hugo Sánchez</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>No necesitas motivación extra contra Barcelona, el mismo rival te la da.</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>CNN Español</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista 2023</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista TV</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Único mexicano que marcó en El Clásico. Goleador histórico del Madrid contra el Barça.</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>https://www.cnnespanol.cnn.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Hugo Sánchez sobre el Clásico</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Hugo Sánchez</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>¿Cuántas tiene el Madrid y cuántas el Barcelona? (En referencia a Ligas y Champions)</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>TUDN</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>TV</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>Burla sobre los títulos.</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tudn.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>1958-1960</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Helenio Herrera (entrenador Barça)</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Helenio Herrera</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Me preguntan por qué solo dirijo clubes grandes y es que los pequeños no pueden pagarme.</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Panenka</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Recopilación frases</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Cita retrospectiva</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Pionero del entrenador mediático. Influyó en Mourinho.</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>https://www.panenka.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>1958-1960</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Helenio Herrera (entrenador Barça)</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Helenio Herrera</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Ganar sin bajar del autobús. (Antes de un partido en Sevilla)</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Panenka</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Cita retrospectiva</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>https://www.panenka.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>1958-1960</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Helenio Herrera (entrenador Barça)</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Helenio Herrera</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Al fútbol se juega mejor con diez que con once.</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>La Pelota No Dobla</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Recopilación frases</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Cita retrospectiva</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>https://www.la-pelota-no-dobla.blogspot.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>1958-1960</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Helenio Herrera (entrenador Barça)</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Helenio Herrera</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>He pasado por clubes como el Barcelona, el Sevilla y el Inter; he dirigido las selecciones de Francia y de España y nunca he conocido el fracaso.</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Panenka</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Cita retrospectiva</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>https://www.panenka.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>2015-07-12</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Casillas se despide del Madrid</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Iker Casillas</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Después de 25 años defendiendo el escudo del mejor club del mundo, llega un día difícil... despedirme de esta institución que me lo ha dado todo.</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Emol</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Rueda de prensa Bernabéu 12/07/2015</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Sala de prensa</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>RP en directo</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>Sin homenaje oficial. Casillas solo en sala de prensa tras 25 años.</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>https://www.emol.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>2015-07-12</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Casillas se despide del Madrid</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Iker Casillas</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Son treinta segundos pero me llevará casi una hora. (El discurso duró 8 minutos entre lágrimas)</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Emol</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Rueda de prensa Bernabéu 12/07/2015</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Sala de prensa</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>RP en directo</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>https://www.emol.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>2015-07-12</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Casillas se despide del Madrid</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Iker Casillas</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Se terminó.</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>El Universal (México)</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>12/07/2015</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>RP en directo</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>Cierre de la rueda de prensa de despedida.</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>https://www.eluniversal.com.mx/</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Casillas y Xavi Premio Asturias</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Iker Casillas + Xavi Hernández</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>(Premio Príncipe de Asturias de los Deportes 2012, símbolo de reconciliación tras la guerra Mou-Pep)</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Memorias del Fútbol</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Hecho institucional</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>Tras los 4 Clásicos en 18 días (2011), Casillas llamó a Xavi y Puyol para frenar el conflicto.</t>
-        </is>
-      </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>https://www.memoriasdelfutbol.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>2011 verano</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Casillas y Xavi Premio Asturias</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Xavi Hernández</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Fue por el bien del fútbol español. (Sobre la llamada de Casillas para frenar el conflicto)</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>El Español</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista retrospectiva</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Mou se enfureció con Casillas; le acusaría más tarde de ser 'el topo'.</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>https://www.elespanol.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>2016-04-02</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Zidane primer Clásico como entrenador</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Zinedine Zidane</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>El Barcelona es un equipo que siempre ha sido fuerte. Cada entrenador tiene cosas diferentes, pero el Barça siempre es el Barça. Es un equipo competitivo que sabe jugar muy buen fútbol y que te pone difíciles las cosas.</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>La Nación</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Previa Camp Nou 2/04/2016</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>RP previa</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>Madrid 2-1 Barça. Cortó la racha de 39 partidos invicto del Barça.</t>
-        </is>
-      </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>https://www.lanacion.com.ar/</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>2016-2018</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Zidane filosofía de equipo</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Zinedine Zidane</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Estábamos a disposición de los jugadores. Para mí, es lo que hace fuerte al equipo, estás ahí para el jugador.</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>ESPN</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>https://www.espn.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Cruyff (atribución dudosa)</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Johan Cruyff</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Preferiría perder un Clásico que un partido cualquiera.</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Frases de Futbolistas (sin fuente primaria)</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Atribuida</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>NO — posiblemente apócrifa</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>No localizada en fuentes primarias.</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>https://www.frasesdefutbolistas.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Cristiano Ronaldo (atribución dudosa)</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Cristiano Ronaldo</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Siempre intento cuidar mi cuerpo, la comida y dormir, que es muy importante.</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>frasesdefutbolistas.com</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Atribuida</t>
-        </is>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>NO — sin fuente primaria</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>Coherente con su discurso pero atribución exacta no localizada.</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
           <t>https://as.com/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K60"/>
+  <autoFilter ref="A1:K37"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -10551,53 +10645,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -3284,7 +3284,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://www.lavanguardia.com/</t>
+          <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1902-05-14&amp;fechaFin=1902-05-14</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>https://www.lavanguardia.com/</t>
+          <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1929-02-18&amp;fechaFin=1929-02-18</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://hemerotecadigital.bne.es/hd/es/results?titulo=marca&amp;fechaFin=1953-07-24&amp;fechaInicio=1953-07-24</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>https://www.lavanguardia.com/</t>
+          <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1953-10-25&amp;fechaFin=1953-10-25</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://hemerotecadigital.bne.es/hd/es/results?titulo=marca&amp;fechaFin=1953-10-26&amp;fechaInicio=1953-10-26</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>https://www.lavanguardia.com/</t>
+          <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1953-10-26&amp;fechaFin=1953-10-26</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://www.abc.es/</t>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19650922.html</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://www.abc.es/</t>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19650922.html</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://www.abc.es/</t>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19830925.html</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20021125120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>https://www.abc.es/</t>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19880715.html</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://hemerotecadigital.bne.es/hd/es/results?titulo=marca&amp;fechaFin=1988-07-15&amp;fechaInicio=1988-07-15</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/1958/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://hemerotecadigital.bne.es/</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>https://www.lavanguardia.com/</t>
+          <t>https://web.archive.org/web/1958/https://www.lavanguardia.com/</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/1958/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20150713120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8180,7 @@
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/20150713120000/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>https://as.com/</t>
+          <t>https://web.archive.org/web/20150713120000/https://as.com/</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/2011/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/2016/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>https://as.com/</t>
+          <t>https://web.archive.org/web/2017/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.ole.com.ar/</t>
+          <t>https://web.archive.org/web/1983/https://www.ole.com.ar/</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.ole.com.ar/</t>
+          <t>https://web.archive.org/web/2003/https://www.ole.com.ar/</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.sport.es/</t>
+          <t>https://web.archive.org/web/2003/https://www.sport.es/</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/1996/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.goal.com/</t>
+          <t>https://web.archive.org/web/20110426120000/https://www.goal.com/</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.libertaddigital.com/</t>
+          <t>https://web.archive.org/web/20110427120000/https://www.libertaddigital.com/</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.libertaddigital.com/</t>
+          <t>https://web.archive.org/web/20110427120000/https://www.libertaddigital.com/</t>
         </is>
       </c>
     </row>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.goal.com/</t>
+          <t>https://web.archive.org/web/20110817120000/https://www.goal.com/</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.elespanol.com/</t>
+          <t>https://web.archive.org/web/2020/https://www.elespanol.com/</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.defensacentral.com/</t>
+          <t>https://web.archive.org/web/2020/https://www.defensacentral.com/</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/</t>
+          <t>https://web.archive.org/web/20251023120000/https://www.infobae.com/</t>
         </is>
       </c>
     </row>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.goal.com/</t>
+          <t>https://web.archive.org/web/20151121120000/https://www.goal.com/</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.spherasports.com/</t>
+          <t>https://web.archive.org/web/20151121120000/https://www.spherasports.com/</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.goal.com/</t>
+          <t>https://web.archive.org/web/20170423120000/https://www.goal.com/</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.goal.com/</t>
+          <t>https://web.archive.org/web/2017/https://www.goal.com/</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.bleacherreport.com/</t>
+          <t>https://web.archive.org/web/2009/https://www.bleacherreport.com/</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/</t>
+          <t>https://web.archive.org/web/2025/https://www.infobae.com/</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/</t>
+          <t>https://web.archive.org/web/2022/https://www.lanacion.com.ar/</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@PiersMorganUncensored/</t>
+          <t>https://web.archive.org/web/20221115120000/https://www.youtube.com/@PiersMorganUncensored/</t>
         </is>
       </c>
     </row>
@@ -9902,7 +9902,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.lequipe.fr/</t>
+          <t>https://web.archive.org/web/2023/https://www.lequipe.fr/</t>
         </is>
       </c>
     </row>
@@ -9955,7 +9955,7 @@
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://as.com/</t>
+          <t>https://web.archive.org/web/2025/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.twitch.tv/ibai/</t>
+          <t>https://web.archive.org/web/20251025120000/https://www.twitch.tv/ibai/</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://www.eurosport.es/</t>
+          <t>https://web.archive.org/web/2025/https://www.eurosport.es/</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10122,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.eurosport.es/</t>
+          <t>https://web.archive.org/web/2025/https://www.eurosport.es/</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
+          <t>https://web.archive.org/web/2020/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
+          <t>https://web.archive.org/web/2017/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
     </row>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
+          <t>https://web.archive.org/web/2018/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
     </row>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.libero.pe/</t>
+          <t>https://web.archive.org/web/2014/https://www.libero.pe/</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnnespanol.cnn.com/</t>
+          <t>https://web.archive.org/web/2023/https://www.cnnespanol.cnn.com/</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.tudn.com/</t>
+          <t>https://web.archive.org/web/20240421120000/https://www.tudn.com/</t>
         </is>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/</t>
+          <t>https://web.archive.org/web/20150527120000/https://www.espn.com/</t>
         </is>
       </c>
     </row>
@@ -10969,7 +10969,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.fox8.com/</t>
+          <t>https://web.archive.org/web/2014/https://www.fox8.com/</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.sport.es/</t>
+          <t>https://web.archive.org/web/2014/https://www.sport.es/</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.nbcsports.com/</t>
+          <t>https://web.archive.org/web/2008/https://www.nbcsports.com/</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.semana.es/</t>
+          <t>https://web.archive.org/web/2025/https://www.semana.es/</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.gq.com/</t>
+          <t>https://web.archive.org/web/2026/https://www.gq.com/</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.womenshealthmag.com/</t>
+          <t>https://web.archive.org/web/2021/https://www.womenshealthmag.com/</t>
         </is>
       </c>
     </row>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/</t>
+          <t>https://web.archive.org/web/20230423120000/https://www.instagram.com/</t>
         </is>
       </c>
     </row>
@@ -12053,7 +12053,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/</t>
+          <t>https://web.archive.org/web/2026/https://www.cnbc.com/</t>
         </is>
       </c>
     </row>
@@ -12375,7 +12375,7 @@
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.olympics.com/</t>
+          <t>https://web.archive.org/web/2025/https://www.olympics.com/</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12481,7 @@
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://www.womenshealthmag.com/</t>
+          <t>https://web.archive.org/web/2020/https://www.womenshealthmag.com/</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.womenshealthmag.com/</t>
+          <t>https://web.archive.org/web/2020/https://www.womenshealthmag.com/</t>
         </is>
       </c>
     </row>
@@ -12644,7 +12644,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.elespanol.com/</t>
+          <t>https://web.archive.org/web/2026/https://www.elespanol.com/</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://www.elespanol.com/</t>
+          <t>https://web.archive.org/web/2026/https://www.elespanol.com/</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.elespanol.com/</t>
+          <t>https://web.archive.org/web/2026/https://www.elespanol.com/</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.thesefootballtimes.co/</t>
+          <t>https://web.archive.org/web/19740217120000/https://www.thesefootballtimes.co/</t>
         </is>
       </c>
     </row>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/1988/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.elgrafico.com.ar/</t>
+          <t>https://web.archive.org/web/1986/https://www.elgrafico.com.ar/</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.ole.com.ar/</t>
+          <t>https://web.archive.org/web/2000/https://www.ole.com.ar/</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/2000/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/2003/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/1992/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.abc.es/</t>
+          <t>https://web.archive.org/web/1985/https://www.abc.es/</t>
         </is>
       </c>
     </row>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/1978/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20000716120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13869,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://as.com/</t>
+          <t>https://web.archive.org/web/2018/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.elmundo.es/</t>
+          <t>https://web.archive.org/web/2024/https://www.elmundo.es/</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.elperiodico.com/</t>
+          <t>https://web.archive.org/web/2003/https://www.elperiodico.com/</t>
         </is>
       </c>
     </row>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/2021/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -14089,7 +14089,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.rac1.cat/</t>
+          <t>https://web.archive.org/web/2023/https://www.rac1.cat/</t>
         </is>
       </c>
     </row>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20021123120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14199,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.thetimes.co.uk/</t>
+          <t>https://web.archive.org/web/2003/https://www.thetimes.co.uk/</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://www.tycsports.com/</t>
+          <t>https://web.archive.org/web/2007/https://www.tycsports.com/</t>
         </is>
       </c>
     </row>
@@ -14305,7 +14305,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.tribuna.com/</t>
+          <t>https://web.archive.org/web/2024/https://www.tribuna.com/</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/2003/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -14415,7 +14415,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/19991010120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -14468,7 +14468,7 @@
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://as.com/</t>
+          <t>https://web.archive.org/web/20100724120000/https://as.com/</t>
         </is>
       </c>
     </row>
@@ -14521,7 +14521,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/2011/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://as.com/</t>
+          <t>https://web.archive.org/web/2010/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -14631,7 +14631,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20110426120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14688,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.rocaeditorial.com/</t>
+          <t>https://web.archive.org/web/2010/https://www.rocaeditorial.com/</t>
         </is>
       </c>
     </row>
@@ -14741,7 +14741,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/2012/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -14794,7 +14794,7 @@
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20180710120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://as.com/</t>
+          <t>https://web.archive.org/web/2014/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -14900,7 +14900,7 @@
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@PiersMorganUncensored/</t>
+          <t>https://web.archive.org/web/2022/https://www.youtube.com/@PiersMorganUncensored/</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.penguinrandomhouse.com/</t>
+          <t>https://web.archive.org/web/2011/https://www.penguinrandomhouse.com/</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15010,7 @@
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://www.penguinrandomhouse.com/</t>
+          <t>https://web.archive.org/web/2011/https://www.penguinrandomhouse.com/</t>
         </is>
       </c>
     </row>
@@ -15063,7 +15063,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://www.penguinrandomhouse.com/</t>
+          <t>https://web.archive.org/web/2011/https://www.penguinrandomhouse.com/</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://www.francefootball.fr/</t>
+          <t>https://web.archive.org/web/2007/https://www.francefootball.fr/</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15275,7 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20100711120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -15328,7 +15328,7 @@
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>https://as.com/</t>
+          <t>https://web.archive.org/web/20170423120000/https://as.com/</t>
         </is>
       </c>
     </row>
@@ -15381,7 +15381,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/2014/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://www.rac1.cat/</t>
+          <t>https://web.archive.org/web/2014/https://www.rac1.cat/</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15491,7 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>https://www.elperiodico.com/</t>
+          <t>https://web.archive.org/web/2017/https://www.elperiodico.com/</t>
         </is>
       </c>
     </row>
@@ -15544,7 +15544,7 @@
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>https://www.rac1.cat/</t>
+          <t>https://web.archive.org/web/2018/https://www.rac1.cat/</t>
         </is>
       </c>
     </row>
@@ -15597,7 +15597,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/2012/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -15650,7 +15650,7 @@
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/2010/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -15703,7 +15703,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/2018/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20090502120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -15813,7 +15813,7 @@
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/</t>
+          <t>https://web.archive.org/web/2024/https://www.bbc.com/</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/</t>
+          <t>https://web.archive.org/web/2024/https://www.espn.com/</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15923,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/2022/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -15980,7 +15980,7 @@
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>https://www.elperiodico.com/</t>
+          <t>https://web.archive.org/web/1980/https://www.elperiodico.com/</t>
         </is>
       </c>
     </row>
@@ -16037,7 +16037,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://www.lavanguardia.com/</t>
+          <t>https://web.archive.org/web/19680117120000/https://www.lavanguardia.com/</t>
         </is>
       </c>
     </row>
@@ -16090,7 +16090,7 @@
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpuntavui.cat/</t>
+          <t>https://web.archive.org/web/2003/https://www.elpuntavui.cat/</t>
         </is>
       </c>
     </row>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://www.abc.es/</t>
+          <t>https://web.archive.org/web/2000/https://www.abc.es/</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/2004/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -16253,7 +16253,7 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpuntavui.cat/</t>
+          <t>https://web.archive.org/web/2004/https://www.elpuntavui.cat/</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/2003/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -16530,7 +16530,7 @@
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://www.cadenaser.com/</t>
+          <t>https://web.archive.org/web/2014/https://www.cadenaser.com/</t>
         </is>
       </c>
     </row>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/2007/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://www.abc.es/</t>
+          <t>https://web.archive.org/web/1989/https://www.abc.es/</t>
         </is>
       </c>
     </row>
@@ -16697,7 +16697,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/2008/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -16754,7 +16754,7 @@
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://www.lasexta.com/</t>
+          <t>https://web.archive.org/web/2000/https://www.lasexta.com/</t>
         </is>
       </c>
     </row>
@@ -16864,7 +16864,7 @@
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>https://www.cope.es/</t>
+          <t>https://web.archive.org/web/2014/https://www.cope.es/</t>
         </is>
       </c>
     </row>
@@ -16917,7 +16917,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://www.as.com/</t>
+          <t>https://web.archive.org/web/2000/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16970,7 @@
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
+          <t>https://web.archive.org/web/2010/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>https://www.movistarplus.es/</t>
+          <t>https://web.archive.org/web/2000/https://www.movistarplus.es/</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://www.cadenaser.com/</t>
+          <t>https://web.archive.org/web/2012/https://www.cadenaser.com/</t>
         </is>
       </c>
     </row>
@@ -17137,7 +17137,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/2018/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -17190,7 +17190,7 @@
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>https://as.com/</t>
+          <t>https://web.archive.org/web/2010/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -17243,7 +17243,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>https://www.gazzetta.it/</t>
+          <t>https://web.archive.org/web/2007/https://www.gazzetta.it/</t>
         </is>
       </c>
     </row>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://www.elperiodico.com/</t>
+          <t>https://web.archive.org/web/2010/https://www.elperiodico.com/</t>
         </is>
       </c>
     </row>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>https://www.sport.es/</t>
+          <t>https://web.archive.org/web/2015/https://www.sport.es/</t>
         </is>
       </c>
     </row>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>https://www.marca.com/</t>
+          <t>https://web.archive.org/web/2024/https://www.marca.com/</t>
         </is>
       </c>
     </row>

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -8797,12 +8797,12 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Sancionado con 18 partidos (rebajados a 7-10). Frase recogida en 'Andoni Goikoetxea: barro y gloria' Panenka.</t>
+          <t>Sancionado con 18 partidos (rebajados a 7-10). Frase recogida en 'Andoni Goikoetxea: barro y gloria' Panenka. URL: https://www.panenka.org/pasaportes/andoni-goikoetxea-barro-y-gloria/</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.panenka.org/</t>
+          <t>https://www.panenka.org/pasaportes/andoni-goikoetxea-barro-y-gloria/</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9147,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Posterior</t>
+          <t>2014-04-25</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Fallé. (Tras la muerte de Vilanova)</t>
+          <t>Fallé. (Tras la muerte de Vilanova en abril 2014)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -9172,17 +9172,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>El Nacional 25/04/2014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -9190,10 +9190,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.elnacional.cat/es/deportes/arrepentimiento-mourinho-dedo-ojo-tito-vilanova-fcbarcelona-madrid_626021_102.html</t>
+        </is>
+      </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.elnacional.cat/</t>
+          <t>https://www.elnacional.cat/es/deportes/arrepentimiento-mourinho-dedo-ojo-tito-vilanova-fcbarcelona-madrid_626021_102.html</t>
         </is>
       </c>
     </row>
@@ -13131,7 +13135,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Recopilación de frases</t>
+          <t>Recopilación de frases (atribución)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -13141,17 +13145,17 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Prensa retrospectiva</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Parcial — atribución repetida en biografías y recopilaciones</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Frase legendaria atribuida a Cruyff en distintas entrevistas.</t>
+          <t>Cita característica del estilo Cruyff. Aparece en biografías y libros de frases pero no localizada en entrevista primaria con fecha exacta.</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -13751,15 +13755,19 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Parcial — atribución repetida en libros y prensa retrospectiva</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Frase recogida en libros sobre Núñez (1978-2000); fuente primaria exacta no localizada en hemeroteca digital.</t>
+        </is>
+      </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.elperiodico.com/</t>
+          <t>https://web.archive.org/web/1978/https://www.elperiodico.com/</t>
         </is>
       </c>
     </row>
@@ -13933,12 +13941,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2003-2010</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Laporta presidente Barça</t>
+          <t>Laporta caso Negreira</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -13948,22 +13956,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>El Real Madrid es el equipo del régimen. El Barça siempre fue el club del pueblo.</t>
+          <t>El Real Madrid es un club que ha sido considerado el equipo del régimen. (Sobre los árbitros y los Comités históricos.)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>El Periódico</t>
+          <t>ESPN Deportes / eldiario.es</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Mitin elecciones 2003</t>
+          <t>Rueda de prensa Negreira 17/04/2023</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Auditorio FC Barcelona</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -13976,10 +13984,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.eldiario.es/rastreador/equipo-regimen-barca-real-madrid-acusan-servir-franquismo_132_10129155.html</t>
+        </is>
+      </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2003/https://www.elperiodico.com/</t>
+          <t>https://www.eldiario.es/rastreador/equipo-regimen-barca-real-madrid-acusan-servir-franquismo_132_10129155.html</t>
         </is>
       </c>
     </row>
@@ -16285,7 +16297,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Declaración años 80</t>
+          <t>Declaración años 80 (atribución)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -16295,17 +16307,17 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital ABC</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>NO — atribuida sin fuente primaria localizada</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Frase polémica que reavivó la rivalidad política.</t>
+          <t>Frase repetida en blogs y libros. La fuente primaria en hemeroteca ABC años 80 no localizada con esta cita literal.</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -16317,7 +16329,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Años 60-90</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -16332,27 +16344,27 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>El Barça es el ejército desarmado de Cataluña. La forma más eficaz de no rendirse a Madrid.</t>
+          <t>El Barça actúa como medio que establece contacto con la propia historia del pueblo catalán. (Versión 1969)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Triunfo / El País</t>
+          <t>Triunfo</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Múltiples artículos años 70-90</t>
+          <t>Triunfo 1969</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artículo</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria + libros</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -16362,19 +16374,19 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Vázquez Montalbán fue uno de los grandes intelectuales culés.</t>
+          <t>Primer artículo conocido del autor sobre Barça-Catalunya.</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/1969/https://www.triunfodigital.com/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Años 80</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -16389,27 +16401,27 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Si España fuera el Real Madrid, Cataluña sería siempre el FC Barcelona.</t>
+          <t>El Barça es el ejército desarmado de Cataluña. (Frase formal del título 'Barça, el ejército de un país desarmado')</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Cuadernos del Norte</t>
+          <t>Catalonia (revista)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Artículo años 80</t>
+          <t>Catalonia 1987 nº 1</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Página 45</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Prensa retrospectiva</t>
+          <t>Prensa primaria + libros</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -16417,10 +16429,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Artículo de referencia: 'Barça, el ejército de un país desarmado'. URL: https://dialnet.unirioja.es/servlet/articulo?codigo=1985572</t>
+        </is>
+      </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://www.cuadernosdefutbol.com/</t>
+          <t>https://dialnet.unirioja.es/servlet/articulo?codigo=1985572</t>
         </is>
       </c>
     </row>

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Clásico frases icónicas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$K$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$K$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$K$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$K$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dietas deportistas'!$A$1:$K$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clásico frases icónicas'!$A$1:$K$83</definedName>
   </definedNames>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K142"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3348,64 +3348,64 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1953-07-24</t>
+          <t>1953-10-25</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Di Stéfano ficha</t>
+          <t>Di Stéfano vs Kubala</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Alfredo Di Stéfano</t>
+          <t>Daucik (entrenador Barça)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Yo he venido a España para jugar en el Barcelona.</t>
+          <t>Di Stéfano es más ágil y resistente, pero no llega al nivel de Kubala en concepción del juego.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>La Vanguardia</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Marca 24/07/1953</t>
+          <t>La Vanguardia 25/10/1953</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Portada</t>
+          <t>Crónica previa</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital BNE (Marca 1953)</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>Parcial (microfilm BNE)</t>
+          <t>Hemeroteca digital La Vanguardia</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Acabó fichando por el Madrid. Caso histórico. BNE Hemeroteca: hemerotecadigital.bne.es/details.vm?lang=es&amp;q=Marca+1953</t>
+          <t>Análisis previo al primer Di Stéfano-Kubala. Hemeroteca: hemeroteca-paginas.lavanguardia.com/LVE07/PUB/1953/10/25/</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://hemerotecadigital.bne.es/hd/es/results?titulo=marca&amp;fechaFin=1953-07-24&amp;fechaInicio=1953-07-24</t>
+          <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1953-10-25&amp;fechaFin=1953-10-25</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1953-10-25</t>
+          <t>1953-10-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3415,47 +3415,43 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Daucik (entrenador Barça)</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Di Stéfano es más ágil y resistente, pero no llega al nivel de Kubala en concepción del juego.</t>
+          <t>Kubala, el mejor interior del mundo.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>La Vanguardia</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>La Vanguardia 25/10/1953</t>
+          <t>Marca 26/10/1953</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Crónica previa</t>
+          <t>Titular portada</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital La Vanguardia</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>Análisis previo al primer Di Stéfano-Kubala. Hemeroteca: hemeroteca-paginas.lavanguardia.com/LVE07/PUB/1953/10/25/</t>
-        </is>
-      </c>
+          <t>Hemeroteca digital BNE</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Parcial (microfilm BNE)</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1953-10-25&amp;fechaFin=1953-10-25</t>
+          <t>https://hemerotecadigital.bne.es/hd/es/results?titulo=marca&amp;fechaFin=1953-10-26&amp;fechaInicio=1953-10-26</t>
         </is>
       </c>
     </row>
@@ -3472,132 +3468,136 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>La Vanguardia</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Kubala, el mejor interior del mundo.</t>
+          <t>La gente solo se fija en dos hombres: Kubala y Di Stéfano.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>La Vanguardia</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Marca 26/10/1953</t>
+          <t>La Vanguardia 26/10/1953</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Titular portada</t>
+          <t>Corresponsal en Madrid</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital BNE</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>Parcial (microfilm BNE)</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr"/>
+          <t>Hemeroteca digital La Vanguardia</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Hemeroteca: hemeroteca-paginas.lavanguardia.com/LVE07/PUB/1953/10/26/</t>
+        </is>
+      </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://hemerotecadigital.bne.es/hd/es/results?titulo=marca&amp;fechaFin=1953-10-26&amp;fechaInicio=1953-10-26</t>
+          <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1953-10-26&amp;fechaFin=1953-10-26</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>1953-10-26</t>
+          <t>1983-09-25</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Di Stéfano vs Kubala</t>
+          <t>Goikoetxea-Maradona</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>La Vanguardia</t>
+          <t>César Luis Menotti (entrenador Barça)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>La gente solo se fija en dos hombres: Kubala y Di Stéfano.</t>
+          <t>Deberá morirse alguien para que cambien las cosas.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>La Vanguardia</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>La Vanguardia 26/10/1953</t>
+          <t>ABC 25/09/1983</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Corresponsal en Madrid</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital La Vanguardia</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Hemeroteca digital ABC</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Parcial (en crónica al día siguiente)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca: hemeroteca-paginas.lavanguardia.com/LVE07/PUB/1953/10/26/</t>
+          <t>Declaración del entrenador del Barça tras el partido.</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1953-10-26&amp;fechaFin=1953-10-26</t>
+          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19830925.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>1965-09-22</t>
+          <t>1983-09-25</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Era Bernabéu presidente</t>
+          <t>Goikoetxea-Maradona</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Santiago Bernabéu (presidente Madrid)</t>
+          <t>Javier Clemente (entrenador Athletic)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>El colegiado Leafe fue el mejor jugador del Barça.</t>
+          <t>Estoy orgulloso de mis jugadores.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>El Correo (Bilbao)</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>ABC 22/09/1965</t>
+          <t>El Correo 25/09/1983</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3607,231 +3607,227 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital ABC</t>
+          <t>Hemeroteca digital El Correo</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Parcial (atribución repetida en blogs y libros)</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Comentario sarcástico tras la eliminación europea del Madrid contra el Inter (semifinal Copa de Europa 1964-65). Frase recogida en la biografía 'Bernabéu y Saporta' (Marca, 2005).</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19650922.html</t>
-        </is>
-      </c>
+          <t>Declaración tras Athletic-Barça.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>1965-09-22</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Era Bernabéu presidente</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Francisco Gento</t>
+          <t>AS (titular)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Se quería que otro club ganara la Copa de Europa, no siempre el mismo.</t>
+          <t>Mourinho le metió un dedo en el ojo a Tito Vilanova. ¿Por qué? Por Messi.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>ABC 22/09/1965</t>
+          <t>AS 18/08/2011</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Sección Deportes</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital ABC</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Frase atribuida en la biografía 'Gento' (La Esfera, 2010).</t>
+          <t>Snap 18/08/2011 20:56 UTC.</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19650922.html</t>
+          <t>https://web.archive.org/web/20110818205600/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>1983-09-25</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Goikoetxea-Maradona</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>César Luis Menotti (entrenador Barça)</t>
+          <t>Joan Gaspart (recogido por AS)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Deberá morirse alguien para que cambien las cosas.</t>
+          <t>Mourinho tiene una doble personalidad. Aunque en Madrid estén encantados con él, no es el Mourinho que yo conocí. Le gustaría que todo terminara con una disculpa del luso.</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>ABC 25/09/1983</t>
+          <t>AS 18/08/2011</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Sección Deportes</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital ABC</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>Parcial (en crónica al día siguiente)</t>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Declaración del entrenador del Barça tras el partido.</t>
+          <t>Ex-presidente del Barça.</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19830925.html</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>1983-09-25</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Goikoetxea-Maradona</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Javier Clemente (entrenador Athletic)</t>
+          <t>Xavi Hernández (recogido por AS)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Estoy orgulloso de mis jugadores.</t>
+          <t>Es lamentable la imagen del Madrid. No están a la altura.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>El Correo (Bilbao)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>El Correo 25/09/1983</t>
+          <t>AS 18/08/2011</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Sección Deportes</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital El Correo</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>Declaración tras Athletic-Barça.</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr"/>
+          <t>Wayback Machine (archive.org)</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2002-11-25</t>
+          <t>2011-08-18</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Cochinillo a Figo</t>
+          <t>Dedo en el ojo a Tito</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Luis Figo</t>
+          <t>Gerard Piqué (recogido por AS)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>No me siento ni Judas ni traidor.</t>
+          <t>Mourinho se está cargando el fútbol español.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Marca 25/11/2002</t>
+          <t>AS 18/08/2011</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Páginas 1-3 Deportes</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital Marca</t>
+          <t>Wayback Machine (archive.org)</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3839,14 +3835,10 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>Lanzamientos: cabeza de cochinillo, botellas whisky, agua, móviles. Pancartas 'Judas'. 110 dB. Tras partido del 23/11/2002.</t>
-        </is>
-      </c>
+      <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20021125120000/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3855,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>AS (titular)</t>
+          <t>Joaquim Villarrubí (vicepresidente FC Barcelona)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Mourinho le metió un dedo en el ojo a Tito Vilanova. ¿Por qué? Por Messi.</t>
+          <t>Mourinho es una lacra para el fútbol. Fue el entrenador del Real Madrid quien obligó a sus jugadores a abandonar el campo cuando los jugadores del Barcelona recogían la Supercopa.</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3883,7 +3875,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3896,14 +3888,10 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Snap 18/08/2011 20:56 UTC.</t>
-        </is>
-      </c>
+      <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20110818205600/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
@@ -3920,12 +3908,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Joan Gaspart (recogido por AS)</t>
+          <t>AS (identificación 'tío del bigote')</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Mourinho tiene una doble personalidad. Aunque en Madrid estén encantados con él, no es el Mourinho que yo conocí. Le gustaría que todo terminara con una disculpa del luso.</t>
+          <t>Se llama Francesc Satorra y es el encargado del túnel de vestuarios del Camp Nou. Ayer vio cómo Mourinho le metía un dedo en el ojo a Tito Vilanova y hoy en internet ya se venden camisetas con su cara.</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3940,7 +3928,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3955,7 +3943,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Ex-presidente del Barça.</t>
+          <t>Identifica al fotógrafo viral del momento.</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -3977,27 +3965,27 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Xavi Hernández (recogido por AS)</t>
+          <t>Marca (titular crónica)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Es lamentable la imagen del Madrid. No están a la altura.</t>
+          <t>El Barcelona se lleva la Supercopa tras derrotar a un buen Real Madrid en un partidazo que acabó de forma vergonzosa.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>AS 18/08/2011</t>
+          <t>Marca 18/08/2011</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -4010,10 +3998,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Snap 18/08/2011 01:34 UTC.</t>
+        </is>
+      </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/20110818013400/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -4030,27 +4022,27 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Gerard Piqué (recogido por AS)</t>
+          <t>José Mourinho (a Marca)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Mourinho se está cargando el fútbol español.</t>
+          <t>De 'Pito' o como se llame no tengo nada que ocultar.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>AS 18/08/2011</t>
+          <t>Marca 18/08/2011</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4063,10 +4055,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Mourinho niega haber metido el dedo en el ojo a Tito Vilanova, vacilando con su nombre.</t>
+        </is>
+      </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -4083,27 +4079,27 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Joaquim Villarrubí (vicepresidente FC Barcelona)</t>
+          <t>Pep Guardiola (a Marca)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Mourinho es una lacra para el fútbol. Fue el entrenador del Real Madrid quien obligó a sus jugadores a abandonar el campo cuando los jugadores del Barcelona recogían la Supercopa.</t>
+          <t>Cuidado, porque un día nos haremos daño. Las imágenes hablan por sí solas.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>AS 18/08/2011</t>
+          <t>Marca 18/08/2011</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -4119,7 +4115,7 @@
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -4136,27 +4132,27 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>AS (identificación 'tío del bigote')</t>
+          <t>Pep Guardiola (a Mundo Deportivo)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Se llama Francesc Satorra y es el encargado del túnel de vestuarios del Camp Nou. Ayer vio cómo Mourinho le metía un dedo en el ojo a Tito Vilanova y hoy en internet ya se venden camisetas con su cara.</t>
+          <t>Un día pasará algo grave. Tenemos que andar con cuidado. Estas cosas no se deben hacer.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>AS 18/08/2011</t>
+          <t>MD 18/08/2011</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4171,12 +4167,12 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Identifica al fotógrafo viral del momento.</t>
+          <t>Sobre la agresión de Mourinho a Tito.</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -4193,12 +4189,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Marca (titular crónica)</t>
+          <t>Iker Casillas (a Marca)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>El Barcelona se lleva la Supercopa tras derrotar a un buen Real Madrid en un partidazo que acabó de forma vergonzosa.</t>
+          <t>Una entrada, al suelo y lo de siempre.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4213,7 +4209,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4228,12 +4224,12 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Snap 18/08/2011 01:34 UTC.</t>
+          <t>Capitán del Madrid sobre la tangana.</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20110818013400/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -4250,12 +4246,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho (a Marca)</t>
+          <t>Gerard Piqué (a Marca)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>De 'Pito' o como se llame no tengo nada que ocultar.</t>
+          <t>Espero no se hable de la tangana, es una pena, no es la primera vez y siempre son los mismos. Alguien tiene que tomar cartas en el asunto. Mourinho está destrozando el fútbol español. Hablan mucho de los catalanes, pero el problema lo tienen en Madrid.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4270,7 +4266,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Sala mixta</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4283,11 +4279,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>Mourinho niega haber metido el dedo en el ojo a Tito Vilanova, vacilando con su nombre.</t>
-        </is>
-      </c>
+      <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
@@ -4307,27 +4299,27 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Pep Guardiola (a Marca)</t>
+          <t>Gerard Piqué (a Mundo Deportivo)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Cuidado, porque un día nos haremos daño. Las imágenes hablan por sí solas.</t>
+          <t>Están haciendo cosas que no son propias de personas.</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Marca 18/08/2011</t>
+          <t>MD 18/08/2011</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Sala mixta</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4343,7 +4335,7 @@
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -4360,12 +4352,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Pep Guardiola (a Mundo Deportivo)</t>
+          <t>Mundo Deportivo (titular)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Un día pasará algo grave. Tenemos que andar con cuidado. Estas cosas no se deben hacer.</t>
+          <t>Los buenos siempre ganan. Un buen Madrid que ha acabado recurriendo a la violencia como única arma para frenar a los cracks barcelonistas.</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4380,7 +4372,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4393,11 +4385,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Sobre la agresión de Mourinho a Tito.</t>
-        </is>
-      </c>
+      <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
@@ -4417,27 +4405,27 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Iker Casillas (a Marca)</t>
+          <t>José Mourinho (a El País)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Una entrada, al suelo y lo de siempre.</t>
+          <t>El fútbol es para hombres.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Marca 18/08/2011</t>
+          <t>El País 18/08/2011</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Crónica de Nadia Tronchoni</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4452,12 +4440,12 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Capitán del Madrid sobre la tangana.</t>
+          <t>Frase tras la agresión a Tito Vilanova.</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -4474,27 +4462,27 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Gerard Piqué (a Marca)</t>
+          <t>El País (José Sámano)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Espero no se hable de la tangana, es una pena, no es la primera vez y siempre son los mismos. Alguien tiene que tomar cartas en el asunto. Mourinho está destrozando el fútbol español. Hablan mucho de los catalanes, pero el problema lo tienen en Madrid.</t>
+          <t>Messi sí que es único. El Madrid no puede con el argentino, el mayor castigo de su historia y artífice del triunfo del Barcelona en una Supercopa intensa.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Marca 18/08/2011</t>
+          <t>El País 18/08/2011</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Sala mixta</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4510,7 +4498,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -4527,27 +4515,27 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Gerard Piqué (a Mundo Deportivo)</t>
+          <t>El País (datos)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Están haciendo cosas que no son propias de personas.</t>
+          <t>El discípulo ya iguala al maestro: con la Supercopa conquistada ayer, Guardiola alcanza el número de trofeos (11) alzados durante los ocho años de Cruyff en el banquillo.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>MD 18/08/2011</t>
+          <t>El País 18/08/2011</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Sala mixta</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4563,14 +4551,14 @@
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>2011-08-19</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4580,22 +4568,22 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (titular)</t>
+          <t>Marca (titular)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Los buenos siempre ganan. Un buen Madrid que ha acabado recurriendo a la violencia como única arma para frenar a los cracks barcelonistas.</t>
+          <t>Que sea la última vez.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>MD 18/08/2011</t>
+          <t>Marca 19/08/2011</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4613,17 +4601,21 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Snap 19/08/2011 08:22 UTC.</t>
+        </is>
+      </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/20110819082200/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>2011-08-19</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4633,27 +4625,27 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho (a El País)</t>
+          <t>Marca (editorial)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>El fútbol es para hombres.</t>
+          <t>Esto se tiene que acabar. Real Madrid y Barcelona no pueden salir a tangana por partido.</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>El País 18/08/2011</t>
+          <t>Marca 19/08/2011</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Crónica de Nadia Tronchoni</t>
+          <t>Editorial</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4666,21 +4658,17 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>Frase tras la agresión a Tito Vilanova.</t>
-        </is>
-      </c>
+      <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>2011-08-19</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4690,27 +4678,27 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>El País (José Sámano)</t>
+          <t>Real Madrid (vestuario, anónimo)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Messi sí que es único. El Madrid no puede con el argentino, el mayor castigo de su historia y artífice del triunfo del Barcelona en una Supercopa intensa.</t>
+          <t>Jugando así lo normal es que les ganemos.</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>El País 18/08/2011</t>
+          <t>Marca 19/08/2011</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Sergio Fernández</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4723,17 +4711,21 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Valoración interna del vestuario blanco a pesar de la derrota.</t>
+        </is>
+      </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2011-08-18</t>
+          <t>2011-08-19</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4743,27 +4735,27 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>El País (datos)</t>
+          <t>Rafael Nadal (desde Cincinnati)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>El discípulo ya iguala al maestro: con la Supercopa conquistada ayer, Guardiola alcanza el número de trofeos (11) alzados durante los ocho años de Cruyff en el banquillo.</t>
+          <t>Hay cosas más importantes que ganar o perder.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>El País 18/08/2011</t>
+          <t>Marca 19/08/2011</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Sección Deportes</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4776,10 +4768,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Nadal sobre los incidentes de la Supercopa.</t>
+        </is>
+      </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
@@ -4796,12 +4792,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Marca (titular)</t>
+          <t>Marca (blog 'Tirando a dar')</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Que sea la última vez.</t>
+          <t>Mourinho eclipsa al Papa. ¿Qué pretende el entrenador y su propio club? ¿Tratar de que nadie se de cuenta de que el archirrival les venció?</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4816,7 +4812,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Blog 'Tirando a dar'</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4831,49 +4827,49 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Snap 19/08/2011 08:22 UTC.</t>
+          <t>El día de la JMJ, el dedo en el ojo eclipsa al Papa en los medios.</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20110819082200/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2011-08-19</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Marca (editorial)</t>
+          <t>AS (titular hoy)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Esto se tiene que acabar. Real Madrid y Barcelona no pueden salir a tangana por partido.</t>
+          <t>Goleada al Florentinato.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/08/2011</t>
+          <t>AS 22/11/2015</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Editorial</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4886,47 +4882,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Madrid 0 - 4 Barça.</t>
+        </is>
+      </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2011-08-19</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Real Madrid (vestuario, anónimo)</t>
+          <t>AS (titular crónica)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Jugando así lo normal es que les ganemos.</t>
+          <t>Uno a uno del Madrid: desastre general y naufragio de la BBC.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/08/2011</t>
+          <t>AS 22/11/2015</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Sergio Fernández</t>
+          <t>Sección Madrid</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4941,49 +4941,49 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Valoración interna del vestuario blanco a pesar de la derrota.</t>
+          <t>Crítica al tridente Bale-Benzema-Cristiano.</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2011-08-19</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Rafael Nadal (desde Cincinnati)</t>
+          <t>Mundo Deportivo (titular)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Hay cosas más importantes que ganar o perder.</t>
+          <t>Sinfonía espectacular del Barça y concierto de pitos para el Real Madrid. El equipo de Luis Enrique degradó al equipo blanco, muy vulgar en su juego, hasta el ridículo en el Bernabéu y provocó gritos de 'Florentino, dimisión'.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/08/2011</t>
+          <t>MD 22/11/2015</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4998,49 +4998,49 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Nadal sobre los incidentes de la Supercopa.</t>
+          <t>Snap MD 22/11/2015 14:31 UTC.</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20151122143100/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2011-08-19</t>
+          <t>2015-11-22</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Marca (blog 'Tirando a dar')</t>
+          <t>Mundo Deportivo (revista de prensa)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Mourinho eclipsa al Papa. ¿Qué pretende el entrenador y su propio club? ¿Tratar de que nadie se de cuenta de que el archirrival les venció?</t>
+          <t>La prensa mundial se rinde al Barça. La prensa internacional habla de 'Real Barça' y define como 'exhibición' el partido realizado por los de Luis Enrique.</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/08/2011</t>
+          <t>MD 22/11/2015</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Blog 'Tirando a dar'</t>
+          <t>Revista de prensa</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -5053,14 +5053,10 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>El día de la JMJ, el dedo en el ojo eclipsa al Papa en los medios.</t>
-        </is>
-      </c>
+      <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -5077,27 +5073,27 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>AS (titular hoy)</t>
+          <t>Cristiano Ronaldo (vía La Gazzetta dello Sport)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Goleada al Florentinato.</t>
+          <t>O Benítez o yo.</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>La Gazzetta / Mundo Deportivo</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>AS 22/11/2015</t>
+          <t>MD 22/11/2015</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Top Secret</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -5112,12 +5108,12 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Madrid 0 - 4 Barça.</t>
+          <t>Cristiano habría pedido la destitución de Benítez tras el 0-4.</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -5134,27 +5130,27 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>AS (titular crónica)</t>
+          <t>Rivaldo</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Uno a uno del Madrid: desastre general y naufragio de la BBC.</t>
+          <t>El ex azulgrana le aconseja al Madrid que Zidane ocupe el lugar de Rafa Benítez en el banquillo blanco.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>AS 22/11/2015</t>
+          <t>MD 22/11/2015</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Sección Madrid</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -5169,12 +5165,12 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Crítica al tridente Bale-Benzema-Cristiano.</t>
+          <t>Rivaldo predice la sustitución de Benítez por Zidane.</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -5191,12 +5187,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (titular)</t>
+          <t>Marcelo (anécdota)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Sinfonía espectacular del Barça y concierto de pitos para el Real Madrid. El equipo de Luis Enrique degradó al equipo blanco, muy vulgar en su juego, hasta el ridículo en el Bernabéu y provocó gritos de 'Florentino, dimisión'.</t>
+          <t>Marcelo pierde los papeles y llama 'tonto' a un periodista.</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -5211,7 +5207,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -5224,51 +5220,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>Snap MD 22/11/2015 14:31 UTC.</t>
-        </is>
-      </c>
+      <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20151122143100/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2015-11-19</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Previa 0-4 Bernabéu 2015</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (revista de prensa)</t>
+          <t>Andrés Iniesta (RP previa)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>La prensa mundial se rinde al Barça. La prensa internacional habla de 'Real Barça' y define como 'exhibición' el partido realizado por los de Luis Enrique.</t>
+          <t>El Clásico me pone como una moto. Cada uno le pone al partido el calificativo que quiere, ojalá me siga poniendo como una moto.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>MD 22/11/2015</t>
+          <t>Marca 19/11/2015</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Revista de prensa</t>
+          <t>Por S. Font, Barcelona</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5284,44 +5276,44 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2015-11-19</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Previa 0-4 Bernabéu 2015</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo (vía La Gazzetta dello Sport)</t>
+          <t>Manolo Sanchís</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>O Benítez o yo.</t>
+          <t>La continuidad de Benítez no pasa por este partido.</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>La Gazzetta / Mundo Deportivo</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>MD 22/11/2015</t>
+          <t>Marca 19/11/2015</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Top Secret</t>
+          <t>Videoblog</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5336,19 +5328,19 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Cristiano habría pedido la destitución de Benítez tras el 0-4.</t>
+          <t>Aunque cree que perder sería un drama.</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2015-11-23</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5358,27 +5350,27 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Rivaldo</t>
+          <t>AS (titular hoy)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>El ex azulgrana le aconseja al Madrid que Zidane ocupe el lugar de Rafa Benítez en el banquillo blanco.</t>
+          <t>Florentino segundo frente.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>MD 22/11/2015</t>
+          <t>AS 23/11/2015</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5393,19 +5385,19 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Rivaldo predice la sustitución de Benítez por Zidane.</t>
+          <t>Snap AS 23/11/2015 14:42 UTC.</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/20151123144200/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2015-11-22</t>
+          <t>2015-11-23</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5415,27 +5407,27 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Marcelo (anécdota)</t>
+          <t>Dani Alves (a AS)</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Marcelo pierde los papeles y llama 'tonto' a un periodista.</t>
+          <t>Al Real Madrid que le vaya mal, no, lo siguiente.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>MD 22/11/2015</t>
+          <t>AS 23/11/2015</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Sección Barcelona</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5448,47 +5440,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Por Moisés Llorens.</t>
+        </is>
+      </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2015-11-19</t>
+          <t>2015-11-23</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Previa 0-4 Bernabéu 2015</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Andrés Iniesta (RP previa)</t>
+          <t>Dani Alves (a Mundo Deportivo)</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>El Clásico me pone como una moto. Cada uno le pone al partido el calificativo que quiere, ojalá me siga poniendo como una moto.</t>
+          <t>El problema de Cristiano es querer ser demasiado protagonista. El secreto del Barça para ganar al Madrid y no debilitarse es no tener ego.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/11/2015</t>
+          <t>MD 23/11/2015</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Por S. Font, Barcelona</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5504,44 +5500,44 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2015-11-19</t>
+          <t>2015-11-23</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Previa 0-4 Bernabéu 2015</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Manolo Sanchís</t>
+          <t>Florentino Pérez (RP de defensa de Benítez)</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>La continuidad de Benítez no pasa por este partido.</t>
+          <t>Yo no sé lo que pasará en seis meses. Hay una campaña contra mí. El equipo lleva desde enero viviendo un desgaste.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Marca 19/11/2015</t>
+          <t>MD 23/11/2015</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Videoblog</t>
+          <t>RP Florentino</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5556,12 +5552,12 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Aunque cree que perder sería un drama.</t>
+          <t>Florentino ratifica a Rafa Benítez tras el 0-4 y culpa a Ancelotti.</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -5578,27 +5574,27 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>AS (titular hoy)</t>
+          <t>Ramón Calderón (sobre Florentino)</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Florentino segundo frente.</t>
+          <t>¡Qué poca vergüenza! Hablar de campaña contra él, quien ha contratado a dos periodistas condenados por delitos de calumnias contra mí.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>AS 23/11/2015</t>
+          <t>MD 23/11/2015</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Twitter</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5613,12 +5609,12 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Snap AS 23/11/2015 14:42 UTC.</t>
+          <t>Ex-presidente del Madrid sobre Florentino.</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20151123144200/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
@@ -5635,27 +5631,27 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Dani Alves (a AS)</t>
+          <t>Jugador del Madrid (anónimo, top secret)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Al Real Madrid que le vaya mal, no, lo siguiente.</t>
+          <t>Cristiano Ronaldo quiere irse. No es bueno el ambiente en el vestuario.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>AS 23/11/2015</t>
+          <t>MD 23/11/2015</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Sección Barcelona</t>
+          <t>Top Secret</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5670,49 +5666,49 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Por Moisés Llorens.</t>
+          <t>Mensaje WhatsApp de un jugador del Madrid a un compañero de Brasil del Barça tras el 0-4.</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2015-11-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Dani Alves (a Mundo Deportivo)</t>
+          <t>AS (titular hoy)</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>El problema de Cristiano es querer ser demasiado protagonista. El secreto del Barça para ganar al Madrid y no debilitarse es no tener ego.</t>
+          <t>Rompe récords de Lamine. ¿Debe sancionar el Madrid a Vinicius? ¿Tiene que renovar o salir?</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>MD 23/11/2015</t>
+          <t>AS 27/10/2025</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5725,47 +5721,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Snap AS 27/10/2025 16:55 UTC.</t>
+        </is>
+      </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/20251027165500/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2015-11-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Florentino Pérez (RP de defensa de Benítez)</t>
+          <t>Vinicius Junior (a Lamine Yamal)</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Yo no sé lo que pasará en seis meses. Hay una campaña contra mí. El equipo lleva desde enero viviendo un desgaste.</t>
+          <t>Llorón, no me toques.</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>MD 23/11/2015</t>
+          <t>AS 27/10/2025</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>RP Florentino</t>
+          <t>Vídeo del partido</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5780,49 +5780,49 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Florentino ratifica a Rafa Benítez tras el 0-4 y culpa a Ancelotti.</t>
+          <t>Cita literal de Vini hacia Yamal en la tangana.</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2015-11-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Ramón Calderón (sobre Florentino)</t>
+          <t>AS (titular sobre Vinicius)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>¡Qué poca vergüenza! Hablar de campaña contra él, quien ha contratado a dos periodistas condenados por delitos de calumnias contra mí.</t>
+          <t>Vinicius valora la opción de salir si todo sigue igual. Vinicius siente que ha cumplido con su parte, pero no se está respetando su estatus. La opción de marcharse se valora seriamente.</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>MD 23/11/2015</t>
+          <t>AS 27/10/2025</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>Marco Ruiz</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5835,51 +5835,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>Ex-presidente del Madrid sobre Florentino.</t>
-        </is>
-      </c>
+      <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2015-11-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Bronca Yamal-Carvajal-Vinicius</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Jugador del Madrid (anónimo, top secret)</t>
+          <t>AS (debate de usuarios)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo quiere irse. No es bueno el ambiente en el vestuario.</t>
+          <t>El 'vámonos fuera' de Lamine a Carvajal es un gesto de soberbia.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>MD 23/11/2015</t>
+          <t>AS 27/10/2025</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Top Secret</t>
+          <t>El debate de los usuarios</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5894,19 +5890,19 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Mensaje WhatsApp de un jugador del Madrid a un compañero de Brasil del Barça tras el 0-4.</t>
+          <t>Frase del día tras la bronca.</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5916,12 +5912,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>AS (titular hoy)</t>
+          <t>AS (titular crónica)</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Rompe récords de Lamine. ¿Debe sancionar el Madrid a Vinicius? ¿Tiene que renovar o salir?</t>
+          <t>Marcó Bellingham y Vinicius no pudo contenerse: el gesto del que pocos se percataron.</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5931,12 +5927,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>AS 27/10/2025</t>
+          <t>AS 28/10/2025</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>AStv</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5949,21 +5945,17 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>Snap AS 27/10/2025 16:55 UTC.</t>
-        </is>
-      </c>
+      <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20251027165500/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5973,12 +5965,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Vinicius Junior (a Lamine Yamal)</t>
+          <t>AS (Sergio López)</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Llorón, no me toques.</t>
+          <t>El 'Caso Vinicius' se expande.</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5988,12 +5980,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>AS 27/10/2025</t>
+          <t>AS 28/10/2025</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Vídeo del partido</t>
+          <t>Sección Madrid</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -6006,11 +5998,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>Cita literal de Vini hacia Yamal en la tangana.</t>
-        </is>
-      </c>
+      <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
@@ -6030,27 +6018,27 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>AS (titular sobre Vinicius)</t>
+          <t>El País (Lorenzo Calonge)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Vinicius valora la opción de salir si todo sigue igual. Vinicius siente que ha cumplido con su parte, pero no se está respetando su estatus. La opción de marcharse se valora seriamente.</t>
+          <t>La victoria en el clásico refuerza a Xabi Alonso, que afronta el mayor desafío de Vinicius a su autoridad. El necesitado triunfo blanco impulsa el proyecto del técnico, que debe gestionar el desaire más grave del brasileño dentro de un vestuario con más de un morro torcido.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>AS 27/10/2025</t>
+          <t>El País 27/10/2025</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Marco Ruiz</t>
+          <t>Crónica El Clásico</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -6066,14 +6054,14 @@
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -6083,27 +6071,27 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>AS (debate de usuarios)</t>
+          <t>Xabi Alonso (a El País)</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>El 'vámonos fuera' de Lamine a Carvajal es un gesto de soberbia.</t>
+          <t>El equipo necesitaba la sensación de ganar un partido grande.</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>AS 27/10/2025</t>
+          <t>El País 26/10/2025</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>El debate de los usuarios</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6118,19 +6106,19 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Frase del día tras la bronca.</t>
+          <t>Por Lorenzo Calonge. Xabi anuncia que hablará por supuesto con Vinicius.</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6140,27 +6128,27 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>AS (titular crónica)</t>
+          <t>El País (David Álvarez)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Marcó Bellingham y Vinicius no pudo contenerse: el gesto del que pocos se percataron.</t>
+          <t>El Madrid reconquista el clásico. Tras cuatro derrotas seguidas, el equipo de Xabi Alonso arrolla a un Barça mermado por las bajas y con Lamine Yamal desaparecido con un partido de gran intensidad en el que volvió a brillar Bellingham y se distancia cinco puntos en cabeza.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>AS 28/10/2025</t>
+          <t>El País 26/10/2025</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>AStv</t>
+          <t>Crónica</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -6176,14 +6164,14 @@
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6193,27 +6181,27 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>AS (Sergio López)</t>
+          <t>Markus Sorg (2º entrenador del Barça)</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>El 'Caso Vinicius' se expande.</t>
+          <t>Lamine está aprendiendo, le ayudaremos.</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>El País (web)</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>AS 28/10/2025</t>
+          <t>El País 26/10/2025</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Sección Madrid</t>
+          <t>RP post-partido</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -6226,10 +6214,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Yamal estuvo en el foco, abucheado por el Bernabéu y enfrentado a Carvajal y Vinicius.</t>
+        </is>
+      </c>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -6246,12 +6238,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>El País (Lorenzo Calonge)</t>
+          <t>El País (Manuel Jabois opinión)</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>La victoria en el clásico refuerza a Xabi Alonso, que afronta el mayor desafío de Vinicius a su autoridad. El necesitado triunfo blanco impulsa el proyecto del técnico, que debe gestionar el desaire más grave del brasileño dentro de un vestuario con más de un morro torcido.</t>
+          <t>Este infernal y precioso olor al viejo Clásico de siempre.</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -6266,7 +6258,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Crónica El Clásico</t>
+          <t>Opinión</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -6289,7 +6281,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6299,12 +6291,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Xabi Alonso (a El País)</t>
+          <t>El País (Daniel Verdú, París)</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>El equipo necesitaba la sensación de ganar un partido grande.</t>
+          <t>Lamine, algo tan grave.</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -6314,12 +6306,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>El País 26/10/2025</t>
+          <t>El País 28/10/2025</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Opinión desde París</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -6332,11 +6324,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>Por Lorenzo Calonge. Xabi anuncia que hablará por supuesto con Vinicius.</t>
-        </is>
-      </c>
+      <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
@@ -6346,7 +6334,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6356,12 +6344,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>El País (David Álvarez)</t>
+          <t>El País (Juan I. Irigoyen)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>El Madrid reconquista el clásico. Tras cuatro derrotas seguidas, el equipo de Xabi Alonso arrolla a un Barça mermado por las bajas y con Lamine Yamal desaparecido con un partido de gran intensidad en el que volvió a brillar Bellingham y se distancia cinco puntos en cabeza.</t>
+          <t>Los dilemas de Flick en su segundo año en el Barcelona. La política del club y la gestión de Lamine preocupan a un técnico sin respuestas tácticas.</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6371,12 +6359,12 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>El País 26/10/2025</t>
+          <t>El País 28/10/2025</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Crónica</t>
+          <t>Sección Barcelona</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -6399,7 +6387,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -6409,27 +6397,27 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Markus Sorg (2º entrenador del Barça)</t>
+          <t>Marca (titular hoy)</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Lamine está aprendiendo, le ayudaremos.</t>
+          <t>El Real Madrid se escapa.</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>El País 26/10/2025</t>
+          <t>Marca 27/10/2025</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>RP post-partido</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -6444,19 +6432,19 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>Yamal estuvo en el foco, abucheado por el Bernabéu y enfrentado a Carvajal y Vinicius.</t>
+          <t>Snap Marca 27/10/2025 17:12 UTC.</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/20251027171200/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6466,27 +6454,27 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>El País (Manuel Jabois opinión)</t>
+          <t>Marca (titular hoy)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Este infernal y precioso olor al viejo Clásico de siempre.</t>
+          <t>El Madrid quiere la fiesta en paz.</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>El País 27/10/2025</t>
+          <t>Marca 28/10/2025</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>Opinión</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -6499,47 +6487,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Snap Marca 28/10/2025 18:52 UTC.</t>
+        </is>
+      </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/20251028185200/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2002-11-24</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Cochinillo a Figo</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>El País (Daniel Verdú, París)</t>
+          <t>AS (encuesta portada)</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Lamine, algo tan grave.</t>
+          <t>¿Crees que debe clausurarse el Camp Nou?</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>El País 28/10/2025</t>
+          <t>AS 24/11/2002</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Opinión desde París</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6552,47 +6544,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Snap AS 24/11/2002 22:26 UTC.</t>
+        </is>
+      </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/20021124222600/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2002-11-24</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Cochinillo a Figo</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>El País (Juan I. Irigoyen)</t>
+          <t>Johan Cruyff (sobre Joan Gaspart)</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Los dilemas de Flick en su segundo año en el Barcelona. La política del club y la gestión de Lamine preocupan a un técnico sin respuestas tácticas.</t>
+          <t>Al presidente le queda cada vez menos.</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>El País (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>El País 28/10/2025</t>
+          <t>AS 24/11/2002</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>Sección Barcelona</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6605,47 +6601,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Cruyff sobre la situación de Gaspart como presidente del Barça.</t>
+        </is>
+      </c>
       <c r="K110" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2002-11-24</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Cochinillo a Figo</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Marca (titular hoy)</t>
+          <t>Luis Figo</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>El Real Madrid se escapa.</t>
+          <t>(Figo pide perdón por decir 'mongolo'.)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Marca 27/10/2025</t>
+          <t>AS 24/11/2002</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6660,49 +6660,49 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Snap Marca 27/10/2025 17:12 UTC.</t>
+          <t>Tras los lanzamientos de objetos en el Camp Nou.</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20251027171200/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2002-11-24</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal-Vinicius</t>
+          <t>Cochinillo a Figo</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Marca (titular hoy)</t>
+          <t>Medina Cantalejo (árbitro)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>El Madrid quiere la fiesta en paz.</t>
+          <t>(Medina pensó en la suspensión del partido.)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Marca 28/10/2025</t>
+          <t>AS 24/11/2002</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Declaraciones</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6717,49 +6717,49 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Snap Marca 28/10/2025 18:52 UTC.</t>
+          <t>El árbitro suspendió el encuentro 15 minutos por los lanzamientos a Figo.</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20251028185200/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>2002-11-24</t>
+          <t>2002-11-22</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Cochinillo a Figo</t>
+          <t>Previa Cochinillo Figo</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>AS (encuesta portada)</t>
+          <t>Pilar Rahola (escritora, a Sport)</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>¿Crees que debe clausurarse el Camp Nou?</t>
+          <t>Ganar al Real Madrid se merece un orgasmo.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Sport (web)</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>AS 24/11/2002</t>
+          <t>Sport 22/11/2002</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Entrevista</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6774,44 +6774,44 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>Snap AS 24/11/2002 22:26 UTC.</t>
+          <t>Periodista catalana en programa de entrevistas.</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20021124222600/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2002-11-24</t>
+          <t>2002-11-22</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Cochinillo a Figo</t>
+          <t>Previa Cochinillo Figo</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruyff (sobre Joan Gaspart)</t>
+          <t>Patrick Kluivert (a Sport)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Al presidente le queda cada vez menos.</t>
+          <t>Me toca marcar en un Barça-Madrid. La última vez que marqué en un partido con el FC Barcelona, hizo un 'hat trick' al Alavés.</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Sport (web)</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>AS 24/11/2002</t>
+          <t>Sport 22/11/2002</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -6829,51 +6829,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>Cruyff sobre la situación de Gaspart como presidente del Barça.</t>
-        </is>
-      </c>
+      <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2002-11-24</t>
+          <t>2002-11-22</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Cochinillo a Figo</t>
+          <t>Previa Cochinillo Figo</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Luis Figo</t>
+          <t>Luis Enrique (lesionado, mensaje desde grada)</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>(Figo pide perdón por decir 'mongolo'.)</t>
+          <t>Cuando pite el árbitro, seré un socio más dando apoyo al equipo desde la grada.</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Sport (web)</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>AS 24/11/2002</t>
+          <t>Sport 22/11/2002</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Mensaje del capitán</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6888,49 +6884,49 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>Tras los lanzamientos de objetos en el Camp Nou.</t>
+          <t>Lucho Enrique no jugó el partido, ya estaba como capitán retirado en grada.</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2002-11-24</t>
+          <t>2002-11-22</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Cochinillo a Figo</t>
+          <t>Previa Cochinillo Figo</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Medina Cantalejo (árbitro)</t>
+          <t>Sport (titular)</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>(Medina pensó en la suspensión del partido.)</t>
+          <t>Ronaldo mete cizaña en el vestuario del Madrid.</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Sport (web)</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>AS 24/11/2002</t>
+          <t>Sport 22/11/2002</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6945,12 +6941,12 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>El árbitro suspendió el encuentro 15 minutos por los lanzamientos a Figo.</t>
+          <t>Ronaldo Nazário en su último Clásico antes de la baja.</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
     </row>
@@ -6967,12 +6963,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Pilar Rahola (escritora, a Sport)</t>
+          <t>Vizcaíno Casas (escritor, a Sport)</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Ganar al Real Madrid se merece un orgasmo.</t>
+          <t>Los jugadores de antes sí sentían los colores.</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -7000,11 +6996,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>Periodista catalana en programa de entrevistas.</t>
-        </is>
-      </c>
+      <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
@@ -7014,32 +7006,32 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2002-11-22</t>
+          <t>2005-11-20</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Previa Cochinillo Figo</t>
+          <t>Ronaldinho ovación Bernabéu</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Patrick Kluivert (a Sport)</t>
+          <t>Joan Gaspart (a AS)</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Me toca marcar en un Barça-Madrid. La última vez que marqué en un partido con el FC Barcelona, hizo un 'hat trick' al Alavés.</t>
+          <t>Lo de Figo fue un robo y lo de Eto'o no.</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>AS (web)</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Sport 22/11/2002</t>
+          <t>AS 20/11/2005</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -7057,32 +7049,36 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Ex-presidente del Barça comparando los fichajes Figo→Madrid (2000) y Eto'o→Barça.</t>
+        </is>
+      </c>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>2002-11-22</t>
+          <t>2005-11-23</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Previa Cochinillo Figo</t>
+          <t>Ronaldinho ovación Bernabéu</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Luis Enrique (lesionado, mensaje desde grada)</t>
+          <t>Sport (titular)</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Cuando pite el árbitro, seré un socio más dando apoyo al equipo desde la grada.</t>
+          <t>Ronaldinho, a un gol de sus 'bodas de oro' azulgranas. El 'crack' brasileño del Barça Ronaldinho, que maravilla a propios y extraños en cada partido que disputa, está a un solo tanto de alcanzar los 50 goles con la camiseta azulgrana.</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -7092,12 +7088,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Sport 22/11/2002</t>
+          <t>Sport 23/11/2005</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Mensaje del capitán</t>
+          <t>Portada digital</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -7112,34 +7108,34 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>Lucho Enrique no jugó el partido, ya estaba como capitán retirado en grada.</t>
+          <t>Snap Sport 23/11/2005 01:19 UTC.</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/20051123011900/https://www.sport.es/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2002-11-22</t>
+          <t>2005-11-23</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Previa Cochinillo Figo</t>
+          <t>Ronaldinho ovación Bernabéu</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Sport (titular)</t>
+          <t>Ll. Mascaró (Sport, La ventana indiscreta)</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Ronaldo mete cizaña en el vestuario del Madrid.</t>
+          <t>Gamper creó al Barça... y Ronaldinho lo lleva a la gloria.</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -7149,12 +7145,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Sport 22/11/2002</t>
+          <t>Sport 23/11/2005</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>Columna de opinión</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -7167,11 +7163,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>Ronaldo Nazário en su último Clásico antes de la baja.</t>
-        </is>
-      </c>
+      <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
@@ -7181,22 +7173,22 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>2002-11-22</t>
+          <t>2005-11-23</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Previa Cochinillo Figo</t>
+          <t>Ronaldinho ovación Bernabéu</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Vizcaíno Casas (escritor, a Sport)</t>
+          <t>J. Prats (Sport, Línea directa)</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Los jugadores de antes sí sentían los colores.</t>
+          <t>Ronaldinho, el crack generoso.</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -7206,12 +7198,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Sport 22/11/2002</t>
+          <t>Sport 23/11/2005</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Entrevista</t>
+          <t>Columna de opinión</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -7234,7 +7226,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2005-11-20</t>
+          <t>2005-11-23</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -7244,27 +7236,27 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Joan Gaspart (a AS)</t>
+          <t>J.M. Casanovas (Sport, Mi verdad)</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Lo de Figo fue un robo y lo de Eto'o no.</t>
+          <t>El Barça, un equipo que sólo sabe ganar.</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>AS (web)</t>
+          <t>Sport (web)</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>AS 20/11/2005</t>
+          <t>Sport 23/11/2005</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Declaraciones</t>
+          <t>Editorial</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -7277,21 +7269,17 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>Ex-presidente del Barça comparando los fichajes Figo→Madrid (2000) y Eto'o→Barça.</t>
-        </is>
-      </c>
+      <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.as.com/</t>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2005-11-23</t>
+          <t>2005-11-21</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -7301,12 +7289,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Sport (titular)</t>
+          <t>Sport (encuesta del día)</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho, a un gol de sus 'bodas de oro' azulgranas. El 'crack' brasileño del Barça Ronaldinho, que maravilla a propios y extraños en cada partido que disputa, está a un solo tanto de alcanzar los 50 goles con la camiseta azulgrana.</t>
+          <t>¿Quién es mejor jugador? Pelé / Maradona / Ronaldinho.</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -7316,7 +7304,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Sport 23/11/2005</t>
+          <t>Sport 21/11/2005</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -7336,49 +7324,49 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>Snap Sport 23/11/2005 01:19 UTC.</t>
+          <t>Pone a Ronaldinho a la altura de Pelé y Maradona tras ovación Bernabéu.</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20051123011900/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2005-11-23</t>
+          <t>2011-04-25</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho ovación Bernabéu</t>
+          <t>Pre-Clásico Champions</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Ll. Mascaró (Sport, La ventana indiscreta)</t>
+          <t>Andrés Iniesta (RP previa)</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Gamper creó al Barça... y Ronaldinho lo lleva a la gloria.</t>
+          <t>Todos conocemos a Guardiola. Yo no creo que quisiera decir eso. El máster no busca excusas.</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>Marca (web)</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Sport 23/11/2005</t>
+          <t>Marca 25/04/2011</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Columna de opinión</t>
+          <t>RP previa</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -7391,47 +7379,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Defensa pública del Pep tras críticas de Mou.</t>
+        </is>
+      </c>
       <c r="K124" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>2005-11-23</t>
+          <t>2011-04-25</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho ovación Bernabéu</t>
+          <t>Pre-Clásico Champions</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>J. Prats (Sport, Línea directa)</t>
+          <t>Johan Cruyff (a El Periódico)</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho, el crack generoso.</t>
+          <t>Más que temer quién pitará o si el césped estará alto, preocúpate de tu equipo. El Madrid llega más fuerte.</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>El Periódico (vía Marca)</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Sport 23/11/2005</t>
+          <t>El Periódico 25/04/2011</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Columna de opinión</t>
+          <t>Columna</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7444,47 +7436,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>Recadito de Cruyff a Pep.</t>
+        </is>
+      </c>
       <c r="K125" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2005-11-23</t>
+          <t>2011-04-25</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho ovación Bernabéu</t>
+          <t>Pre-Clásico Champions</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>J.M. Casanovas (Sport, Mi verdad)</t>
+          <t>Víctor Valdés (RP previa)</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>El Barça, un equipo que sólo sabe ganar.</t>
+          <t>Dependerá del árbitro que podamos hacer nuestro juego. No hay que obsesionarse con estas cosas. Tenemos que ir a lo nuestro y hacer el partido que nos interesa.</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>Mundo Deportivo (web)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Sport 23/11/2005</t>
+          <t>MD 25/04/2011</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Editorial</t>
+          <t>RP previa</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -7497,223 +7493,227 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Snap MD 25/04/2011 08:55 UTC.</t>
+        </is>
+      </c>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/20110425085500/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>2005-11-21</t>
+          <t>1958-1960</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Ronaldinho ovación Bernabéu</t>
+          <t>Helenio Herrera (entrenador Barça)</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Sport (encuesta del día)</t>
+          <t>Helenio Herrera</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>¿Quién es mejor jugador? Pelé / Maradona / Ronaldinho.</t>
+          <t>Me preguntan por qué solo dirijo clubes grandes y es que los pequeños no pueden pagarme.</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Sport (web)</t>
+          <t>Mundo Deportivo</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Sport 21/11/2005</t>
+          <t>Mundo Deportivo entrevista años 1958-60</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Portada digital</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
-        </is>
-      </c>
-      <c r="I127" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Hemeroteca digital Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>Parcial (atribución repetida)</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>Pone a Ronaldinho a la altura de Pelé y Maradona tras ovación Bernabéu.</t>
+          <t>Pionero del entrenador mediático. Recogida en Panenka 'El primer técnico mediático' (2014).</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/1958/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2011-04-25</t>
+          <t>1958-1960</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Pre-Clásico Champions</t>
+          <t>Helenio Herrera (entrenador Barça)</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Andrés Iniesta (RP previa)</t>
+          <t>Helenio Herrera</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Todos conocemos a Guardiola. Yo no creo que quisiera decir eso. El máster no busca excusas.</t>
+          <t>Al fútbol se juega mejor con diez que con once.</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Marca (web)</t>
+          <t>La Vanguardia</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Marca 25/04/2011</t>
+          <t>La Vanguardia años 50-60</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>RP previa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Hemeroteca digital La Vanguardia</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>Parcial (atribución repetida)</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>Defensa pública del Pep tras críticas de Mou.</t>
+          <t>Aforismo característico de HH.</t>
         </is>
       </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/1958/https://www.lavanguardia.com/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>2011-04-25</t>
+          <t>1958-1960</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Pre-Clásico Champions</t>
+          <t>Helenio Herrera (entrenador Barça)</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruyff (a El Periódico)</t>
+          <t>Helenio Herrera</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Más que temer quién pitará o si el césped estará alto, preocúpate de tu equipo. El Madrid llega más fuerte.</t>
+          <t>He pasado por clubes como el Barcelona, el Sevilla y el Inter; he dirigido las selecciones de Francia y de España y nunca he conocido el fracaso.</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>El Periódico (vía Marca)</t>
+          <t>Mundo Deportivo</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>El Periódico 25/04/2011</t>
+          <t>Entrevista MD años 60-70</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>Columna</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
-        </is>
-      </c>
-      <c r="I129" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Hemeroteca digital Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>Recadito de Cruyff a Pep.</t>
+          <t>Frase repetida en biografía y prensa retrospectiva.</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/*/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/1958/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2011-04-25</t>
+          <t>2015-07-12</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Pre-Clásico Champions</t>
+          <t>Casillas se despide del Madrid</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Víctor Valdés (RP previa)</t>
+          <t>Iker Casillas</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Dependerá del árbitro que podamos hacer nuestro juego. No hay que obsesionarse con estas cosas. Tenemos que ir a lo nuestro y hacer el partido que nos interesa.</t>
+          <t>Después de 25 años defendiendo el escudo del mejor club del mundo, llega un día difícil... despedirme de esta institución que me lo ha dado todo.</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo (web)</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>MD 25/04/2011</t>
+          <t>Marca 13/07/2015</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>RP previa</t>
+          <t>Portada y páginas Deportes</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Wayback Machine (archive.org)</t>
+          <t>Hemeroteca digital Marca + RP en directo</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
@@ -7723,44 +7723,44 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Snap MD 25/04/2011 08:55 UTC.</t>
+          <t>Sin homenaje oficial. Casillas solo en sala de prensa tras 25 años. Recogida también por El País 13/07/2015 y AS.</t>
         </is>
       </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20110425085500/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/20150713120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>1988-07-15</t>
+          <t>2015-07-12</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Schuster ficha por el Madrid</t>
+          <t>Casillas se despide del Madrid</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Ramón Mendoza (presidente Real Madrid)</t>
+          <t>Iker Casillas</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Es un fichaje con intriga, que daría un susto pequeño o grande a su gran rival.</t>
+          <t>Son treinta segundos pero me llevará casi una hora. (El discurso duró 8 minutos entre lágrimas)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>ABC 15/07/1988</t>
+          <t>El País 13/07/2015</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -7770,158 +7770,154 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital ABC</t>
-        </is>
-      </c>
-      <c r="I131" s="5" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>Schuster ficha gratis del Barça por el Madrid en julio 1988. Recogida también en La Galerna 'Schuster: genio y conflicto' (2014).</t>
-        </is>
-      </c>
+          <t>Hemeroteca digital El País + RP</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
-          <t>https://www.abc.es/archivo/periodicos/abc-madrid-19880715.html</t>
+          <t>https://web.archive.org/web/20150713120000/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>1988-07-15</t>
+          <t>2015-07-12</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Schuster ficha por el Madrid</t>
+          <t>Casillas se despide del Madrid</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Bernd Schuster</t>
+          <t>Iker Casillas</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>He recuperado las ganas por el fútbol. Llego motivado y con ganas de hacer las cosas bien para ganar títulos.</t>
+          <t>Se terminó.</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Marca 15/07/1988</t>
+          <t>AS 13/07/2015</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>Presentación oficial</t>
+          <t>Portada</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital BNE (Marca 1988)</t>
-        </is>
-      </c>
-      <c r="I132" s="5" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+          <t>Hemeroteca digital AS + RP en directo</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Tras su fichaje. En el primer Clásico al Camp Nou (1988) salió escoltado por la policía.</t>
+          <t>Cierre de la rueda de prensa de despedida.</t>
         </is>
       </c>
       <c r="K132" s="4" t="inlineStr">
         <is>
-          <t>https://hemerotecadigital.bne.es/hd/es/results?titulo=marca&amp;fechaFin=1988-07-15&amp;fechaInicio=1988-07-15</t>
+          <t>https://web.archive.org/web/20150713120000/https://as.com/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>1958-1960</t>
+          <t>2011-08</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Helenio Herrera (entrenador Barça)</t>
+          <t>Casillas y Xavi Premio Asturias</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Helenio Herrera</t>
+          <t>Xavi Hernández</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Me preguntan por qué solo dirijo clubes grandes y es que los pequeños no pueden pagarme.</t>
+          <t>Fue por el bien del fútbol español. (Sobre la llamada de Casillas para frenar el conflicto)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo entrevista años 1958-60</t>
+          <t>Entrevista El País agosto 2011</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital Mundo Deportivo</t>
-        </is>
-      </c>
-      <c r="I133" s="5" t="inlineStr">
-        <is>
-          <t>Parcial (atribución repetida)</t>
+          <t>Hemeroteca digital El País</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>Pionero del entrenador mediático. Recogida en Panenka 'El primer técnico mediático' (2014).</t>
+          <t>Mou se enfureció con Casillas; le acusaría más tarde de ser 'el topo'.</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/1958/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/2011/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>1958-1960</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Helenio Herrera (entrenador Barça)</t>
+          <t>Zidane primer Clásico como entrenador</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Helenio Herrera</t>
+          <t>Zinedine Zidane</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Ganar sin bajar del autobús. (Antes de un partido en Sevilla)</t>
+          <t>El Barcelona es un equipo que siempre ha sido fuerte. Cada entrenador tiene cosas diferentes, pero el Barça siempre es el Barça. Es un equipo competitivo que sabe jugar muy buen fútbol y que te pone difíciles las cosas.</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7931,485 +7927,90 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Marca crónica años 50-60</t>
+          <t>Marca 1/04/2016</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sección Deportes RP previa</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital BNE</t>
-        </is>
-      </c>
-      <c r="I134" s="5" t="inlineStr">
-        <is>
-          <t>Parcial</t>
+          <t>Hemeroteca digital Marca + RP en directo</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Frase repetida en biografía 'Helenio Herrera' (Maxi Fink, T&amp;B Editores 2003).</t>
+          <t>Madrid 2-1 Barça. Cortó la racha de 39 partidos invicto del Barça.</t>
         </is>
       </c>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>https://hemerotecadigital.bne.es/</t>
+          <t>https://web.archive.org/web/2016/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>1958-1960</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Helenio Herrera (entrenador Barça)</t>
+          <t>Zidane filosofía de equipo</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Helenio Herrera</t>
+          <t>Zinedine Zidane</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Al fútbol se juega mejor con diez que con once.</t>
+          <t>Estábamos a disposición de los jugadores. Para mí, es lo que hace fuerte al equipo, estás ahí para el jugador.</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>La Vanguardia</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>La Vanguardia años 50-60</t>
+          <t>AS entrevista 2017</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital La Vanguardia</t>
-        </is>
-      </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>Parcial (atribución repetida)</t>
-        </is>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>Aforismo característico de HH.</t>
-        </is>
-      </c>
+          <t>Hemeroteca digital AS</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/1958/https://www.lavanguardia.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>1958-1960</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Helenio Herrera (entrenador Barça)</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Helenio Herrera</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>He pasado por clubes como el Barcelona, el Sevilla y el Inter; he dirigido las selecciones de Francia y de España y nunca he conocido el fracaso.</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>Mundo Deportivo</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista MD años 60-70</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>Hemeroteca digital Mundo Deportivo</t>
-        </is>
-      </c>
-      <c r="I136" s="5" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>Frase repetida en biografía y prensa retrospectiva.</t>
-        </is>
-      </c>
-      <c r="K136" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/1958/https://www.mundodeportivo.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>2015-07-12</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>Casillas se despide del Madrid</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Iker Casillas</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Después de 25 años defendiendo el escudo del mejor club del mundo, llega un día difícil... despedirme de esta institución que me lo ha dado todo.</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>Marca 13/07/2015</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>Portada y páginas Deportes</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>Hemeroteca digital Marca + RP en directo</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>Sin homenaje oficial. Casillas solo en sala de prensa tras 25 años. Recogida también por El País 13/07/2015 y AS.</t>
-        </is>
-      </c>
-      <c r="K137" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20150713120000/https://www.marca.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>2015-07-12</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Casillas se despide del Madrid</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Iker Casillas</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Son treinta segundos pero me llevará casi una hora. (El discurso duró 8 minutos entre lágrimas)</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>El País</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>El País 13/07/2015</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>Sección Deportes</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>Hemeroteca digital El País + RP</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="inlineStr"/>
-      <c r="K138" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20150713120000/https://www.elpais.com/deportes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>2015-07-12</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>Casillas se despide del Madrid</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Iker Casillas</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Se terminó.</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>AS</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>AS 13/07/2015</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Portada</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>Hemeroteca digital AS + RP en directo</t>
-        </is>
-      </c>
-      <c r="I139" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>Cierre de la rueda de prensa de despedida.</t>
-        </is>
-      </c>
-      <c r="K139" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/20150713120000/https://as.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>2011-08</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Casillas y Xavi Premio Asturias</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Xavi Hernández</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Fue por el bien del fútbol español. (Sobre la llamada de Casillas para frenar el conflicto)</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>El País</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista El País agosto 2011</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Sección Deportes</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>Hemeroteca digital El País</t>
-        </is>
-      </c>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>Mou se enfureció con Casillas; le acusaría más tarde de ser 'el topo'.</t>
-        </is>
-      </c>
-      <c r="K140" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/2011/https://www.elpais.com/deportes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>2016-04-01</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Zidane primer Clásico como entrenador</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Zinedine Zidane</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>El Barcelona es un equipo que siempre ha sido fuerte. Cada entrenador tiene cosas diferentes, pero el Barça siempre es el Barça. Es un equipo competitivo que sabe jugar muy buen fútbol y que te pone difíciles las cosas.</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>Marca 1/04/2016</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>Sección Deportes RP previa</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>Hemeroteca digital Marca + RP en directo</t>
-        </is>
-      </c>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>Madrid 2-1 Barça. Cortó la racha de 39 partidos invicto del Barça.</t>
-        </is>
-      </c>
-      <c r="K141" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/2016/https://www.marca.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Zidane filosofía de equipo</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Zinedine Zidane</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Estábamos a disposición de los jugadores. Para mí, es lo que hace fuerte al equipo, estás ahí para el jugador.</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>AS</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>AS entrevista 2017</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>Sección Deportes</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>Hemeroteca digital AS</t>
-        </is>
-      </c>
-      <c r="I142" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="inlineStr"/>
-      <c r="K142" s="4" t="inlineStr">
-        <is>
           <t>https://web.archive.org/web/2017/https://www.as.com/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K142"/>
+  <autoFilter ref="A1:K135"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -8465,9 +8066,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId60"/>
@@ -8544,13 +8145,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8562,7 +8156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8638,89 +8232,89 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1983-06-26</t>
+          <t>1953-07-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Maradona ovacionado Bernabéu</t>
+          <t>Di Stéfano ficha</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Diego Armando Maradona</t>
+          <t>Alfredo Di Stéfano</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Carrasco me la dio en mitad de campo, me llevé al portero por delante y esperé a Juan José, que ya venía, y le dejé pasar. Se rompió las pelotas contra el palo y yo la empujé. Después nos cruzamos y le pedí perdón. Me mandó a la mierda.</t>
+          <t>Yo he venido a España para jugar en el Barcelona.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Olé (entrevista)</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Olé, años después</t>
+          <t>Marca 24/07/1953</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Portada</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (verificada en ESPN, Futbol Gate, Kodro Magazine)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Final Copa de la Liga ida, Bernabéu 2-2.</t>
+          <t>Acabó fichando por el Madrid. URL: https://espndeportes.espn.com/noticias/nota/_/id/2127933/di-stefano-el-fichaje-que-no-fue</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/1983/https://www.ole.com.ar/</t>
+          <t>https://espndeportes.espn.com/noticias/nota/_/id/2127933/di-stefano-el-fichaje-que-no-fue</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1983-09-24</t>
+          <t>1960-1961</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Goikoetxea-Maradona</t>
+          <t>Era Bernabéu presidente</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Diego Maradona</t>
+          <t>Santiago Bernabéu (presidente Madrid)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Me partió el tobillo en nuestro campo, a 60 metros del arco de ellos. Nunca creí que iba a venirme a buscar con tanta mala leche. Cuando paro la pelota, siento un 'crack', como cuando se rompe una madera.</t>
+          <t>El colegiado Leafe fue el mejor jugador del Barça.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>TyC Sports / Olé</t>
+          <t>Futbol Gate (retrospectiva) + libros sobre Bernabéu</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Documental 'Maradona en Sinaloa' 2003 + entrevista TyC 1995</t>
+          <t>Tras eliminatoria Copa de Europa 1960-61</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -8730,54 +8324,54 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Documental + entrevista TV</t>
+          <t>Prensa retrospectiva + libros</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (verificada — Futbol Gate)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Fractura del maléolo peroneal. Citado en doc 'Maradona' (Asif Kapadia, 2019) y libro 'Yo soy el Diego' (Planeta, 2000).</t>
+          <t>Frase sarcástica tras la eliminatoria europea de la 1960-61. URL: https://www.futbolgate.com/investigaci%C3%B3n/el-mayor-atraco-del-siglo-xx</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2003/https://www.ole.com.ar/</t>
+          <t>https://www.futbolgate.com/investigaci%C3%B3n/el-mayor-atraco-del-siglo-xx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1990s-2000s</t>
+          <t>1965-1980s</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Goikoetxea-Maradona</t>
+          <t>Era Bernabéu presidente</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Andoni Goikoetxea</t>
+          <t>Francisco Gento</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Fue una acción más del partido, no merezco ninguna sanción. Viví lo peor y lo mejor del fútbol con solo cuatro días de diferencia, por eso las guardo (las botas).</t>
+          <t>Se quería que otro club ganara la Copa de Europa, no siempre el mismo.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Panenka</t>
+          <t>Atribución (biografías de Gento)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Reportaje retrospectivo 'Barro y gloria'</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8787,64 +8381,60 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Prensa retrospectiva</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Atribución</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Parcial — atribución repetida en biografías</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Sancionado con 18 partidos (rebajados a 7-10). Frase recogida en 'Andoni Goikoetxea: barro y gloria' Panenka. URL: https://www.panenka.org/pasaportes/andoni-goikoetxea-barro-y-gloria/</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.panenka.org/pasaportes/andoni-goikoetxea-barro-y-gloria/</t>
-        </is>
-      </c>
+          <t>Frase atribuida en libros sobre la Copa de Europa de los 60. Fuente primaria de hemeroteca no localizada con esta cita exacta.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2003-2004</t>
+          <t>1983-06-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Stoichkov</t>
+          <t>Maradona ovacionado Bernabéu</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Hristo Stoichkov</t>
+          <t>Diego Armando Maradona</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Siempre voy a odiar al Real Madrid. Es más fácil que se abra la tierra a que yo acepte trabajar en ese club. El Real Madrid me da ganas de vomitar.</t>
+          <t>Carrasco me la dio en mitad de campo, me llevé al portero por delante y esperé a Juan José, que ya venía, y le dejé pasar. Se rompió las pelotas contra el palo y yo la empujé. Después nos cruzamos y le pedí perdón. Me mandó a la mierda.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Olé (entrevista)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Sport entrevista febrero 2003</t>
+          <t>Olé, años después</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Página deportes</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Prensa secundaria</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -8854,44 +8444,44 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Recogido también en Milenio (México).</t>
+          <t>Final Copa de la Liga ida, Bernabéu 2-2.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2003/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/1983/https://www.ole.com.ar/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1983-09-24</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Stoichkov</t>
+          <t>Goikoetxea-Maradona</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hristo Stoichkov</t>
+          <t>Diego Maradona</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>El Madrid me da asco, nunca me veréis con una camiseta blanca.</t>
+          <t>Me partió el tobillo en nuestro campo, a 60 metros del arco de ellos. Nunca creí que iba a venirme a buscar con tanta mala leche. Cuando paro la pelota, siento un 'crack', como cuando se rompe una madera.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo</t>
+          <t>TyC Sports / Olé</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo entrevista enero 1996</t>
+          <t>Documental 'Maradona en Sinaloa' 2003 + entrevista TyC 1995</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8901,64 +8491,64 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>Parcial (atribución repetida)</t>
+          <t>Documental + entrevista TV</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Frase de Stoichkov en su segunda etapa Barça (1996-1998).</t>
+          <t>Fractura del maléolo peroneal. Citado en doc 'Maradona' (Asif Kapadia, 2019) y libro 'Yo soy el Diego' (Planeta, 2000).</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/1996/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/2003/https://www.ole.com.ar/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2011-04-26</t>
+          <t>1990s-2000s</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>RP del 'puto jefe'</t>
+          <t>Goikoetxea-Maradona</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Pep Guardiola</t>
+          <t>Andoni Goikoetxea</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Como Mou me trata de Pep, yo le voy a tratar de José. No le conozco personalmente, pero al gerente que sí le conoce, mañana a las 8.45 nos enfrentamos en el campo. Fuera del campo, él ya ha ganado todo el año. Que se lleve la Champions personal fuera del campo, se la regalo y nos vamos a casa. En esta sala (de prensa), él es el puto jefe, el puto amo. Yo no quiero competir con él aquí ni un instante.</t>
+          <t>Fue una acción más del partido, no merezco ninguna sanción. Viví lo peor y lo mejor del fútbol con solo cuatro días de diferencia, por eso las guardo (las botas).</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Libertad Digital, Goal, TUDN</t>
+          <t>Panenka</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26/04/2011</t>
+          <t>Reportaje retrospectivo 'Barro y gloria'</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Bernabéu (sala de prensa)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Prensa retrospectiva</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -8968,49 +8558,49 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Rueda de prensa previa Champions semifinal.</t>
+          <t>Sancionado con 18 partidos (rebajados a 7-10). Frase recogida en 'Andoni Goikoetxea: barro y gloria' Panenka. URL: https://www.panenka.org/pasaportes/andoni-goikoetxea-barro-y-gloria/</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20110426120000/https://www.goal.com/</t>
+          <t>https://www.panenka.org/pasaportes/andoni-goikoetxea-barro-y-gloria/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2011-04-27</t>
+          <t>2010-11-28</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>RP UNICEF Mou</t>
+          <t>Stoichkov</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho</t>
+          <t>Hristo Stoichkov</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>¿Por qué? ¿Por qué? Yo no entiendo por qué. No sé si es por la publicidad de UNICEF, no sé si son muy simpáticos. Stark, Ovrebo, De Bleeckere, Bussaca... no entiendo por qué.</t>
+          <t>Siempre voy a odiar al Real Madrid. Es más fácil que se abra la tierra a que yo acepte trabajar en ese club. El Real Madrid me da ganas de vomitar.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Libertad Digital</t>
+          <t>Goal + Telecinco + Milenio + La Tercera</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27/04/2011</t>
+          <t>Tras manita 5-0 Camp Nou 28/11/2010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Sala de prensa Bernabéu</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -9020,54 +8610,54 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (verificada en múltiples medios el 28/11/2010)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Tras roja a Pepe en 0-2 Champions.</t>
+          <t>Declaraciones de Stoichkov tras el 5-0 al Madrid. URL: https://www.goal.com/es/news/27/liga-de-espa%C3%B1a/2010/11/28/2235578/barcelona-stoichkov-y-unas-declaraciones-subidas-de-tono</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20110427120000/https://www.libertaddigital.com/</t>
+          <t>https://www.goal.com/es/news/27/liga-de-espa%C3%B1a/2010/11/28/2235578/barcelona-stoichkov-y-unas-declaraciones-subidas-de-tono</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2011-04-27</t>
+          <t>2010-11-28</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>RP UNICEF Mou</t>
+          <t>Stoichkov</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho</t>
+          <t>Hristo Stoichkov</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Guardiola ha ganado una Champions que a mí me daría vergüenza haber ganado.</t>
+          <t>El Madrid me da asco, nunca me veréis con una camiseta blanca.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Libertad Digital</t>
+          <t>Telecinco / La Tercera</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27/04/2011</t>
+          <t>28/11/2010</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Sala de prensa Bernabéu</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -9077,112 +8667,116 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Misma rueda de prensa post-manita. URL: https://www.telecinco.es/noticias/Stoichkov-Real-Madrid-da-asco_0_1101975169.html</t>
+        </is>
+      </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20110427120000/https://www.libertaddigital.com/</t>
+          <t>https://www.telecinco.es/noticias/Stoichkov-Real-Madrid-da-asco_0_1101975169.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2011-08-17</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito Vilanova</t>
+          <t>Cochinillo a Figo</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho (acción)</t>
+          <t>Luis Figo</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>(Mourinho mete el dedo en el ojo a Tito Vilanova, segundo de Pep, durante tangana al final del partido.)</t>
+          <t>No me siento ni Judas ni traidor.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Goal, El Nacional, vídeo viral</t>
+          <t>Infobae (retrospectiva) + Memorias del Fútbol</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17/08/2011</t>
+          <t>Antes del partido 23/11/2002 Camp Nou</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Camp Nou</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Vídeo + prensa</t>
+          <t>Prensa primaria + retrospectiva</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (verificada)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Sanción: 2 partidos. Imagen icónica con 'El Observador' (Francesc Satorra).</t>
+          <t>Lanzamientos: cabeza de cochinillo, botellas whisky, agua, móviles. Pancartas 'Judas'. 110 dB. URL: https://www.infobae.com/america/deportes/2019/12/18/el-ultimo-gran-escandalo-en-el-clasico-espanol-en-el-camp-nou-cuando-los-hinchas-del-barcelona-le-tiraron-a-figo-una-cabeza-de-cerdo/</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20110817120000/https://www.goal.com/</t>
+          <t>https://www.infobae.com/america/deportes/2019/12/18/el-ultimo-gran-escandalo-en-el-clasico-espanol-en-el-camp-nou-cuando-los-hinchas-del-barcelona-le-tiraron-a-figo-una-cabeza-de-cerdo/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2014-04-25</t>
+          <t>2011-04-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Dedo en el ojo a Tito Vilanova</t>
+          <t>RP del 'puto jefe'</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>José Mourinho</t>
+          <t>Pep Guardiola</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Fallé. (Tras la muerte de Vilanova en abril 2014)</t>
+          <t>Como Mou me trata de Pep, yo le voy a tratar de José. No le conozco personalmente, pero al gerente que sí le conoce, mañana a las 8.45 nos enfrentamos en el campo. Fuera del campo, él ya ha ganado todo el año. Que se lleve la Champions personal fuera del campo, se la regalo y nos vamos a casa. En esta sala (de prensa), él es el puto jefe, el puto amo. Yo no quiero competir con él aquí ni un instante.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>El Nacional</t>
+          <t>Libertad Digital, Goal, TUDN</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>El Nacional 25/04/2014</t>
+          <t>26/04/2011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Sección Deportes</t>
+          <t>Bernabéu (sala de prensa)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -9192,49 +8786,49 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>URL: https://www.elnacional.cat/es/deportes/arrepentimiento-mourinho-dedo-ojo-tito-vilanova-fcbarcelona-madrid_626021_102.html</t>
+          <t>Rueda de prensa previa Champions semifinal.</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.elnacional.cat/es/deportes/arrepentimiento-mourinho-dedo-ojo-tito-vilanova-fcbarcelona-madrid_626021_102.html</t>
+          <t>https://web.archive.org/web/20110426120000/https://www.goal.com/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2011-04-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Casillas-Mourinho topo</t>
+          <t>RP UNICEF Mou</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Iker Casillas</t>
+          <t>José Mourinho</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Asumí que yo era el topo.</t>
+          <t>¿Por qué? ¿Por qué? Yo no entiendo por qué. No sé si es por la publicidad de UNICEF, no sé si son muy simpáticos. Stark, Ovrebo, De Bleeckere, Bussaca... no entiendo por qué.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Infobae, El Español, Libertad Digital</t>
+          <t>Libertad Digital</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Documental 2020</t>
+          <t>27/04/2011</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sala de prensa Bernabéu</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -9249,49 +8843,49 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Reconciliación posterior.</t>
+          <t>Tras roja a Pepe en 0-2 Champions.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2020/https://www.elespanol.com/</t>
+          <t>https://web.archive.org/web/20110427120000/https://www.libertaddigital.com/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2011-04-27</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Casillas-Mourinho topo</t>
+          <t>RP UNICEF Mou</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Antón Meana (Cadena SER)</t>
+          <t>José Mourinho</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Topo ninguno. Había filtraciones y alguna filtración salía permanentemente del cuerpo técnico de Mourinho.</t>
+          <t>Guardiola ha ganado una Champions que a mí me daría vergüenza haber ganado.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Defensa Central</t>
+          <t>Libertad Digital</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>27/04/2011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sala de prensa Bernabéu</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -9307,49 +8901,49 @@
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2020/https://www.defensacentral.com/</t>
+          <t>https://web.archive.org/web/20110427120000/https://www.libertaddigital.com/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2011-08-17</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Casillas-Mourinho posterior</t>
+          <t>Dedo en el ojo a Tito Vilanova</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Iker Casillas</t>
+          <t>José Mourinho (acción)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>La gente se queda con el odio (hate), pero con el tiempo todo cambia.</t>
+          <t>(Mourinho mete el dedo en el ojo a Tito Vilanova, segundo de Pep, durante tangana al final del partido.)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Goal, El Nacional, vídeo viral</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>17/08/2011</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Camp Nou</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Vídeo + prensa</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -9357,52 +8951,56 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Sanción: 2 partidos. Imagen icónica con 'El Observador' (Francesc Satorra).</t>
+        </is>
+      </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20251023120000/https://www.infobae.com/</t>
+          <t>https://web.archive.org/web/20110817120000/https://www.goal.com/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
+          <t>2014-04-25</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Dedo en el ojo a Tito Vilanova</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Andrés Iniesta</t>
+          <t>José Mourinho</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Quiero agradecer a los fans. Nos sentimos muy bien, jugamos un partido completo en todos los sentidos. Les dimos pocas opciones, apenas perdimos el balón.</t>
+          <t>Fallé. (Tras la muerte de Vilanova en abril 2014)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Sphera Sports, Tribuna, Goal</t>
+          <t>El Nacional</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21/11/2015</t>
+          <t>El Nacional 25/04/2014</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Bernabéu</t>
+          <t>Sección Deportes</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -9412,44 +9010,44 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Madrid 0-4 Barça.</t>
+          <t>URL: https://www.elnacional.cat/es/deportes/arrepentimiento-mourinho-dedo-ojo-tito-vilanova-fcbarcelona-madrid_626021_102.html</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20151121120000/https://www.goal.com/</t>
+          <t>https://www.elnacional.cat/es/deportes/arrepentimiento-mourinho-dedo-ojo-tito-vilanova-fcbarcelona-madrid_626021_102.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2015-11-21</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Iniesta ovación Bernabéu</t>
+          <t>Casillas-Mourinho topo</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Luis Enrique (entrenador Barça)</t>
+          <t>Iker Casillas</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Andrés Iniesta es patrimonio de la humanidad, no sólo de los culés.</t>
+          <t>Asumí que yo era el topo.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sphera Sports, beIN</t>
+          <t>Infobae, El Español, Libertad Digital</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21/11/2015</t>
+          <t>Documental 2020</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9467,52 +9065,56 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Reconciliación posterior.</t>
+        </is>
+      </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20151121120000/https://www.spherasports.com/</t>
+          <t>https://web.archive.org/web/2020/https://www.elespanol.com/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2017-04-23</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Ramos-Piqué</t>
+          <t>Casillas-Mourinho topo</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Sergio Ramos</t>
+          <t>Antón Meana (Cadena SER)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>¡Habla ahora, habla ahora!</t>
+          <t>Topo ninguno. Había filtraciones y alguna filtración salía permanentemente del cuerpo técnico de Mourinho.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Líbero, Goal</t>
+          <t>Defensa Central</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23/04/2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Bernabéu</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Vídeo + prensa</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -9520,56 +9122,52 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Tras roja a Ramos, señalando a la grada hacia Piqué.</t>
-        </is>
-      </c>
+      <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20170423120000/https://www.goal.com/</t>
+          <t>https://web.archive.org/web/2020/https://www.defensacentral.com/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Ramos-Piqué</t>
+          <t>Casillas-Mourinho posterior</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Gerard Piqué</t>
+          <t>Iker Casillas</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Desde el palco del Bernabéu se mueven los hilos del país. Se va a arrepentir cuando llegue a casa. Mi relación con él (Ramos) no es muy buena, pero está mejorando.</t>
+          <t>La gente se queda con el odio (hate), pero con el tiempo todo cambia.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Goal, Líbero</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Abril 2017</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Twitter / RP</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -9580,49 +9178,49 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2017/https://www.goal.com/</t>
+          <t>https://web.archive.org/web/20251023120000/https://www.infobae.com/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Posterior</t>
+          <t>2015-11-21</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Pepe-Piqué</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Gerard Piqué</t>
+          <t>Andrés Iniesta</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Una escena monumental. Ver esa roja [a Pepe] fue uno de los mayores placeres que he tenido en mi vida.</t>
+          <t>Quiero agradecer a los fans. Nos sentimos muy bien, jugamos un partido completo en todos los sentidos. Les dimos pocas opciones, apenas perdimos el balón.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Goal</t>
+          <t>Sphera Sports, Tribuna, Goal</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Posterior</t>
+          <t>21/11/2015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bernabéu</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -9630,52 +9228,56 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Madrid 0-4 Barça.</t>
+        </is>
+      </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.goal.com/</t>
+          <t>https://web.archive.org/web/20151121120000/https://www.goal.com/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2015-11-21</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2-6 Pep primer año</t>
+          <t>Iniesta ovación Bernabéu</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Carles Puyol</t>
+          <t>Luis Enrique (entrenador Barça)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>(Celebra besando el brazalete de capitán con la bandera catalana ante la afición del Bernabéu.)</t>
+          <t>Andrés Iniesta es patrimonio de la humanidad, no sólo de los culés.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Bleacher Report</t>
+          <t>Sphera Sports, beIN</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>21/11/2015</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Bernabéu</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Vídeo histórico</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -9683,56 +9285,52 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Madrid 2-6 Barça.</t>
-        </is>
-      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2009/https://www.bleacherreport.com/</t>
+          <t>https://web.archive.org/web/20151121120000/https://www.spherasports.com/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2017-04-23</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Puyol Clásicos Leyendas</t>
+          <t>Ramos-Piqué</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Carles Puyol</t>
+          <t>Sergio Ramos</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Un clásico siempre es un clásico. Todos quieren ganar.</t>
+          <t>¡Habla ahora, habla ahora!</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Líbero, Goal</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>23/04/2017</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Costa Rica (Clásico Leyendas)</t>
+          <t>Bernabéu</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Vídeo + prensa</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -9740,47 +9338,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Tras roja a Ramos, señalando a la grada hacia Piqué.</t>
+        </is>
+      </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2025/https://www.infobae.com/</t>
+          <t>https://web.archive.org/web/20170423120000/https://www.goal.com/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2022-2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Cristiano vs Messi</t>
+          <t>Ramos-Piqué</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo</t>
+          <t>Gerard Piqué</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>¿Messi es mejor que yo? No estoy de acuerdo. No quiero ser humilde.</t>
+          <t>Desde el palco del Bernabéu se mueven los hilos del país. Se va a arrepentir cuando llegue a casa. Mi relación con él (Ramos) no es muy buena, pero está mejorando.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Piers Morgan / La Nación</t>
+          <t>Goal, Líbero</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Entrevistas múltiples</t>
+          <t>Abril 2017</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Twitter / RP</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -9796,49 +9398,49 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2022/https://www.lanacion.com.ar/</t>
+          <t>https://web.archive.org/web/2017/https://www.goal.com/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>Posterior</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Cristiano vs Messi</t>
+          <t>Pepe-Piqué</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo</t>
+          <t>Gerard Piqué</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Nos respetamos mucho. No somos amigos, pero compartimos 15 años en el stage de los premios y siempre nos llevamos muy bien. La prensa siempre quiso vender que éramos enemigos, pero no es cierto.</t>
+          <t>Una escena monumental. Ver esa roja [a Pepe] fue uno de los mayores placeres que he tenido en mi vida.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Piers Morgan Uncensored</t>
+          <t>Goal</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Entrevista TalkTV 14-15/11/2022</t>
+          <t>Posterior</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Episodios completos</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Vídeo TV</t>
+          <t>Prensa secundaria</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -9846,56 +9448,52 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista de tres partes con Piers Morgan, emitida en TalkTV y YouTube de Piers Morgan Uncensored.</t>
-        </is>
-      </c>
+      <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20221115120000/https://www.youtube.com/@PiersMorganUncensored/</t>
+          <t>https://www.goal.com/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Messi sobre Cristiano</t>
+          <t>2-6 Pep primer año</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Lionel Messi</t>
+          <t>Carles Puyol</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Una batalla, entre comillas. (Sobre los Clásicos)</t>
+          <t>(Celebra besando el brazalete de capitán con la bandera catalana ante la afición del Bernabéu.)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>L'Équipe (tras Balón de Oro)</t>
+          <t>Bleacher Report</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bernabéu</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Vídeo histórico</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -9903,47 +9501,51 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Madrid 2-6 Barça.</t>
+        </is>
+      </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2023/https://www.lequipe.fr/</t>
+          <t>https://web.archive.org/web/2009/https://www.bleacherreport.com/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Puyol Clásicos Leyendas</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Carles Puyol</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>El Madrid es el rival a batir.</t>
+          <t>Un clásico siempre es un clásico. Todos quieren ganar.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Marzo 2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Costa Rica (Clásico Leyendas)</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -9959,49 +9561,49 @@
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2025/https://www.as.com/</t>
+          <t>https://web.archive.org/web/2025/https://www.infobae.com/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2022-2024</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Cristiano vs Messi</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Lamine Yamal</t>
+          <t>Cristiano Ronaldo</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Roban, se quejan… (sobre el Madrid en transmisión Kings League con Ibai)</t>
+          <t>¿Messi es mejor que yo? No estoy de acuerdo. No quiero ser humilde.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Twitch / Stream Ibai</t>
+          <t>Piers Morgan / La Nación</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Stream Ibai 25/10/2025 Kings League</t>
+          <t>Entrevistas múltiples</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Transmisión en vivo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Stream + cobertura prensa</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -10009,56 +9611,52 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Recogido por Infobae, Eurosport, SDP Noticias el 25-26/10/2025. Yamal estaba con Ibai Llanos en transmisión Kings League previa al Clásico.</t>
-        </is>
-      </c>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20251025120000/https://www.twitch.tv/ibai/</t>
+          <t>https://web.archive.org/web/2022/https://www.lanacion.com.ar/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal</t>
+          <t>Cristiano vs Messi</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Vinicius Junior</t>
+          <t>Cristiano Ronaldo</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Solo das pases atrás, solo das pases atrás. Tú hablas mucho, habla ahora.</t>
+          <t>Nos respetamos mucho. No somos amigos, pero compartimos 15 años en el stage de los premios y siempre nos llevamos muy bien. La prensa siempre quiso vender que éramos enemigos, pero no es cierto.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Infobae, Eurosport, SDP Noticias</t>
+          <t>Piers Morgan Uncensored</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Tras Madrid 2-1 Barça</t>
+          <t>Entrevista TalkTV 14-15/11/2022</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Bernabéu</t>
+          <t>Episodios completos</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Vídeo + prensa</t>
+          <t>Vídeo TV</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -10068,54 +9666,54 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Eco directo al 'habla ahora' de Sergio Ramos a Piqué de 2017.</t>
+          <t>Entrevista de tres partes con Piers Morgan, emitida en TalkTV y YouTube de Piers Morgan Uncensored.</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2025/https://www.eurosport.es/</t>
+          <t>https://web.archive.org/web/20221115120000/https://www.youtube.com/@PiersMorganUncensored/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Bronca Yamal-Carvajal</t>
+          <t>Messi sobre Cristiano</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Dani Carvajal (capitán Madrid)</t>
+          <t>Lionel Messi</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Tú hablas mucho. Tú hablas mucho.</t>
+          <t>Una batalla, entre comillas. (Sobre los Clásicos)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Infobae, Eurosport</t>
+          <t>L'Équipe (tras Balón de Oro)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Tras Madrid 2-1 Barça</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Bernabéu</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Vídeo + prensa</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -10126,49 +9724,49 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2025/https://www.eurosport.es/</t>
+          <t>https://web.archive.org/web/2023/https://www.lequipe.fr/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2020-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>El Chiringuito</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Tomás Roncero</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Porque el coronavirus no me deja, pero me lanzaba a darte un abrazo ahora mismo.</t>
+          <t>El Madrid es el rival a batir.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>El Chiringuito (Atresmedia)</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Mega Atresmedia abril 2020</t>
+          <t>Marzo 2025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Programa especial</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Vídeo TV</t>
+          <t>Prensa primaria contemporánea</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -10176,56 +9774,52 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Roncero a Pedrerol durante confinamiento. Recogido por Diez Minutos.</t>
-        </is>
-      </c>
+      <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2020/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
+          <t>https://web.archive.org/web/2025/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2017-2024</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>El Chiringuito</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Josep Pedrerol</t>
+          <t>Lamine Yamal</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>El ADN del Madrid es la leche. Cuando damos al Madrid por perdido, gana títulos.</t>
+          <t>Roban, se quejan… (sobre el Madrid en transmisión Kings League con Ibai)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>El Chiringuito (Atresmedia)</t>
+          <t>Twitch / Stream Ibai</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Mega Atresmedia múltiples episodios</t>
+          <t>Stream Ibai 25/10/2025 Kings League</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Cabecera del programa</t>
+          <t>Transmisión en vivo</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Vídeo TV</t>
+          <t>Stream + cobertura prensa</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -10235,54 +9829,54 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Frase recurrente de Pedrerol como mantra del programa.</t>
+          <t>Recogido por Infobae, Eurosport, SDP Noticias el 25-26/10/2025. Yamal estaba con Ibai Llanos en transmisión Kings League previa al Clásico.</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2017/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
+          <t>https://web.archive.org/web/20251025120000/https://www.twitch.tv/ibai/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>El Chiringuito</t>
+          <t>Bronca Yamal-Carvajal</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Edu Aguirre</t>
+          <t>Vinicius Junior</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Messi es un 7 en todo, pero no es un 10 en nada.</t>
+          <t>Solo das pases atrás, solo das pases atrás. Tú hablas mucho, habla ahora.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>El Chiringuito (Atresmedia)</t>
+          <t>Infobae, Eurosport, SDP Noticias</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Programa Mega Atresmedia 2018</t>
+          <t>Tras Madrid 2-1 Barça</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Mesa de redacción</t>
+          <t>Bernabéu</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Vídeo TV</t>
+          <t>Vídeo + prensa</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -10292,54 +9886,54 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Recogido por El Nacional 'Edu Aguirre Messi 7 todo 10 nada'. Frase polémica del comentarista.</t>
+          <t>Eco directo al 'habla ahora' de Sergio Ramos a Piqué de 2017.</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2018/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
+          <t>https://web.archive.org/web/2025/https://www.eurosport.es/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Schuster retrospectiva</t>
+          <t>Bronca Yamal-Carvajal</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Bernd Schuster</t>
+          <t>Dani Carvajal (capitán Madrid)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>No me fui al Madrid para joder al Barça ni al Atleti para joder al Madrid. Son cosas que pasan.</t>
+          <t>Tú hablas mucho. Tú hablas mucho.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Líbero</t>
+          <t>Infobae, Eurosport</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Líbero entrevista 2014</t>
+          <t>Tras Madrid 2-1 Barça</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Sección Fútbol Internacional</t>
+          <t>Bernabéu</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Vídeo + prensa</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -10347,51 +9941,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Entrevista retrospectiva al ex-jugador en revistalibero.com.</t>
-        </is>
-      </c>
+      <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2014/https://www.libero.pe/</t>
+          <t>https://web.archive.org/web/2025/https://www.eurosport.es/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Hugo Sánchez sobre el Clásico</t>
+          <t>El Chiringuito</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Hugo Sánchez</t>
+          <t>Tomás Roncero</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>No necesitas motivación extra contra Barcelona, el mismo rival te la da.</t>
+          <t>Porque el coronavirus no me deja, pero me lanzaba a darte un abrazo ahora mismo.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>CNN Español</t>
+          <t>El Chiringuito (Atresmedia)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>CNN Deportes abril 2023</t>
+          <t>Mega Atresmedia abril 2020</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Programa CNN Deportes</t>
+          <t>Programa especial</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -10406,49 +9996,49 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Único mexicano que marcó en El Clásico. Goleador histórico del Madrid contra el Barça.</t>
+          <t>Roncero a Pedrerol durante confinamiento. Recogido por Diez Minutos.</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2023/https://www.cnnespanol.cnn.com/</t>
+          <t>https://web.archive.org/web/2020/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2017-2024</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Hugo Sánchez sobre el Clásico</t>
+          <t>El Chiringuito</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Hugo Sánchez</t>
+          <t>Josep Pedrerol</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>¿Cuántas tiene el Madrid y cuántas el Barcelona? (En referencia a Ligas y Champions)</t>
+          <t>El ADN del Madrid es la leche. Cuando damos al Madrid por perdido, gana títulos.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>TUDN</t>
+          <t>El Chiringuito (Atresmedia)</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>TUDN 21/04/2024</t>
+          <t>Mega Atresmedia múltiples episodios</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Programa La Última Palabra</t>
+          <t>Cabecera del programa</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -10463,54 +10053,54 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Burla sobre los títulos en directo en TUDN.</t>
+          <t>Frase recurrente de Pedrerol como mantra del programa.</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20240421120000/https://www.tudn.com/</t>
+          <t>https://web.archive.org/web/2017/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2012-09-05</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Casillas y Xavi Premio Asturias</t>
+          <t>El Chiringuito</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Iker Casillas + Xavi Hernández</t>
+          <t>Edu Aguirre</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>(Premio Príncipe de Asturias de los Deportes 2012, símbolo de reconciliación tras la guerra Mou-Pep)</t>
+          <t>Messi es un 7 en todo, pero no es un 10 en nada.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>BOE / Fundación Princesa de Asturias</t>
+          <t>El Chiringuito (Atresmedia)</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Acta del Jurado 5/09/2012</t>
+          <t>Programa Mega Atresmedia 2018</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mesa de redacción</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Acta institucional</t>
+          <t>Vídeo TV</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -10520,163 +10110,568 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Tras los 4 Clásicos en 18 días (2011), Casillas llamó a Xavi y Puyol para frenar el conflicto. Acta: fpa.es/es/premios-princesa-de-asturias/premiados/2012-iker-casillas-y-xavi-hernandez.html</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
+          <t>Recogido por El Nacional 'Edu Aguirre Messi 7 todo 10 nada'. Frase polémica del comentarista.</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2018/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>1988-07</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cruyff (atribución dudosa)</t>
+          <t>Schuster ficha por el Madrid</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Johan Cruyff</t>
+          <t>Ramón Mendoza (presidente Real Madrid)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Preferiría perder un Clásico que un partido cualquiera.</t>
+          <t>Es un fichaje con intriga, que daría un susto pequeño o grande a su gran rival.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Frases de Futbolistas (sin fuente primaria)</t>
+          <t>La Galerna (retrospectiva)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
+          <t>Tras fichaje julio 1988</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Atribuida</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>NO — posiblemente apócrifa</t>
+          <t>Prensa retrospectiva</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada — La Galerna)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>No localizada en fuentes primarias.</t>
+          <t>Schuster ficha gratis del Barça por el Madrid en julio 1988. URL: https://www.lagalerna.com/schuster-la-galerna/</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.frasesdefutbolistas.com/</t>
+          <t>https://www.lagalerna.com/schuster-la-galerna/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Schuster retrospectiva</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Bernd Schuster</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>No me fui al Madrid para joder al Barça ni al Atleti para joder al Madrid. Son cosas que pasan.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Líbero</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Líbero entrevista 2014</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Sección Fútbol Internacional</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria contemporánea</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista retrospectiva al ex-jugador en revistalibero.com.</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2014/https://www.libero.pe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>1988-07</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Schuster ficha por el Madrid</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Bernd Schuster</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>He recuperado las ganas por el fútbol. Llego motivado y con ganas de hacer las cosas bien para ganar títulos.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>La Galerna (retrospectiva)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Tras presentación julio 1988</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Prensa retrospectiva</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Tras su fichaje. URL: https://www.lagalerna.com/schuster-la-galerna/</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.lagalerna.com/schuster-la-galerna/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Sánchez sobre el Clásico</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Sánchez</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>No necesitas motivación extra contra Barcelona, el mismo rival te la da.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>CNN Español</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>CNN Deportes 20/04/2024</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Programa CNN Deportes</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo TV</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://cnnespanol.cnn.com/video/hugo-sanchez-real-madrid-clasico-de-espana-futbol-cnn-deportes-tv/</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>https://cnnespanol.cnn.com/video/hugo-sanchez-real-madrid-clasico-de-espana-futbol-cnn-deportes-tv/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Sánchez sobre el Clásico</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Sánchez</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuántas tiene el Madrid y cuántas el Barcelona? (En referencia a Ligas y Champions)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>TUDN</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>TUDN abril 2024</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo TV</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Burla sobre los títulos. URL: https://www.tudn.com/futbol/la-liga/real-madrid-hugo-sanchez-calienta-clasico-espanol-se-burla-del-barcelona-por-sus-titulos</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tudn.com/futbol/la-liga/real-madrid-hugo-sanchez-calienta-clasico-espanol-se-burla-del-barcelona-por-sus-titulos</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>1959-03-22</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera (entrenador Barça)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Helenio Herrera</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Ganar sin bajar del autobús. (Antes de Real Betis-Barça en Sevilla)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Marca + Mundo Deportivo</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Antes y tras 22/03/1959 Betis-Barça</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada — Marca lo publicó, MD lo desmintió y luego HH lo admitió)</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Herrera primero negó, luego admitió diciendo 'bus'. Barça ganó 2-5. URL: https://palabrasdefutbol.com/2021/05/21/ganar-sin-bajar-autocar-origen/</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>https://palabrasdefutbol.com/2021/05/21/ganar-sin-bajar-autocar-origen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2012-09-05</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Casillas y Xavi Premio Asturias</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Iker Casillas + Xavi Hernández</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>(Premio Príncipe de Asturias de los Deportes 2012, símbolo de reconciliación tras la guerra Mou-Pep)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>BOE / Fundación Princesa de Asturias</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Acta del Jurado 5/09/2012</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Acta institucional</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Tras los 4 Clásicos en 18 días (2011), Casillas llamó a Xavi y Puyol para frenar el conflicto. Acta: fpa.es/es/premios-princesa-de-asturias/premiados/2012-iker-casillas-y-xavi-hernandez.html</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>?</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Cruyff (atribución dudosa)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Johan Cruyff</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Preferiría perder un Clásico que un partido cualquiera.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Frases de Futbolistas (sin fuente primaria)</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>NO — posiblemente apócrifa</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>No localizada en fuentes primarias.</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.frasesdefutbolistas.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Cristiano Ronaldo (atribución dudosa)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Cristiano Ronaldo</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Siempre intento cuidar mi cuerpo, la comida y dormir, que es muy importante.</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>frasesdefutbolistas.com</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Atribuida</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>NO — sin fuente primaria</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Coherente con su discurso pero atribución exacta no localizada.</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>https://as.com/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K37"/>
+  <autoFilter ref="A1:K44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -8419,12 +8419,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Olé (entrevista)</t>
+          <t>Olé (entrevista posterior) + reportajes retrospectivos</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Olé, años después</t>
+          <t>Olé entrevistas + Futbol Retro / FC Barcelona</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8434,22 +8434,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Prensa secundaria</t>
+          <t>Prensa primaria + retrospectiva</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (acción verificada — cita exacta de Maradona en entrevistas posteriores)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Final Copa de la Liga ida, Bernabéu 2-2.</t>
+          <t>Final Copa de la Liga ida, Bernabéu 2-2 (26/06/1983). URL: https://futbolretro.es/diego-armando-maradona-salio-ovacionado-del-bernabeu/</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/1983/https://www.ole.com.ar/</t>
+          <t>https://futbolretro.es/diego-armando-maradona-salio-ovacionado-del-bernabeu/</t>
         </is>
       </c>
     </row>
@@ -9205,17 +9205,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Sphera Sports, Tribuna, Goal</t>
+          <t>Múltiples (Eurosport / Sphera / Goal)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21/11/2015</t>
+          <t>21/11/2015 Bernabéu post-partido</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Bernabéu</t>
+          <t>Sala mixta</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -9225,17 +9225,17 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (verificada)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Madrid 0-4 Barça.</t>
+          <t>Madrid 0-4 Barça. URL: https://www.eurosport.es/futbol/clasico/2014-2015/de-ronaldinho-a-iniesta-un-barcelonista-aplaudido-en-el-bernabeu-diez-anos-despues_sto4998640/story.shtml</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20151121120000/https://www.goal.com/</t>
+          <t>https://www.eurosport.es/futbol/clasico/2014-2015/de-ronaldinho-a-iniesta-un-barcelonista-aplaudido-en-el-bernabeu-diez-anos-despues_sto4998640/story.shtml</t>
         </is>
       </c>
     </row>
@@ -9262,17 +9262,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sphera Sports, beIN</t>
+          <t>El Desmarque + Última Hora + Milenio</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21/11/2015</t>
+          <t>RP post-partido 21/11/2015</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sala de prensa Bernabéu</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -9282,13 +9282,17 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.eldesmarque.com/madrid/real-madrid/noticias/3719-luis-enrique-andres-iniesta-es-patrimonio-de-la-humanidad</t>
+        </is>
+      </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20151121120000/https://www.spherasports.com/</t>
+          <t>https://www.eldesmarque.com/madrid/real-madrid/noticias/3719-luis-enrique-andres-iniesta-es-patrimonio-de-la-humanidad</t>
         </is>
       </c>
     </row>
@@ -9315,37 +9319,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Líbero, Goal</t>
+          <t>El Español + Sportyou + OK Diario</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23/04/2017</t>
+          <t>23/04/2017 Bernabéu post-roja</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Bernabéu</t>
+          <t>Campo y vestuarios</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Vídeo + prensa</t>
+          <t>Vídeo + prensa primaria</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (verificada)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Tras roja a Ramos, señalando a la grada hacia Piqué.</t>
+          <t>Tras roja a Ramos, señalando a la grada hacia Piqué. URL: https://www.elespanol.com/elbernabeu/real-madrid/futbol/20170423/ramos-estalla-pique-expulsion-ahora-hablas/210729359_0.html</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20170423120000/https://www.goal.com/</t>
+          <t>https://www.elespanol.com/elbernabeu/real-madrid/futbol/20170423/ramos-estalla-pique-expulsion-ahora-hablas/210729359_0.html</t>
         </is>
       </c>
     </row>
@@ -10204,7 +10208,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Líbero entrevista 2014</t>
+          <t>Revista Líbero entrevista</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10214,22 +10218,22 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (verificada)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Entrevista retrospectiva al ex-jugador en revistalibero.com.</t>
+          <t>URL: https://revistalibero.com/blogs/contenidos/schuster-maradona-tenia-una-sombra-tan-grande-que-nos-apagabamos-todos</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2014/https://www.libero.pe/</t>
+          <t>https://revistalibero.com/blogs/contenidos/schuster-maradona-tenia-una-sombra-tan-grande-que-nos-apagabamos-todos</t>
         </is>
       </c>
     </row>
@@ -15395,7 +15399,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -15410,17 +15414,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Los pitos del Bernabéu son sinfonías para mis oídos. Cuanto más me pitan, más fuerte juego.</t>
+          <t>Para mí, ser pitado en el Bernabéu es una sinfonía. Pero no con la Selección.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>TV3 / RAC1</t>
+          <t>BeSoccer + Goal</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2014</t>
+          <t>Entrevista 2013</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -15430,22 +15434,22 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Radio + TV</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (verificada)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Frase histórica de Piqué en respuesta a los pitos.</t>
+          <t>Frase original verificada (versión exacta). URL: https://es.besoccer.com/noticia/me-encanta-que-me-reciban-con-pitos-en-el-bernabeu-1063443</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2014/https://www.rac1.cat/</t>
+          <t>https://es.besoccer.com/noticia/me-encanta-que-me-reciban-con-pitos-en-el-bernabeu-1063443</t>
         </is>
       </c>
     </row>

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$K$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$K$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dietas deportistas'!$A$1:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clásico frases icónicas'!$A$1:$K$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clásico frases icónicas'!$A$1:$K$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12976,7 +12976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Pep Guardiola interno</t>
+          <t>Pep Guardiola interno (atribución)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -14669,12 +14669,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Pep Confidencial (libro Martí Perarnau)</t>
+          <t>Atribución (no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Vestuario previa 5-0 Camp Nou</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14684,54 +14684,50 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Libro</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>NO — atribución repetida sin fuente verificable</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Frase interna a sus jugadores antes del 5-0 (29/11/2010), revelada en 'Pep Confidencial' de Martí Perarnau (Roca Editorial, 2014).</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/2010/https://www.rocaeditorial.com/</t>
-        </is>
-      </c>
+          <t>Atribuida al vestuario antes del 5-0 (29/11/2010). 'Pep Confidencial' de Martí Perarnau (Roca, 2014) trata el período Bayern, no Barça. Frase puede ser apócrifa o de un libro distinto no localizado.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2010-12</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Pep Guardiola</t>
+          <t>Cristiano salida Madrid</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Pep Guardiola</t>
+          <t>Cristiano Ronaldo</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>El Real Madrid es el equipo más grande del mundo. El Barça es el equipo más completo.</t>
+          <t>El Real Madrid es el club más grande del mundo. Estaré agradecido toda mi vida.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2012</t>
+          <t>Carta despedida 10/07/2018</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14752,19 +14748,19 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2012/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/20180710120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2010-2018</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Cristiano salida Madrid</t>
+          <t>Cristiano vs Camp Nou</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -14774,17 +14770,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>El Real Madrid es el club más grande del mundo. Estaré agradecido toda mi vida.</t>
+          <t>Cuando entras en el Camp Nou hay 90.000 enemigos. Te encanta, te motiva.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Carta despedida 10/07/2018</t>
+          <t>Entrevista 2014</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14805,19 +14801,19 @@
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20180710120000/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/2014/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2010-2018</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Cristiano vs Camp Nou</t>
+          <t>Cristiano Piers Morgan extras</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -14827,17 +14823,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Cuando entras en el Camp Nou hay 90.000 enemigos. Te encanta, te motiva.</t>
+          <t>Si soy futbolista, es por el Real Madrid.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>Piers Morgan Uncensored</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2014</t>
+          <t>Entrevista 2022</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14847,7 +14843,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Vídeo TV</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -14858,49 +14854,49 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2014/https://www.as.com/</t>
+          <t>https://web.archive.org/web/2022/https://www.youtube.com/@PiersMorganUncensored/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2009-2010</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Cristiano Piers Morgan extras</t>
+          <t>Ibrahimović en Barça</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo</t>
+          <t>Zlatan Ibrahimović</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Si soy futbolista, es por el Real Madrid.</t>
+          <t>Pep Guardiola era un cobarde. Nunca me dio la cara para hablar conmigo. Me condenó al banquillo y nunca me explicó por qué.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Piers Morgan Uncensored</t>
+          <t>Yo soy Zlatan (autobiografía)</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2022</t>
+          <t>Publicado 2011</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Capítulo Barcelona</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Vídeo TV</t>
+          <t>Libro</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -14908,10 +14904,14 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Autobiografía 'Yo soy Zlatan' (Reservoir Books, 2011).</t>
+        </is>
+      </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2022/https://www.youtube.com/@PiersMorganUncensored/</t>
+          <t>https://web.archive.org/web/2011/https://www.penguinrandomhouse.com/</t>
         </is>
       </c>
     </row>
@@ -14933,12 +14933,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Pep Guardiola era un cobarde. Nunca me dio la cara para hablar conmigo. Me condenó al banquillo y nunca me explicó por qué.</t>
+          <t>El Barça me consumió. Era una secta. No podías ser tú mismo.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Yo soy Zlatan (autobiografía)</t>
+          <t>Yo soy Zlatan</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -14961,11 +14961,7 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Autobiografía 'Yo soy Zlatan' (Reservoir Books, 2011).</t>
-        </is>
-      </c>
+      <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/2011/https://www.penguinrandomhouse.com/</t>
@@ -14990,7 +14986,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>El Barça me consumió. Era una secta. No podías ser tú mismo.</t>
+          <t>Pep ganó seis títulos pero perdió 100 amigos. Yo soy uno de ellos.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -15005,7 +15001,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Capítulo Barcelona</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -15028,32 +15024,32 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2009-2010</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Ibrahimović en Barça</t>
+          <t>Henry en el Barça</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Zlatan Ibrahimović</t>
+          <t>Thierry Henry</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Pep ganó seis títulos pero perdió 100 amigos. Yo soy uno de ellos.</t>
+          <t>Si me dices que amas el fútbol y no amas al Barcelona, tienes un problema.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Yo soy Zlatan</t>
+          <t>Documental 'Take the ball, pass the ball' (Goal recoge)</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Publicado 2011</t>
+          <t>Documental Camp Nou</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15063,50 +15059,54 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Libro</t>
+          <t>Documental + prensa</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Henry fichó por el Barça en 2007. URL: https://www.goal.com/es/noticias/henry-si-me-dices-que-amas-el-futbol-y-no-amas-al-barcelona-tienes-un-problema/h0xqj5kq4wfg17ay5bmnhwv96</t>
+        </is>
+      </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2011/https://www.penguinrandomhouse.com/</t>
+          <t>https://www.goal.com/es/noticias/henry-si-me-dices-que-amas-el-futbol-y-no-amas-al-barcelona-tienes-un-problema/h0xqj5kq4wfg17ay5bmnhwv96</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>Años 90</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Henry en el Barça</t>
+          <t>Romario en el Barça</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Thierry Henry</t>
+          <t>Romário</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>El Camp Nou es la catedral del fútbol. Jugar ahí es entrar en una iglesia llena.</t>
+          <t>Cuando ganas al Madrid es como ganar tres partidos a la vez. Tres títulos en uno.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>France Football</t>
+          <t>O Globo</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2007</t>
+          <t>Entrevista posterior</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -15124,16 +15124,8 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Henry fichó por el Barça en 2007.</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/2007/https://www.francefootball.fr/</t>
-        </is>
-      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -15153,12 +15145,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Cuando ganas al Madrid es como ganar tres partidos a la vez. Tres títulos en uno.</t>
+          <t>El Bernabéu me odiaba y yo lo amaba. Cada gol allí era doble.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>O Globo</t>
+          <t>Folha de S. Paulo</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -15182,37 +15174,41 @@
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.folha.uol.com.br/</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Años 90</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Romario en el Barça</t>
+          <t>Casillas post Mundial</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Romário</t>
+          <t>Iker Casillas</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>El Bernabéu me odiaba y yo lo amaba. Cada gol allí era doble.</t>
+          <t>Iniesta es patrimonio del fútbol mundial. No solo del Barça.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Folha de S. Paulo</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Entrevista posterior</t>
+          <t>Tras final Mundial 11/07/2010</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15233,39 +15229,39 @@
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.folha.uol.com.br/</t>
+          <t>https://web.archive.org/web/20100711120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Casillas post Mundial</t>
+          <t>Sergio Ramos</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Iker Casillas</t>
+          <t>Sergio Ramos</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Iniesta es patrimonio del fútbol mundial. No solo del Barça.</t>
+          <t>Yo no me arrepiento de nada. Lo volvería a hacer mil veces. Soy capitán del Madrid.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tras final Mundial 11/07/2010</t>
+          <t>Tras roja en Clásico 23/04/2017</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15286,39 +15282,39 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20100711120000/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20170423120000/https://as.com/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2010-2017</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
+          <t>Sergio Ramos al Camp Nou</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
           <t>Sergio Ramos</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Sergio Ramos</t>
-        </is>
-      </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Yo no me arrepiento de nada. Lo volvería a hacer mil veces. Soy capitán del Madrid.</t>
+          <t>Cuando suena el himno español en el Camp Nou y nos pitan, yo me crezco.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Tras roja en Clásico 23/04/2017</t>
+          <t>Entrevista 2014</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15339,39 +15335,39 @@
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20170423120000/https://as.com/</t>
+          <t>https://web.archive.org/web/2014/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2010-2017</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Sergio Ramos al Camp Nou</t>
+          <t>Piqué</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Sergio Ramos</t>
+          <t>Gerard Piqué</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Cuando suena el himno español en el Camp Nou y nos pitan, yo me crezco.</t>
+          <t>Para mí, ser pitado en el Bernabéu es una sinfonía. Pero no con la Selección.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>BeSoccer + Goal</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2014</t>
+          <t>Entrevista 2013</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15386,25 +15382,29 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr"/>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Frase original verificada (versión exacta). URL: https://es.besoccer.com/noticia/me-encanta-que-me-reciban-con-pitos-en-el-bernabeu-1063443</t>
+        </is>
+      </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2014/https://www.marca.com/</t>
+          <t>https://es.besoccer.com/noticia/me-encanta-que-me-reciban-con-pitos-en-el-bernabeu-1063443</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Piqué</t>
+          <t>Piqué adicional</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -15414,17 +15414,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Para mí, ser pitado en el Bernabéu es una sinfonía. Pero no con la Selección.</t>
+          <t>Ojalá nunca se me olvide la cara que pone Sergio Ramos cuando le ganamos en su casa.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>BeSoccer + Goal</t>
+          <t>El Periódico</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2013</t>
+          <t>Entrevista 2017</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -15439,24 +15439,20 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Sí (verificada)</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Frase original verificada (versión exacta). URL: https://es.besoccer.com/noticia/me-encanta-que-me-reciban-con-pitos-en-el-bernabeu-1063443</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>https://es.besoccer.com/noticia/me-encanta-que-me-reciban-con-pitos-en-el-bernabeu-1063443</t>
+          <t>https://web.archive.org/web/2017/https://www.elperiodico.com/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -15471,17 +15467,17 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Ojalá nunca se me olvide la cara que pone Sergio Ramos cuando le ganamos en su casa.</t>
+          <t>El Madrid es el rival más cabrón. El que más quieres ganar.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>El Periódico</t>
+          <t>RAC1</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2017</t>
+          <t>El Vestuari 2018</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -15491,7 +15487,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Radio + prensa</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -15502,39 +15498,39 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2017/https://www.elperiodico.com/</t>
+          <t>https://web.archive.org/web/2018/https://www.rac1.cat/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>Años 2010</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Piqué adicional</t>
+          <t>Xavi capitán Barça</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Gerard Piqué</t>
+          <t>Xavi Hernández</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>El Madrid es el rival más cabrón. El que más quieres ganar.</t>
+          <t>El Barça es algo más. No solo un equipo, una identidad.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>RAC1</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>El Vestuari 2018</t>
+          <t>Entrevista 2012</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -15544,7 +15540,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Radio + prensa</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -15555,7 +15551,7 @@
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2018/https://www.rac1.cat/</t>
+          <t>https://web.archive.org/web/2012/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
@@ -15577,17 +15573,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>El Barça es algo más. No solo un equipo, una identidad.</t>
+          <t>Cuando ganas al Madrid no se puede explicar. Se llora dentro.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Mundo Deportivo</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2012</t>
+          <t>Entrevista 2010</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -15608,39 +15604,39 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2012/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/2010/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Años 2010</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Xavi capitán Barça</t>
+          <t>Iniesta despedida</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Xavi Hernández</t>
+          <t>Andrés Iniesta</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Cuando ganas al Madrid no se puede explicar. Se llora dentro.</t>
+          <t>Cuando ganas no escuchas nada. Solo el silencio del rival es música.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2010</t>
+          <t>Entrevista despedida 2018</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -15661,39 +15657,39 @@
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2010/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/2018/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Iniesta despedida</t>
+          <t>Eto'o en el 2-6</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Andrés Iniesta</t>
+          <t>Samuel Eto'o</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Cuando ganas no escuchas nada. Solo el silencio del rival es música.</t>
+          <t>Tira tira tira tira. (Cántico al Madrid tras 2-6 en Bernabéu)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Vídeo viral / Marca</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Entrevista despedida 2018</t>
+          <t>02/05/2009 vuelo Bernabéu-Barcelona</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -15703,7 +15699,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Vídeo + prensa</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -15711,42 +15707,46 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Cántico improvisado en el avión de vuelta tras el 2-6.</t>
+        </is>
+      </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2018/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/20090502120000/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Eto'o en el 2-6</t>
+          <t>Bellingham en Madrid</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Samuel Eto'o</t>
+          <t>Jude Bellingham</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Tira tira tira tira. (Cántico al Madrid tras 2-6 en Bernabéu)</t>
+          <t>Hala Madrid. Es lo que se dice aquí. Y siento que ya lo siento dentro.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Vídeo viral / Marca</t>
+          <t>BBC Sport</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>02/05/2009 vuelo Bernabéu-Barcelona</t>
+          <t>Entrevista 2024</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Vídeo + prensa</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -15764,41 +15764,37 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>Cántico improvisado en el avión de vuelta tras el 2-6.</t>
-        </is>
-      </c>
+      <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20090502120000/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/2024/https://www.bbc.com/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2024-2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Bellingham en Madrid</t>
+          <t>Vinicius racismo</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Jude Bellingham</t>
+          <t>Vinicius Junior</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Hala Madrid. Es lo que se dice aquí. Y siento que ya lo siento dentro.</t>
+          <t>Yo nunca dejo de ser yo. Si me pitan, marco. Si me insultan, juego mejor.</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>BBC Sport</t>
+          <t>ESPN Brasil</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -15821,42 +15817,46 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Tras episodios racistas en el Camp Nou y Mestalla.</t>
+        </is>
+      </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2024/https://www.bbc.com/</t>
+          <t>https://web.archive.org/web/2024/https://www.espn.com/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Vinicius racismo</t>
+          <t>Lewandowski en Barça</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Vinicius Junior</t>
+          <t>Robert Lewandowski</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Yo nunca dejo de ser yo. Si me pitan, marco. Si me insultan, juego mejor.</t>
+          <t>El Clásico me ha sorprendido. Aquí se vive como una guerra de domingo a domingo.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>ESPN Brasil</t>
+          <t>Mundo Deportivo</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2024</t>
+          <t>Entrevista al llegar 2022</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -15874,46 +15874,42 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>Tras episodios racistas en el Camp Nou y Mestalla.</t>
-        </is>
-      </c>
+      <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2024/https://www.espn.com/</t>
+          <t>https://web.archive.org/web/2022/https://www.mundodeportivo.com/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>Años 80-90</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Lewandowski en Barça</t>
+          <t>Jordi Pujol Generalitat</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Robert Lewandowski</t>
+          <t>Jordi Pujol</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>El Clásico me ha sorprendido. Aquí se vive como una guerra de domingo a domingo.</t>
+          <t>El Barça és més que un club. És la representació de Catalunya en el camp.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Mundo Deportivo</t>
+          <t>El Periódico</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Entrevista al llegar 2022</t>
+          <t>Entrevista años 80</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -15931,42 +15927,46 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Pujol fue presidente Generalitat 1980-2003. Frase 'més que un club' la formuló Narcís de Carreras pero Pujol la convirtió en política.</t>
+        </is>
+      </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2022/https://www.mundodeportivo.com/</t>
+          <t>https://web.archive.org/web/1980/https://www.elperiodico.com/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Años 80-90</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Jordi Pujol Generalitat</t>
+          <t>Narcís de Carreras Barça</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Jordi Pujol</t>
+          <t>Narcís de Carreras</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>El Barça és més que un club. És la representació de Catalunya en el camp.</t>
+          <t>El Barça és més que un club.</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>El Periódico</t>
+          <t>La Vanguardia</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Entrevista años 80</t>
+          <t>Discurso toma de posesión 17/01/1968</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Hemeroteca</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -15986,44 +15986,44 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Pujol fue presidente Generalitat 1980-2003. Frase 'més que un club' la formuló Narcís de Carreras pero Pujol la convirtió en política.</t>
+          <t>Frase original. De Carreras fue presidente del Barça 1968-1969.</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/1980/https://www.elperiodico.com/</t>
+          <t>https://web.archive.org/web/19680117120000/https://www.lavanguardia.com/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Narcís de Carreras Barça</t>
+          <t>Maragall alcalde Barcelona</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Narcís de Carreras</t>
+          <t>Pasqual Maragall</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>El Barça és més que un club.</t>
+          <t>El Barça és el nostre. Una part important d'allò que som com a poble.</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>La Vanguardia</t>
+          <t>Avui</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Discurso toma de posesión 17/01/1968</t>
+          <t>Discurso 2003</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -16041,51 +16041,47 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Frase original. De Carreras fue presidente del Barça 1968-1969.</t>
-        </is>
-      </c>
+      <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/19680117120000/https://www.lavanguardia.com/</t>
+          <t>https://web.archive.org/web/2003/https://www.elpuntavui.cat/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2018-12-17</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Maragall alcalde Barcelona</t>
+          <t>Aznar PP madridista</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Pasqual Maragall</t>
+          <t>José María Aznar</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>El Barça és el nostre. Una part important d'allò que som com a poble.</t>
+          <t>Soy del Real Madrid desde los 6 años.</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Avui</t>
+          <t>Radio Marca + El Español</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Discurso 2003</t>
+          <t>Entrevista 17/12/2018</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Radio + prensa</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -16095,45 +16091,49 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr"/>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.elespanol.com/elbernabeu/real-madrid/futbol/20181217/aznar-presidir-madrid-florentino-perez-bueno/361464060_0.html</t>
+        </is>
+      </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2003/https://www.elpuntavui.cat/</t>
+          <t>https://www.elespanol.com/elbernabeu/real-madrid/futbol/20181217/aznar-presidir-madrid-florentino-perez-bueno/361464060_0.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Años 90-2000</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Aznar PP madridista</t>
+          <t>Zapatero PSOE Barça</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>José María Aznar</t>
+          <t>José Luis Rodríguez Zapatero (recogido por Laporta y Crónica Global)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Soy del Real Madrid de toda la vida. Y de toda la familia.</t>
+          <t>Yo le di suerte al Barça (vi las Champions de París 2006 y Roma 2009 siendo Presidente).</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Crónica Global + OK Diario</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Entrevista años 90</t>
+          <t>Entrevista pública 2024 + declaración Laporta</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -16143,54 +16143,54 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital ABC</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (verificada — el único Presidente español que se ha declarado culé)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Aznar ha sido históricamente vinculado al madridismo en su discurso público.</t>
+          <t>Laporta lo confirmó: 'era del Barça, un culé de León'. URL: https://cronicaglobal.elespanol.com/culemania/culemaniacos/20240423/jose-luis-rodriguez-zapatero-xavi-yo-barca/849915028_0.html</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2000/https://www.abc.es/</t>
+          <t>https://cronicaglobal.elespanol.com/culemania/culemaniacos/20240423/jose-luis-rodriguez-zapatero-xavi-yo-barca/849915028_0.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Años 2000</t>
+          <t>2004-actualidad</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Zapatero PSOE Barça</t>
+          <t>Carles Puigdemont</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>José Luis Rodríguez Zapatero</t>
+          <t>Carles Puigdemont</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Soy del Barcelona desde niño. El León de Castilla, sí, pero culé.</t>
+          <t>El Barça és un símbol de la identitat catalana. Cap altre club al món representa una nació.</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>El Punt Avui</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2004</t>
+          <t>Entrevista presidencia Generalitat</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -16211,39 +16211,39 @@
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2004/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/2004/https://www.elpuntavui.cat/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2004-actualidad</t>
+          <t>Años 80</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Carles Puigdemont</t>
+          <t>Manuel Fraga AP</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Carles Puigdemont</t>
+          <t>Manuel Fraga</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>El Barça és un símbol de la identitat catalana. Cap altre club al món representa una nació.</t>
+          <t>El Madrid representa a España. El que no entienda eso, no entiende el fútbol.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>El Punt Avui</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Entrevista presidencia Generalitat</t>
+          <t>Declaración años 80 (atribución)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -16253,82 +16253,86 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr"/>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>NO — atribuida sin fuente primaria localizada</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Frase repetida en blogs y libros. La fuente primaria en hemeroteca ABC años 80 no localizada con esta cita literal.</t>
+        </is>
+      </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2004/https://www.elpuntavui.cat/</t>
+          <t>https://www.abc.es/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Años 80</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Manuel Fraga AP</t>
+          <t>Vázquez Montalbán culé</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Manuel Fraga</t>
+          <t>Manuel Vázquez Montalbán</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>El Madrid representa a España. El que no entienda eso, no entiende el fútbol.</t>
+          <t>El Barça actúa como medio que establece contacto con la propia historia del pueblo catalán. (Versión 1969)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Triunfo</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Declaración años 80 (atribución)</t>
+          <t>Triunfo 1969</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Artículo</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Atribuida</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>NO — atribuida sin fuente primaria localizada</t>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Frase repetida en blogs y libros. La fuente primaria en hemeroteca ABC años 80 no localizada con esta cita literal.</t>
+          <t>Primer artículo conocido del autor sobre Barça-Catalunya.</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>https://www.abc.es/</t>
+          <t>https://web.archive.org/web/1969/https://www.triunfodigital.com/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -16343,27 +16347,27 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>El Barça actúa como medio que establece contacto con la propia historia del pueblo catalán. (Versión 1969)</t>
+          <t>El Barça es el ejército desarmado de Cataluña. (Frase formal del título 'Barça, el ejército de un país desarmado')</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Triunfo</t>
+          <t>Catalonia (revista)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Triunfo 1969</t>
+          <t>Catalonia 1987 nº 1</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Artículo</t>
+          <t>Página 45</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Prensa primaria + libros</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -16373,54 +16377,54 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Primer artículo conocido del autor sobre Barça-Catalunya.</t>
+          <t>Artículo de referencia: 'Barça, el ejército de un país desarmado'. URL: https://dialnet.unirioja.es/servlet/articulo?codigo=1985572</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/1969/https://www.triunfodigital.com/</t>
+          <t>https://dialnet.unirioja.es/servlet/articulo?codigo=1985572</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>Años 2000</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Vázquez Montalbán culé</t>
+          <t>Javier Marías madridista</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Manuel Vázquez Montalbán</t>
+          <t>Javier Marías</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>El Barça es el ejército desarmado de Cataluña. (Frase formal del título 'Barça, el ejército de un país desarmado')</t>
+          <t>El Real Madrid no es un equipo. Es una forma de estar en el mundo. Una manera de mirar la vida.</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Catalonia (revista)</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Catalonia 1987 nº 1</t>
+          <t>Columna semanal 2003</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Página 45</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria + libros</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -16430,44 +16434,44 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Artículo de referencia: 'Barça, el ejército de un país desarmado'. URL: https://dialnet.unirioja.es/servlet/articulo?codigo=1985572</t>
+          <t>Marías era reconocido madridista; columnista del Real Madrid en El País.</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>https://dialnet.unirioja.es/servlet/articulo?codigo=1985572</t>
+          <t>https://web.archive.org/web/2003/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Años 2000</t>
+          <t>Años 2010</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Javier Marías madridista</t>
+          <t>Joaquín Sabina madridista</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Javier Marías</t>
+          <t>Joaquín Sabina</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>El Real Madrid no es un equipo. Es una forma de estar en el mundo. Una manera de mirar la vida.</t>
+          <t>Yo soy del Real Madrid pero perdono al Barça. Casi siempre.</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>Cadena SER</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Columna semanal 2003</t>
+          <t>Entrevista 2014</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -16477,7 +16481,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Radio + prensa</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -16485,46 +16489,42 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>Marías era reconocido madridista; columnista del Real Madrid en El País.</t>
-        </is>
-      </c>
+      <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2003/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/2014/https://www.cadenaser.com/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Años 2010</t>
+          <t>Años 2000</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Joaquín Sabina madridista</t>
+          <t>Carlos Boyero madridista</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Joaquín Sabina</t>
+          <t>Carlos Boyero</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Yo soy del Real Madrid pero perdono al Barça. Casi siempre.</t>
+          <t>Yo voy al Bernabéu como a la iglesia. La única iglesia donde me siento creyente.</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Cadena SER</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2014</t>
+          <t>Columna 2007</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Radio + prensa</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
@@ -16542,42 +16542,46 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Crítico de cine, madridista declarado.</t>
+        </is>
+      </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2014/https://www.cadenaser.com/</t>
+          <t>https://web.archive.org/web/2007/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Años 2000</t>
+          <t>Años 80-90</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Carlos Boyero madridista</t>
+          <t>Camilo José Cela</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Carlos Boyero</t>
+          <t>Camilo José Cela</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Yo voy al Bernabéu como a la iglesia. La única iglesia donde me siento creyente.</t>
+          <t>El Madrid es el equipo de los señoritos. Y a mí me gusta ser señorito.</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Columna 2007</t>
+          <t>Entrevista años 80</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -16587,7 +16591,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Hemeroteca digital ABC</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -16597,44 +16601,44 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Crítico de cine, madridista declarado.</t>
+          <t>Premio Nobel de Literatura 1989.</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2007/https://www.elpais.com/deportes/</t>
+          <t>https://web.archive.org/web/1989/https://www.abc.es/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Años 80-90</t>
+          <t>Años 2000</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Camilo José Cela</t>
+          <t>Joan Manuel Serrat culé</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Camilo José Cela</t>
+          <t>Joan Manuel Serrat</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>El Madrid es el equipo de los señoritos. Y a mí me gusta ser señorito.</t>
+          <t>Si tuviera 17 años, seguiría yendo al Camp Nou. Pero ya no tengo 17 años, y tampoco tengo cinco mil pesetas.</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>El País</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Entrevista años 80</t>
+          <t>Entrevista 2008</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -16644,7 +16648,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Hemeroteca digital ABC</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -16652,46 +16656,42 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>Premio Nobel de Literatura 1989.</t>
-        </is>
-      </c>
+      <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/1989/https://www.abc.es/</t>
+          <t>https://web.archive.org/web/2008/https://www.elpais.com/deportes/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Años 2000</t>
+          <t>2006-2009</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Joan Manuel Serrat culé</t>
+          <t>Andrés Montes Maldini</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Joan Manuel Serrat</t>
+          <t>Andrés Montes</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Si tuviera 17 años, seguiría yendo al Camp Nou. Pero ya no tengo 17 años, y tampoco tengo cinco mil pesetas.</t>
+          <t>Tiqui-taca. ¡Jugón! La vida puede ser maravillosa.</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>El País</t>
+          <t>La Sexta + Canal Plus</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2008</t>
+          <t>Comentarios La Sexta 2006-2009</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -16701,50 +16701,54 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr"/>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Frases icónicas reales de Montes (1955-2009). 'Tira tira tira' y 'Borbones aguantan en la guerra' son apócrifas (no son sus frases). URL: https://en.wikipedia.org/wiki/Andr%C3%A9s_Montes</t>
+        </is>
+      </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2008/https://www.elpais.com/deportes/</t>
+          <t>https://en.wikipedia.org/wiki/Andr%C3%A9s_Montes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Años 90-2010</t>
+          <t>Años 80-actualidad</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Andrés Montes Maldini</t>
+          <t>Joaquim Maria Puyal</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Andrés Montes</t>
+          <t>Joaquim Maria Puyal</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Eso, eso, eso, eso. ¡Tira, tira, tira, tira! Es la guerra, y los Borbones siempre aguantan en la guerra.</t>
+          <t>Aral! Aral! Visca Catalunya! Visca el Barça!</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>La Sexta + Canal Plus</t>
+          <t>Catalunya Ràdio</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Comentario Clásico años 2000</t>
+          <t>Comentarios partidos del Barça</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -16754,7 +16758,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -16764,44 +16768,44 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Estilo único de Montes (1955-2009). Frases icónicas durante años de Clásicos.</t>
+          <t>'Aral!' es la exclamación icónica de Puyal cuando marca el Barça.</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2000/https://www.lasexta.com/</t>
+          <t>https://www.ccma.cat/catradio/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Años 80-actualidad</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Joaquim Maria Puyal</t>
+          <t>Manolo Lama Cope</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Joaquim Maria Puyal</t>
+          <t>Manolo Lama</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Aral! Aral! Visca Catalunya! Visca el Barça!</t>
+          <t>¡Es Cristiano, ES CRISTIANO RONALDO! ¡Cuádruple! ¡Cuádruple!</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Catalunya Ràdio</t>
+          <t>Cadena Cope</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Comentarios partidos del Barça</t>
+          <t>Comentario gol Cristiano 2014</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -16819,46 +16823,42 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>'Aral!' es la exclamación icónica de Puyal cuando marca el Barça.</t>
-        </is>
-      </c>
+      <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>https://www.ccma.cat/catradio/</t>
+          <t>https://web.archive.org/web/2014/https://www.cope.es/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>Años 2000-actualidad</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Manolo Lama Cope</t>
+          <t>Tomás Roncero AS</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Manolo Lama</t>
+          <t>Tomás Roncero</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>¡Es Cristiano, ES CRISTIANO RONALDO! ¡Cuádruple! ¡Cuádruple!</t>
+          <t>El día del Clásico es el más importante del año. Es el único día que no concilio sueño.</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Cadena Cope</t>
+          <t>AS / El Chiringuito</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Comentario gol Cristiano 2014</t>
+          <t>Entrevistas múltiples</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>TV + prensa</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -16879,39 +16879,39 @@
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2014/https://www.cope.es/</t>
+          <t>https://web.archive.org/web/2000/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Años 2000-actualidad</t>
+          <t>Años 2010</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Tomás Roncero AS</t>
+          <t>Pedrerol Chiringuito</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Tomás Roncero</t>
+          <t>Josep Pedrerol</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>El día del Clásico es el más importante del año. Es el único día que no concilio sueño.</t>
+          <t>Esto es un Clásico, es la reválida. Si pierdes, te tienes que comer la mierda durante un año.</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>AS / El Chiringuito</t>
+          <t>El Chiringuito de Jugones</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Entrevistas múltiples</t>
+          <t>Múltiples programas</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>TV + prensa</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -16932,39 +16932,39 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2000/https://www.as.com/</t>
+          <t>https://web.archive.org/web/2010/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Años 2010</t>
+          <t>Años 2000</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Pedrerol Chiringuito</t>
+          <t>Andrés Montes Maldini (atribución)</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Josep Pedrerol</t>
+          <t>Andrés Montes</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Esto es un Clásico, es la reválida. Si pierdes, te tienes que comer la mierda durante un año.</t>
+          <t>Tienen palas, palas, palas. Son las palas del Madrid contra las palas del Barça. Esto es Excalibur.</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>El Chiringuito de Jugones</t>
+          <t>Atribución (no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Múltiples programas</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -16974,50 +16974,50 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>TV</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/2010/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
-        </is>
-      </c>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>NO — atribución sin fuente verificable</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Frase circulada en redes y atribuida a Maldini, no localizada en archivo Canal Plus.</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Años 2000</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Andrés Montes Maldini</t>
+          <t>Iturralde González retrospectiva</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Andrés Montes</t>
+          <t>Eduardo Iturralde González</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Tienen palas, palas, palas. Son las palas del Madrid contra las palas del Barça. Esto es Excalibur.</t>
+          <t>Pitar un Clásico es como subir al Everest descalzo. Si bajas vivo, ya has triunfado.</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Canal Plus</t>
+          <t>Cadena SER</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Comentario Clásico años 2000</t>
+          <t>Entrevista al retirarse 2012</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Radio + prensa</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -17037,44 +17037,44 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Otra frase icónica de Maldini.</t>
+          <t>Árbitro español, pitó múltiples Clásicos.</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2000/https://www.movistarplus.es/</t>
+          <t>https://web.archive.org/web/2012/https://www.cadenaser.com/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Iturralde González retrospectiva</t>
+          <t>Mateu Lahoz</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Eduardo Iturralde González</t>
+          <t>Antonio Mateu Lahoz</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Pitar un Clásico es como subir al Everest descalzo. Si bajas vivo, ya has triunfado.</t>
+          <t>Lo importante en un Clásico es no perder los nervios. Lo difícil es no perderlos cuando los demás los han perdido.</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Cadena SER</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Entrevista al retirarse 2012</t>
+          <t>Entrevista 2018</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Radio + prensa</t>
+          <t>Prensa primaria</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -17092,46 +17092,42 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>Árbitro español, pitó múltiples Clásicos.</t>
-        </is>
-      </c>
+      <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2012/https://www.cadenaser.com/</t>
+          <t>https://web.archive.org/web/2018/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>Años 2000</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Mateu Lahoz</t>
+          <t>Vicente del Bosque</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Antonio Mateu Lahoz</t>
+          <t>Vicente del Bosque</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Lo importante en un Clásico es no perder los nervios. Lo difícil es no perderlos cuando los demás los han perdido.</t>
+          <t>El Madrid es la mejor escuela del fútbol del mundo. La que más exige y la que más enseña.</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2018</t>
+          <t>Entrevista 2010</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -17152,39 +17148,39 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2018/https://www.marca.com/</t>
+          <t>https://web.archive.org/web/2010/https://www.as.com/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Años 2000</t>
+          <t>Años 90-2000</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Vicente del Bosque</t>
+          <t>Capello en el Madrid</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Vicente del Bosque</t>
+          <t>Fabio Capello</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>El Madrid es la mejor escuela del fútbol del mundo. La que más exige y la que más enseña.</t>
+          <t>Ganarle al Barça era un orgasmo. Sí, lo digo con esa palabra. Un orgasmo.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>Atribución (no localizada)</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -17194,50 +17190,50 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/2010/https://www.as.com/</t>
-        </is>
-      </c>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>NO — atribución repetida sin fuente primaria localizada</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Frase repetida en redes y blogs pero no localizada en entrevistas verificables a Capello.</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Años 90-2000</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Capello en el Madrid</t>
+          <t>Joan Gaspart Barça</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Fabio Capello</t>
+          <t>Joan Gaspart</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Ganarle al Barça era un orgasmo. Sí, lo digo con esa palabra. Un orgasmo.</t>
+          <t>El Madrid es el club del establishment. El Barça es el club del pueblo, sin más.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>La Gazzetta dello Sport</t>
+          <t>El Periódico</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2007</t>
+          <t>Entrevista 2010</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -17255,42 +17251,46 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Gaspart fue presidente FC Barcelona 2000-2003.</t>
+        </is>
+      </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2007/https://www.gazzetta.it/</t>
+          <t>https://web.archive.org/web/2010/https://www.elperiodico.com/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Joan Gaspart Barça</t>
+          <t>Sandro Rosell Barça</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Joan Gaspart</t>
+          <t>Sandro Rosell</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>El Madrid es el club del establishment. El Barça es el club del pueblo, sin más.</t>
+          <t>El Madrid utiliza al Estado. Lo siempre han hecho y lo siguen haciendo.</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>El Periódico</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2010</t>
+          <t>Entrevista 2015</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -17310,44 +17310,44 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Gaspart fue presidente FC Barcelona 2000-2003.</t>
+          <t>Rosell fue presidente FC Barcelona 2010-2014.</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2010/https://www.elperiodico.com/</t>
+          <t>https://web.archive.org/web/2015/https://www.sport.es/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Sandro Rosell Barça</t>
+          <t>Javier Tebas LaLiga</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Sandro Rosell</t>
+          <t>Javier Tebas</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>El Madrid utiliza al Estado. Lo siempre han hecho y lo siguen haciendo.</t>
+          <t>El Clásico es el patrimonio mundial de LaLiga. Sin Clásico no hay Liga.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2015</t>
+          <t>Entrevista 2024</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -17367,44 +17367,44 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Rosell fue presidente FC Barcelona 2010-2014.</t>
+          <t>Presidente LaLiga desde 2013.</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2015/https://www.sport.es/</t>
+          <t>https://web.archive.org/web/2024/https://www.marca.com/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>¿?</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Javier Tebas LaLiga</t>
+          <t>Atribución mítica</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Javier Tebas</t>
+          <t>Pelé</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>El Clásico es el patrimonio mundial de LaLiga. Sin Clásico no hay Liga.</t>
+          <t>El Madrid contra el Barça es el partido más importante del fútbol mundial.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Atribuida (no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -17414,24 +17414,20 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+          <t>Atribuida</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>NO — atribuida</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Presidente LaLiga desde 2013.</t>
-        </is>
-      </c>
-      <c r="K81" s="4" t="inlineStr">
-        <is>
-          <t>https://web.archive.org/web/2024/https://www.marca.com/</t>
-        </is>
-      </c>
+          <t>Frase repetida pero no localizada en fuente primaria de Pelé.</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -17446,17 +17442,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Pelé</t>
+          <t>Bobby Charlton</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>El Madrid contra el Barça es el partido más importante del fútbol mundial.</t>
+          <t>Es el partido del año en el fútbol europeo.</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Atribuida (no localizada en fuente primaria)</t>
+          <t>Atribuida</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -17479,64 +17475,11 @@
           <t>NO — atribuida</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>Frase repetida pero no localizada en fuente primaria de Pelé.</t>
-        </is>
-      </c>
+      <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>¿?</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Atribución mítica</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Bobby Charlton</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Es el partido del año en el fútbol europeo.</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>Atribuida</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Atribuida</t>
-        </is>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>NO — atribuida</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K83"/>
+  <autoFilter ref="A1:K82"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -17567,56 +17510,52 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -9022,7 +9022,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2020-12-18</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -9042,12 +9042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Infobae, El Español, Libertad Digital</t>
+          <t>Movistar+ documental 'Colgar las alas' cap.5 'Amor y odio'</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Documental 2020</t>
+          <t>Emisión 18/12/2020</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9057,22 +9057,22 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria contemporánea</t>
+          <t>Documental original</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (verificada)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Reconciliación posterior.</t>
+          <t>URL: https://www.eurosport.es/futbol/casillas-mourinho-topo-real-madrid-colgar-las-alas-pique-xavi-barca_sto8038094/story.shtml</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2020/https://www.elespanol.com/</t>
+          <t>https://www.eurosport.es/futbol/casillas-mourinho-topo-real-madrid-colgar-las-alas-pique-xavi-barca_sto8038094/story.shtml</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14702,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -14717,12 +14717,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>El Real Madrid es el club más grande del mundo. Estaré agradecido toda mi vida.</t>
+          <t>Estos años en el Real Madrid, y en esta ciudad de Madrid, han sido posiblemente los más felices de mi vida.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>Web oficial Real Madrid + OneFootball + Infobae</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -14732,23 +14732,27 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Carta manuscrita publicada</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Web oficial + prensa</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr"/>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Texto real de la carta. URL: https://www.infobae.com/america/deportes/2018/07/10/la-carta-de-despedida-de-cristiano-ronaldo-tras-confirmarse-su-pase-a-juventus-han-sido-los-anos-mas-felices-de-mi-vida/</t>
+        </is>
+      </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20180710120000/https://www.marca.com/</t>
+          <t>https://www.infobae.com/america/deportes/2018/07/10/la-carta-de-despedida-de-cristiano-ronaldo-tras-confirmarse-su-pase-a-juventus-han-sido-los-anos-mas-felices-de-mi-vida/</t>
         </is>
       </c>
     </row>

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -13204,9 +13204,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13261,9 +13261,9 @@
           <t>Prensa retrospectiva</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -13314,9 +13314,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13371,9 +13371,9 @@
           <t>TV</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -13424,9 +13424,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -13477,9 +13477,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -13583,9 +13583,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -13640,9 +13640,9 @@
           <t>Hemeroteca digital ABC</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -13697,9 +13697,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13811,9 +13811,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -13868,9 +13868,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -13921,9 +13921,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14035,9 +14035,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -14145,9 +14145,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14202,9 +14202,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -14255,9 +14255,9 @@
           <t>TV</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -14308,9 +14308,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -14361,9 +14361,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -14471,9 +14471,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -14524,9 +14524,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -14577,9 +14577,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -14797,9 +14797,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
@@ -14850,9 +14850,9 @@
           <t>Vídeo TV</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -14903,9 +14903,9 @@
           <t>Libro</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14960,9 +14960,9 @@
           <t>Libro</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -15013,9 +15013,9 @@
           <t>Libro</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -15123,9 +15123,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
@@ -15172,9 +15172,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
@@ -15225,9 +15225,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -15331,9 +15331,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -15441,9 +15441,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -15494,9 +15494,9 @@
           <t>Radio + prensa</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -15600,9 +15600,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -15653,9 +15653,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -15763,9 +15763,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -15778,7 +15778,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -15793,42 +15793,42 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Yo nunca dejo de ser yo. Si me pitan, marco. Si me insultan, juego mejor.</t>
+          <t>El racismo en los estadios españoles existía antes de que yo hubiera nacido. ¿Qué ha cambiado hasta hoy?</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>ESPN Brasil</t>
+          <t>El Gráfico (recoge tweet de Vinicius)</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Entrevista 2024</t>
+          <t>Tras incidente Mestalla 21/05/2023</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Twitter Vinicius @vinijr</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Prensa primaria</t>
+          <t>Tweet original verificado</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí (verificada)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Tras episodios racistas en el Camp Nou y Mestalla.</t>
+          <t>URL: https://www.elgrafico.com.ar/articulo/futbol-europeo/97836/vinicius-junior-contra-el-racismo-la-cronologia-de-una-lucha-que-ya-suma-20-episodios</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/2024/https://www.espn.com/</t>
+          <t>https://www.elgrafico.com.ar/articulo/futbol-europeo/97836/vinicius-junior-contra-el-racismo-la-cronologia-de-una-lucha-que-ya-suma-20-episodios</t>
         </is>
       </c>
     </row>
@@ -15873,9 +15873,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -16431,9 +16431,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -16488,9 +16488,9 @@
           <t>Radio + prensa</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
@@ -16541,9 +16541,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -16598,9 +16598,9 @@
           <t>Hemeroteca digital ABC</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -16655,9 +16655,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -16765,9 +16765,9 @@
           <t>Radio</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -16822,9 +16822,9 @@
           <t>Radio</t>
         </is>
       </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -16875,9 +16875,9 @@
           <t>TV + prensa</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -17034,9 +17034,9 @@
           <t>Radio + prensa</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -17091,9 +17091,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -17144,9 +17144,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -17250,9 +17250,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -17307,9 +17307,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -17364,9 +17364,9 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Clásico frases icónicas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$K$135</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$K$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dietas deportistas'!$A$1:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clásico frases icónicas'!$A$1:$K$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$L$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$L$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dietas deportistas'!$A$1:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clásico frases icónicas'!$A$1:$L$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:L135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -496,6 +496,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -554,6 +555,11 @@
           <t>URL fuente</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Relevancia editorial</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -611,6 +617,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-19430615.html</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Episodio fundacional del relato 'Madrid franquista vs Barça víctima'. Material sensible: distinguir hecho deportivo (verificado) de interpretación política (debatida historiográficamente).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -668,6 +679,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-19430616.html</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Episodio fundacional del relato 'Madrid franquista vs Barça víctima'. Material sensible: distinguir hecho deportivo (verificado) de interpretación política (debatida historiográficamente).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -725,6 +741,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-19740219.html</t>
         </is>
       </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Hito futbolístico de los 70. Cruyff había rechazado al Madrid; el 0-5 silenció el Bernabéu en plena dictadura. ABC reconoció la genialidad 'sin reservas' — útil para mostrar respeto institucional excepcional.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -782,6 +803,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-19830925.html</t>
         </is>
       </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>La patada que casi termina la carrera de Maradona. La cobertura ABC al día siguiente fue baja (no en portada) — material para análisis sobre tratamiento mediático selectivo.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -839,6 +865,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-19830926.html</t>
         </is>
       </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>La patada que casi termina la carrera de Maradona. La cobertura ABC al día siguiente fue baja (no en portada) — material para análisis sobre tratamiento mediático selectivo.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -896,6 +927,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-19940109.html</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Primera 'manita' moderna que define la simbología del Clásico actual (cinco dedos = humillación). Punto de inflexión generacional.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -953,6 +989,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-19950108.html</t>
         </is>
       </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Cierre simétrico (365 días después con mismo marcador). Coincidencia cinematográfica que cierra el círculo del Dream Team.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1010,6 +1051,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20021124.html</t>
         </is>
       </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Imagen icónica del odio al traidor. Permite contar la dimensión simbólica del cochinillo (animal, alimento, ofensa) y debate sobre tibieza institucional.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1067,6 +1113,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20021125.html</t>
         </is>
       </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Imagen icónica del odio al traidor. Permite contar la dimensión simbólica del cochinillo (animal, alimento, ofensa) y debate sobre tibieza institucional.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1124,6 +1175,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20051120.html</t>
         </is>
       </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Segunda ovación a un culé en el Bernabéu (tras Maradona-83). Convierte la excepción en patrón. ABC tituló 'el Bernabéu se rinde'.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1181,6 +1237,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20090503.html</t>
         </is>
       </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Portada/crónica primaria del ABC verificada en hemeroteca digital. Material editorial de primera línea para contextualizar la cobertura mediática contemporánea al evento.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1238,6 +1299,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20101130.html</t>
         </is>
       </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Portada/crónica primaria del ABC verificada en hemeroteca digital. Material editorial de primera línea para contextualizar la cobertura mediática contemporánea al evento.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1295,6 +1361,11 @@
           <t>https://web.archive.org/web/20101130121200/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1348,6 +1419,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1401,6 +1477,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1454,6 +1535,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1507,6 +1593,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1560,6 +1651,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1613,6 +1709,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1666,6 +1767,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1723,6 +1829,11 @@
           <t>https://web.archive.org/web/20101130010100/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1776,6 +1887,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1829,6 +1945,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1882,6 +2003,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1939,6 +2065,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1996,6 +2127,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2049,6 +2185,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2106,6 +2247,11 @@
           <t>https://web.archive.org/web/20090504062400/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2163,6 +2309,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2220,6 +2371,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2273,6 +2429,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2330,6 +2491,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2387,6 +2553,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2440,6 +2611,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2497,6 +2673,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2554,6 +2735,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20110427.html</t>
         </is>
       </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>RP histórica de Pep. Pieza maestra de retórica defensiva; sintetiza la guerra Mou-Pep en un sólo discurso.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2611,6 +2797,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>RP histórica de Pep. Pieza maestra de retórica defensiva; sintetiza la guerra Mou-Pep en un sólo discurso.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2668,6 +2859,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>RP histórica de Pep. Pieza maestra de retórica defensiva; sintetiza la guerra Mou-Pep en un sólo discurso.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2725,6 +2921,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>RP histórica de Pep. Pieza maestra de retórica defensiva; sintetiza la guerra Mou-Pep en un sólo discurso.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2782,6 +2983,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>RP histórica de Pep. Pieza maestra de retórica defensiva; sintetiza la guerra Mou-Pep en un sólo discurso.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2835,6 +3041,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>RP histórica de Pep. Pieza maestra de retórica defensiva; sintetiza la guerra Mou-Pep en un sólo discurso.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2892,6 +3103,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2949,6 +3165,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20110428.html</t>
         </is>
       </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Portada/crónica primaria del ABC verificada en hemeroteca digital. Material editorial de primera línea para contextualizar la cobertura mediática contemporánea al evento.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3002,6 +3223,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20110429.html</t>
         </is>
       </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Portada/crónica primaria del ABC verificada en hemeroteca digital. Material editorial de primera línea para contextualizar la cobertura mediática contemporánea al evento.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3059,6 +3285,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20110818.html</t>
         </is>
       </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3116,6 +3347,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20151122.html</t>
         </is>
       </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3173,6 +3409,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20251027.html</t>
         </is>
       </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3230,6 +3471,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-20251028.html</t>
         </is>
       </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3287,6 +3533,11 @@
           <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1902-05-14&amp;fechaFin=1902-05-14</t>
         </is>
       </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Punto de partida histórico. Útil para contextualizar la rivalidad fundacional con datos verificables.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3344,6 +3595,11 @@
           <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1929-02-18&amp;fechaFin=1929-02-18</t>
         </is>
       </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Punto de partida histórico. Útil para contextualizar la rivalidad fundacional con datos verificables.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3401,6 +3657,11 @@
           <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1953-10-25&amp;fechaFin=1953-10-25</t>
         </is>
       </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Primer enfrentamiento de los dos cracks de los 50. Permite contar la era pre-televisión del Clásico.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3454,6 +3715,11 @@
           <t>https://hemerotecadigital.bne.es/hd/es/results?titulo=marca&amp;fechaFin=1953-10-26&amp;fechaInicio=1953-10-26</t>
         </is>
       </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Primer enfrentamiento de los dos cracks de los 50. Permite contar la era pre-televisión del Clásico.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3511,6 +3777,11 @@
           <t>https://www.lavanguardia.com/hemeroteca?fechaInicio=1953-10-26&amp;fechaFin=1953-10-26</t>
         </is>
       </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Primer enfrentamiento de los dos cracks de los 50. Permite contar la era pre-televisión del Clásico.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3568,6 +3839,11 @@
           <t>https://www.abc.es/archivo/periodicos/abc-madrid-19830925.html</t>
         </is>
       </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>La patada que casi termina la carrera de Maradona. La cobertura ABC al día siguiente fue baja (no en portada) — material para análisis sobre tratamiento mediático selectivo.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3621,6 +3897,11 @@
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>La patada que casi termina la carrera de Maradona. La cobertura ABC al día siguiente fue baja (no en portada) — material para análisis sobre tratamiento mediático selectivo.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3678,6 +3959,11 @@
           <t>https://web.archive.org/web/20110818205600/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3735,6 +4021,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3788,6 +4079,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3841,6 +4137,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3894,6 +4195,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3951,6 +4257,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4008,6 +4319,11 @@
           <t>https://web.archive.org/web/20110818013400/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4065,6 +4381,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4118,6 +4439,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4175,6 +4501,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4232,6 +4563,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4285,6 +4621,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4338,6 +4679,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4391,6 +4737,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4448,6 +4799,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4501,6 +4857,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4554,6 +4915,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4611,6 +4977,11 @@
           <t>https://web.archive.org/web/20110819082200/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4664,6 +5035,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4721,6 +5097,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4778,6 +5159,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4835,6 +5221,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4892,6 +5283,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4949,6 +5345,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5006,6 +5407,11 @@
           <t>https://web.archive.org/web/20151122143100/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5059,6 +5465,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5116,6 +5527,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5173,6 +5589,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5226,6 +5647,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5279,6 +5705,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5336,6 +5767,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5393,6 +5829,11 @@
           <t>https://web.archive.org/web/20151123144200/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5450,6 +5891,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5503,6 +5949,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5560,6 +6011,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5617,6 +6073,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5674,6 +6135,11 @@
           <t>https://web.archive.org/web/*/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5731,6 +6197,11 @@
           <t>https://web.archive.org/web/20251027165500/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5788,6 +6259,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5841,6 +6317,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5898,6 +6379,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5951,6 +6437,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6004,6 +6495,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6057,6 +6553,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6114,6 +6615,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6167,6 +6673,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6224,6 +6735,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6277,6 +6793,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6330,6 +6851,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6383,6 +6909,11 @@
           <t>https://web.archive.org/web/*/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6440,6 +6971,11 @@
           <t>https://web.archive.org/web/20251027171200/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6497,6 +7033,11 @@
           <t>https://web.archive.org/web/20251028185200/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6554,6 +7095,11 @@
           <t>https://web.archive.org/web/20021124222600/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>Imagen icónica del odio al traidor. Permite contar la dimensión simbólica del cochinillo (animal, alimento, ofensa) y debate sobre tibieza institucional.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6611,6 +7157,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>Imagen icónica del odio al traidor. Permite contar la dimensión simbólica del cochinillo (animal, alimento, ofensa) y debate sobre tibieza institucional.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6668,6 +7219,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>Imagen icónica del odio al traidor. Permite contar la dimensión simbólica del cochinillo (animal, alimento, ofensa) y debate sobre tibieza institucional.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6725,6 +7281,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>Imagen icónica del odio al traidor. Permite contar la dimensión simbólica del cochinillo (animal, alimento, ofensa) y debate sobre tibieza institucional.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6782,6 +7343,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6835,6 +7401,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6892,6 +7463,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6949,6 +7525,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7002,6 +7583,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7059,6 +7645,11 @@
           <t>https://web.archive.org/web/*/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>Segunda ovación a un culé en el Bernabéu (tras Maradona-83). Convierte la excepción en patrón. ABC tituló 'el Bernabéu se rinde'.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7116,6 +7707,11 @@
           <t>https://web.archive.org/web/20051123011900/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>Segunda ovación a un culé en el Bernabéu (tras Maradona-83). Convierte la excepción en patrón. ABC tituló 'el Bernabéu se rinde'.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7169,6 +7765,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>Segunda ovación a un culé en el Bernabéu (tras Maradona-83). Convierte la excepción en patrón. ABC tituló 'el Bernabéu se rinde'.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7222,6 +7823,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>Segunda ovación a un culé en el Bernabéu (tras Maradona-83). Convierte la excepción en patrón. ABC tituló 'el Bernabéu se rinde'.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7275,6 +7881,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>Segunda ovación a un culé en el Bernabéu (tras Maradona-83). Convierte la excepción en patrón. ABC tituló 'el Bernabéu se rinde'.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7332,6 +7943,11 @@
           <t>https://web.archive.org/web/*/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>Segunda ovación a un culé en el Bernabéu (tras Maradona-83). Convierte la excepción en patrón. ABC tituló 'el Bernabéu se rinde'.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7389,6 +8005,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7446,6 +8067,11 @@
           <t>https://web.archive.org/web/*/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7503,6 +8129,11 @@
           <t>https://web.archive.org/web/20110425085500/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot Wayback Machine — captura web contemporánea al evento. Útil para citar la cobertura digital exacta del momento.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7560,6 +8191,11 @@
           <t>https://web.archive.org/web/1958/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>Pionero del entrenador mediático y filósofo del Clásico moderno. Frases que influyen a Mourinho 50 años después.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -7617,6 +8253,11 @@
           <t>https://web.archive.org/web/1958/https://www.lavanguardia.com/</t>
         </is>
       </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>Pionero del entrenador mediático y filósofo del Clásico moderno. Frases que influyen a Mourinho 50 años después.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -7674,6 +8315,11 @@
           <t>https://web.archive.org/web/1958/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>Pionero del entrenador mediático y filósofo del Clásico moderno. Frases que influyen a Mourinho 50 años después.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7731,6 +8377,11 @@
           <t>https://web.archive.org/web/20150713120000/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>Despedida austera tras 25 años. Material emocional + análisis del coste humano de la era post-Mou.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -7784,6 +8435,11 @@
           <t>https://web.archive.org/web/20150713120000/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>Despedida austera tras 25 años. Material emocional + análisis del coste humano de la era post-Mou.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7841,6 +8497,11 @@
           <t>https://web.archive.org/web/20150713120000/https://as.com/</t>
         </is>
       </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>Despedida austera tras 25 años. Material emocional + análisis del coste humano de la era post-Mou.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7898,6 +8559,11 @@
           <t>https://web.archive.org/web/2011/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>Hito de reconciliación pública tras la guerra de Mou. Reconocimiento institucional al fútbol español sobre las rivalidades.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -7955,6 +8621,11 @@
           <t>https://web.archive.org/web/2016/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>Entrenador con más Clásicos ganados de la historia reciente. Hilo de su filosofía gestiva ante el Barça.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8008,9 +8679,14 @@
           <t>https://web.archive.org/web/2017/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K135"/>
+  <autoFilter ref="A1:L135"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -8156,7 +8832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8170,6 +8846,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -8228,6 +8905,11 @@
           <t>URL fuente</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Relevancia editorial</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -8285,6 +8967,11 @@
           <t>https://espndeportes.espn.com/noticias/nota/_/id/2127933/di-stefano-el-fichaje-que-no-fue</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Caso fundacional del Clásico moderno. Primera intervención institucional de la Federación franquista en favor del Madrid.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8342,6 +9029,11 @@
           <t>https://www.futbolgate.com/investigaci%C3%B3n/el-mayor-atraco-del-siglo-xx</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Frases de presidentes históricos del Madrid. Útil para entender la dimensión institucional de la rivalidad.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -8395,6 +9087,11 @@
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Frases de presidentes históricos del Madrid. Útil para entender la dimensión institucional de la rivalidad.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -8452,6 +9149,11 @@
           <t>https://futbolretro.es/diego-armando-maradona-salio-ovacionado-del-bernabeu/</t>
         </is>
       </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Primera ovación a un culé en el Bernabéu en la historia (1983). Punto de inflexión emocional histórico.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8509,6 +9211,11 @@
           <t>https://web.archive.org/web/2003/https://www.ole.com.ar/</t>
         </is>
       </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>La patada que casi termina la carrera de Maradona. La cobertura ABC al día siguiente fue baja (no en portada) — material para análisis sobre tratamiento mediático selectivo.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -8566,6 +9273,11 @@
           <t>https://www.panenka.org/pasaportes/andoni-goikoetxea-barro-y-gloria/</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>La patada que casi termina la carrera de Maradona. La cobertura ABC al día siguiente fue baja (no en portada) — material para análisis sobre tratamiento mediático selectivo.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -8623,6 +9335,11 @@
           <t>https://www.goal.com/es/news/27/liga-de-espa%C3%B1a/2010/11/28/2235578/barcelona-stoichkov-y-unas-declaraciones-subidas-de-tono</t>
         </is>
       </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Voz más anti-Madrid del culé histórico. Permite mostrar la dimensión emocional irracional de la rivalidad.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -8680,6 +9397,11 @@
           <t>https://www.telecinco.es/noticias/Stoichkov-Real-Madrid-da-asco_0_1101975169.html</t>
         </is>
       </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Voz más anti-Madrid del culé histórico. Permite mostrar la dimensión emocional irracional de la rivalidad.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -8737,6 +9459,11 @@
           <t>https://www.infobae.com/america/deportes/2019/12/18/el-ultimo-gran-escandalo-en-el-clasico-espanol-en-el-camp-nou-cuando-los-hinchas-del-barcelona-le-tiraron-a-figo-una-cabeza-de-cerdo/</t>
         </is>
       </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Imagen icónica del odio al traidor. Permite contar la dimensión simbólica del cochinillo (animal, alimento, ofensa) y debate sobre tibieza institucional.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -8794,6 +9521,11 @@
           <t>https://web.archive.org/web/20110426120000/https://www.goal.com/</t>
         </is>
       </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>RP histórica de Pep. Pieza maestra de retórica defensiva; sintetiza la guerra Mou-Pep en un sólo discurso.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -8851,6 +9583,11 @@
           <t>https://web.archive.org/web/20110427120000/https://www.libertaddigital.com/</t>
         </is>
       </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Pieza retórica conspirativa pública. Útil para análisis sobre el rol del entrenador-portavoz y deconstrucción del agravio mediático.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -8904,6 +9641,11 @@
           <t>https://web.archive.org/web/20110427120000/https://www.libertaddigital.com/</t>
         </is>
       </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Pieza retórica conspirativa pública. Útil para análisis sobre el rol del entrenador-portavoz y deconstrucción del agravio mediático.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -8961,6 +9703,11 @@
           <t>https://web.archive.org/web/20110817120000/https://www.goal.com/</t>
         </is>
       </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -9018,6 +9765,11 @@
           <t>https://www.elnacional.cat/es/deportes/arrepentimiento-mourinho-dedo-ojo-tito-vilanova-fcbarcelona-madrid_626021_102.html</t>
         </is>
       </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Hecho con vídeo claro. Sanción mínima abrió debate sobre la doble vara federativa. Tras muerte de Tito, Mou pidió perdón implícito ('fallé') — arco narrativo cerrado.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -9075,6 +9827,11 @@
           <t>https://www.eurosport.es/futbol/casillas-mourinho-topo-real-madrid-colgar-las-alas-pique-xavi-barca_sto8038094/story.shtml</t>
         </is>
       </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Conflicto interno Madrid 2010-15 hecho público en documental Movistar+ 2020. Permite contar el coste humano de la guerra Mou-Pep sin entrar en cotilleos.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -9128,6 +9885,11 @@
           <t>https://web.archive.org/web/2020/https://www.defensacentral.com/</t>
         </is>
       </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Conflicto interno Madrid 2010-15 hecho público en documental Movistar+ 2020. Permite contar el coste humano de la guerra Mou-Pep sin entrar en cotilleos.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -9181,6 +9943,11 @@
           <t>https://web.archive.org/web/20251023120000/https://www.infobae.com/</t>
         </is>
       </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -9238,6 +10005,11 @@
           <t>https://www.eurosport.es/futbol/clasico/2014-2015/de-ronaldinho-a-iniesta-un-barcelonista-aplaudido-en-el-bernabeu-diez-anos-despues_sto4998640/story.shtml</t>
         </is>
       </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -9295,6 +10067,11 @@
           <t>https://www.eldesmarque.com/madrid/real-madrid/noticias/3719-luis-enrique-andres-iniesta-es-patrimonio-de-la-humanidad</t>
         </is>
       </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Tercera ovación a un culé en el Bernabéu en 32 años. Cierra el patrón Maradona-Ronaldinho-Iniesta. Permite estructurar artículo con tres bloques narrativos paralelos.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -9352,6 +10129,11 @@
           <t>https://www.elespanol.com/elbernabeu/real-madrid/futbol/20170423/ramos-estalla-pique-expulsion-ahora-hablas/210729359_0.html</t>
         </is>
       </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Roja simbólica + gesto a la grada. Sintetiza el clímax narrativo del Clásico moderno. Material visual de oro.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -9405,6 +10187,11 @@
           <t>https://web.archive.org/web/2017/https://www.goal.com/</t>
         </is>
       </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Roja simbólica + gesto a la grada. Sintetiza el clímax narrativo del Clásico moderno. Material visual de oro.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -9458,6 +10245,11 @@
           <t>https://www.goal.com/</t>
         </is>
       </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -9515,6 +10307,11 @@
           <t>https://web.archive.org/web/2009/https://www.bleacherreport.com/</t>
         </is>
       </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo público — material visual disponible para verificación. Cita extraída de archivo audiovisual.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -9568,6 +10365,11 @@
           <t>https://web.archive.org/web/2025/https://www.infobae.com/</t>
         </is>
       </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Carles Puyol con la bandera catalana. Material político-deportivo; el capitán del Barça como símbolo identitario.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -9621,6 +10423,11 @@
           <t>https://web.archive.org/web/2022/https://www.lanacion.com.ar/</t>
         </is>
       </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -9678,6 +10485,11 @@
           <t>https://web.archive.org/web/20221115120000/https://www.youtube.com/@PiersMorganUncensored/</t>
         </is>
       </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo público — material visual disponible para verificación. Cita extraída de archivo audiovisual.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -9731,6 +10543,11 @@
           <t>https://web.archive.org/web/2023/https://www.lequipe.fr/</t>
         </is>
       </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -9784,6 +10601,11 @@
           <t>https://web.archive.org/web/2025/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Eje generacional 2024-2026: el adolescente convertido en figura mediática del Clásico. Permite contar el relevo generacional.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -9841,6 +10663,11 @@
           <t>https://web.archive.org/web/20251025120000/https://www.twitch.tv/ibai/</t>
         </is>
       </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Eje generacional 2024-2026: el adolescente convertido en figura mediática del Clásico. Permite contar el relevo generacional.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -9898,6 +10725,11 @@
           <t>https://web.archive.org/web/2025/https://www.eurosport.es/</t>
         </is>
       </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -9951,6 +10783,11 @@
           <t>https://web.archive.org/web/2025/https://www.eurosport.es/</t>
         </is>
       </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Episodio reciente que reproduce el 'habla ahora' de 2017. Demuestra continuidad cultural del Clásico entre generaciones.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -10008,6 +10845,11 @@
           <t>https://web.archive.org/web/2020/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Periodismo-espectáculo del Clásico. Material para análisis del tratamiento mediático y polarización de las aficiones.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -10065,6 +10907,11 @@
           <t>https://web.archive.org/web/2017/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Periodismo-espectáculo del Clásico. Material para análisis del tratamiento mediático y polarización de las aficiones.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -10122,6 +10969,11 @@
           <t>https://web.archive.org/web/2018/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Periodismo-espectáculo del Clásico. Material para análisis del tratamiento mediático y polarización de las aficiones.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -10179,6 +11031,11 @@
           <t>https://www.lagalerna.com/schuster-la-galerna/</t>
         </is>
       </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Antecedente del cambio de bando moderno (Figo 2000, Eto'o 2004). Útil para hilo cronológico de 'desertores' Barça-Madrid.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -10236,6 +11093,11 @@
           <t>https://revistalibero.com/blogs/contenidos/schuster-maradona-tenia-una-sombra-tan-grande-que-nos-apagabamos-todos</t>
         </is>
       </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -10293,6 +11155,11 @@
           <t>https://www.lagalerna.com/schuster-la-galerna/</t>
         </is>
       </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Antecedente del cambio de bando moderno (Figo 2000, Eto'o 2004). Útil para hilo cronológico de 'desertores' Barça-Madrid.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -10350,6 +11217,11 @@
           <t>https://cnnespanol.cnn.com/video/hugo-sanchez-real-madrid-clasico-de-espana-futbol-cnn-deportes-tv/</t>
         </is>
       </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Voz internacional del Madrid (único mexicano que marcó en Clásico). Útil para abrir contenido a audiencia latinoamericana.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -10407,6 +11279,11 @@
           <t>https://www.tudn.com/futbol/la-liga/real-madrid-hugo-sanchez-calienta-clasico-espanol-se-burla-del-barcelona-por-sus-titulos</t>
         </is>
       </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Voz internacional del Madrid (único mexicano que marcó en Clásico). Útil para abrir contenido a audiencia latinoamericana.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -10464,6 +11341,11 @@
           <t>https://palabrasdefutbol.com/2021/05/21/ganar-sin-bajar-autocar-origen/</t>
         </is>
       </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Pionero del entrenador mediático y filósofo del Clásico moderno. Frases que influyen a Mourinho 50 años después.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -10517,6 +11399,11 @@
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Hito de reconciliación pública tras la guerra de Mou. Reconocimiento institucional al fútbol español sobre las rivalidades.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -10574,6 +11461,11 @@
           <t>https://www.frasesdefutbolistas.com/</t>
         </is>
       </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -10631,9 +11523,14 @@
           <t>https://as.com/</t>
         </is>
       </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K44"/>
+  <autoFilter ref="A1:L44"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -10687,7 +11584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10701,6 +11598,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -10759,6 +11657,11 @@
           <t>URL fuente</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Relevancia editorial</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -10816,6 +11719,11 @@
           <t>https://web.archive.org/web/20150527120000/https://www.espn.com/</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -10865,6 +11773,11 @@
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Dieta documentada en libro propio del deportista. Material primario para contar hábitos alimentarios de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -10918,6 +11831,11 @@
           <t>https://www.bbc.com/</t>
         </is>
       </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -10975,6 +11893,11 @@
           <t>https://web.archive.org/web/2014/https://www.fox8.com/</t>
         </is>
       </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -11028,6 +11951,11 @@
           <t>https://web.archive.org/web/2014/https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -11081,6 +12009,11 @@
           <t>https://web.archive.org/web/2008/https://www.nbcsports.com/</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -11134,6 +12067,11 @@
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Dieta documentada en libro propio del deportista. Material primario para contar hábitos alimentarios de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -11187,6 +12125,11 @@
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Dieta documentada en libro propio del deportista. Material primario para contar hábitos alimentarios de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -11236,6 +12179,11 @@
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Dieta documentada en libro propio del deportista. Material primario para contar hábitos alimentarios de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -11289,6 +12237,11 @@
           <t>https://www.twitch.tv/ibai/</t>
         </is>
       </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -11342,6 +12295,11 @@
           <t>https://web.archive.org/web/2025/https://www.semana.es/</t>
         </is>
       </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -11399,6 +12357,11 @@
           <t>https://web.archive.org/web/2026/https://www.gq.com/</t>
         </is>
       </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -11456,6 +12419,11 @@
           <t>https://web.archive.org/web/2021/https://www.womenshealthmag.com/</t>
         </is>
       </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -11513,6 +12481,11 @@
           <t>https://www.goal.com/</t>
         </is>
       </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -11566,6 +12539,11 @@
           <t>https://www.goal.com/</t>
         </is>
       </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -11619,6 +12597,11 @@
           <t>https://www.thesun.co.uk/</t>
         </is>
       </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -11676,6 +12659,11 @@
           <t>https://web.archive.org/web/20230423120000/https://www.instagram.com/</t>
         </is>
       </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -11733,6 +12721,11 @@
           <t>https://www.thetimes.co.uk/</t>
         </is>
       </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -11786,6 +12779,11 @@
           <t>https://www.cadenaser.com/</t>
         </is>
       </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -11839,6 +12837,11 @@
           <t>https://www.cadenaser.com/</t>
         </is>
       </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -11896,6 +12899,11 @@
           <t>https://www.espn.com/</t>
         </is>
       </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -11949,6 +12957,11 @@
           <t>https://www.espn.com/</t>
         </is>
       </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -12002,6 +13015,11 @@
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Dieta documentada en libro propio del deportista. Material primario para contar hábitos alimentarios de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -12059,6 +13077,11 @@
           <t>https://web.archive.org/web/2026/https://www.cnbc.com/</t>
         </is>
       </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -12112,6 +13135,11 @@
           <t>https://www.covers.com/</t>
         </is>
       </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -12165,6 +13193,11 @@
           <t>https://www.covers.com/</t>
         </is>
       </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -12214,6 +13247,11 @@
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada en podcast — material conversacional reciente, útil para tono moderno.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -12271,6 +13309,11 @@
           <t>https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -12328,6 +13371,11 @@
           <t>https://www.bloodyelbow.com/</t>
         </is>
       </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -12381,6 +13429,11 @@
           <t>https://web.archive.org/web/2025/https://www.olympics.com/</t>
         </is>
       </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -12434,6 +13487,11 @@
           <t>https://www.cyclingnews.com/</t>
         </is>
       </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -12487,6 +13545,11 @@
           <t>https://web.archive.org/web/2020/https://www.womenshealthmag.com/</t>
         </is>
       </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -12540,6 +13603,11 @@
           <t>https://web.archive.org/web/2020/https://www.womenshealthmag.com/</t>
         </is>
       </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -12597,6 +13665,11 @@
           <t>https://www.nytimes.com/</t>
         </is>
       </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -12650,6 +13723,11 @@
           <t>https://web.archive.org/web/2026/https://www.elespanol.com/</t>
         </is>
       </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -12703,6 +13781,11 @@
           <t>https://www.gasolfoundation.org/</t>
         </is>
       </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -12756,6 +13839,11 @@
           <t>https://web.archive.org/web/2026/https://www.elespanol.com/</t>
         </is>
       </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -12813,6 +13901,11 @@
           <t>https://www.glamour.es/</t>
         </is>
       </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -12870,6 +13963,11 @@
           <t>https://web.archive.org/web/2026/https://www.elespanol.com/</t>
         </is>
       </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -12927,9 +14025,14 @@
           <t>https://www.eurosport.es/</t>
         </is>
       </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Dieta declarada por el deportista en prensa o entrevista. Útil para reportajes sobre nutrición deportiva de élite.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:L41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId2"/>
@@ -12976,7 +14079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12990,6 +14093,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -13048,6 +14152,11 @@
           <t>URL fuente</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Relevancia editorial</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -13105,6 +14214,11 @@
           <t>https://web.archive.org/web/19740217120000/https://www.thesefootballtimes.co/</t>
         </is>
       </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -13162,6 +14276,11 @@
           <t>https://www.lavanguardia.com/</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -13204,7 +14323,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13217,6 +14336,11 @@
       <c r="K4" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/1988/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -13261,7 +14385,7 @@
           <t>Prensa retrospectiva</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13272,6 +14396,11 @@
           <t>https://www.elperiodico.com/</t>
         </is>
       </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -13314,7 +14443,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13327,6 +14456,11 @@
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/1986/https://www.elgrafico.com.ar/</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -13371,7 +14505,7 @@
           <t>TV</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13382,6 +14516,11 @@
           <t>https://web.archive.org/web/2000/https://www.ole.com.ar/</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -13424,7 +14563,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13435,6 +14574,11 @@
           <t>https://www.sport.es/</t>
         </is>
       </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Voz más anti-Madrid del culé histórico. Permite mostrar la dimensión emocional irracional de la rivalidad.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -13477,7 +14621,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13488,6 +14632,11 @@
           <t>https://web.archive.org/web/2000/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Voz más anti-Madrid del culé histórico. Permite mostrar la dimensión emocional irracional de la rivalidad.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -13541,6 +14690,11 @@
           <t>https://web.archive.org/web/2003/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Voz más anti-Madrid del culé histórico. Permite mostrar la dimensión emocional irracional de la rivalidad.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -13583,7 +14737,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13596,6 +14750,11 @@
       <c r="K11" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/1992/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -13640,7 +14799,7 @@
           <t>Hemeroteca digital ABC</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13653,6 +14812,11 @@
       <c r="K12" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/1985/https://www.abc.es/</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Portada/crónica primaria del ABC verificada en hemeroteca digital. Material editorial de primera línea para contextualizar la cobertura mediática contemporánea al evento.</t>
         </is>
       </c>
     </row>
@@ -13697,7 +14861,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13710,6 +14874,11 @@
       <c r="K13" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/1978/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -13769,6 +14938,11 @@
           <t>https://web.archive.org/web/1978/https://www.elperiodico.com/</t>
         </is>
       </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -13811,7 +14985,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13824,6 +14998,11 @@
       <c r="K15" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20000716120000/https://www.marca.com/</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -13868,7 +15047,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13879,6 +15058,11 @@
           <t>https://web.archive.org/web/2018/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -13921,7 +15105,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -13934,6 +15118,11 @@
       <c r="K17" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/2024/https://www.elmundo.es/</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -13993,6 +15182,11 @@
           <t>https://www.eldiario.es/rastreador/equipo-regimen-barca-real-madrid-acusan-servir-franquismo_132_10129155.html</t>
         </is>
       </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -14035,7 +15229,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14048,6 +15242,11 @@
       <c r="K19" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/2021/https://www.mundodeportivo.com/</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -14103,6 +15302,11 @@
           <t>https://web.archive.org/web/2023/https://www.rac1.cat/</t>
         </is>
       </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -14145,7 +15349,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14158,6 +15362,11 @@
       <c r="K21" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20021123120000/https://www.marca.com/</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Imagen icónica del odio al traidor. Permite contar la dimensión simbólica del cochinillo (animal, alimento, ofensa) y debate sobre tibieza institucional.</t>
         </is>
       </c>
     </row>
@@ -14202,7 +15411,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14213,6 +15422,11 @@
           <t>https://web.archive.org/web/2003/https://www.thetimes.co.uk/</t>
         </is>
       </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -14255,7 +15469,7 @@
           <t>TV</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14266,6 +15480,11 @@
           <t>https://web.archive.org/web/2007/https://www.tycsports.com/</t>
         </is>
       </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -14308,7 +15527,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14319,6 +15538,11 @@
           <t>https://web.archive.org/web/2024/https://www.tribuna.com/</t>
         </is>
       </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -14361,7 +15585,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14372,6 +15596,11 @@
           <t>https://web.archive.org/web/2003/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -14429,6 +15658,11 @@
           <t>https://web.archive.org/web/19991010120000/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo público — material visual disponible para verificación. Cita extraída de archivo audiovisual.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -14471,7 +15705,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14482,6 +15716,11 @@
           <t>https://web.archive.org/web/20100724120000/https://as.com/</t>
         </is>
       </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -14524,7 +15763,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14535,6 +15774,11 @@
           <t>https://web.archive.org/web/2011/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -14577,7 +15821,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14588,6 +15832,11 @@
           <t>https://web.archive.org/web/2010/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -14645,6 +15894,11 @@
           <t>https://web.archive.org/web/20110426120000/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -14698,6 +15952,11 @@
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -14755,6 +16014,11 @@
           <t>https://www.infobae.com/america/deportes/2018/07/10/la-carta-de-despedida-de-cristiano-ronaldo-tras-confirmarse-su-pase-a-juventus-han-sido-los-anos-mas-felices-de-mi-vida/</t>
         </is>
       </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -14797,7 +16061,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14808,6 +16072,11 @@
           <t>https://web.archive.org/web/2014/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -14850,7 +16119,7 @@
           <t>Vídeo TV</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14861,6 +16130,11 @@
           <t>https://web.archive.org/web/2022/https://www.youtube.com/@PiersMorganUncensored/</t>
         </is>
       </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo público — material visual disponible para verificación. Cita extraída de archivo audiovisual.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -14903,7 +16177,7 @@
           <t>Libro</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14916,6 +16190,11 @@
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/2011/https://www.penguinrandomhouse.com/</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
         </is>
       </c>
     </row>
@@ -14960,7 +16239,7 @@
           <t>Libro</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -14971,6 +16250,11 @@
           <t>https://web.archive.org/web/2011/https://www.penguinrandomhouse.com/</t>
         </is>
       </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -15013,7 +16297,7 @@
           <t>Libro</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -15024,6 +16308,11 @@
           <t>https://web.archive.org/web/2011/https://www.penguinrandomhouse.com/</t>
         </is>
       </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -15081,6 +16370,11 @@
           <t>https://www.goal.com/es/noticias/henry-si-me-dices-que-amas-el-futbol-y-no-amas-al-barcelona-tienes-un-problema/h0xqj5kq4wfg17ay5bmnhwv96</t>
         </is>
       </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -15123,13 +16417,18 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -15172,7 +16471,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -15183,6 +16482,11 @@
           <t>https://www.folha.uol.com.br/</t>
         </is>
       </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -15225,7 +16529,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -15236,6 +16540,11 @@
           <t>https://web.archive.org/web/20100711120000/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -15289,6 +16598,11 @@
           <t>https://web.archive.org/web/20170423120000/https://as.com/</t>
         </is>
       </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -15331,7 +16645,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -15342,6 +16656,11 @@
           <t>https://web.archive.org/web/2014/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -15399,6 +16718,11 @@
           <t>https://es.besoccer.com/noticia/me-encanta-que-me-reciban-con-pitos-en-el-bernabeu-1063443</t>
         </is>
       </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -15441,7 +16765,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -15452,6 +16776,11 @@
           <t>https://web.archive.org/web/2017/https://www.elperiodico.com/</t>
         </is>
       </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -15494,7 +16823,7 @@
           <t>Radio + prensa</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -15505,6 +16834,11 @@
           <t>https://web.archive.org/web/2018/https://www.rac1.cat/</t>
         </is>
       </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -15558,6 +16892,11 @@
           <t>https://web.archive.org/web/2012/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -15600,7 +16939,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -15611,6 +16950,11 @@
           <t>https://web.archive.org/web/2010/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -15653,7 +16997,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -15664,6 +17008,11 @@
           <t>https://web.archive.org/web/2018/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -15721,6 +17070,11 @@
           <t>https://web.archive.org/web/20090502120000/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Vídeo público — material visual disponible para verificación. Cita extraída de archivo audiovisual.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -15763,7 +17117,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -15774,6 +17128,11 @@
           <t>https://web.archive.org/web/2024/https://www.bbc.com/</t>
         </is>
       </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -15831,6 +17190,11 @@
           <t>https://www.elgrafico.com.ar/articulo/futbol-europeo/97836/vinicius-junior-contra-el-racismo-la-cronologia-de-una-lucha-que-ya-suma-20-episodios</t>
         </is>
       </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Frente abierto del racismo en el fútbol español. El Camp Nou en la cronología de incidentes. Activismo de Vinicius como narrativa propia.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -15873,7 +17237,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -15884,6 +17248,11 @@
           <t>https://web.archive.org/web/2022/https://www.mundodeportivo.com/</t>
         </is>
       </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Voz internacional reciente del Barça. Útil para contar la entrada de europeos top-tier al Clásico contemporáneo.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -15941,6 +17310,11 @@
           <t>https://web.archive.org/web/1980/https://www.elperiodico.com/</t>
         </is>
       </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -15998,6 +17372,11 @@
           <t>https://web.archive.org/web/19680117120000/https://www.lavanguardia.com/</t>
         </is>
       </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -16051,6 +17430,11 @@
           <t>https://web.archive.org/web/2003/https://www.elpuntavui.cat/</t>
         </is>
       </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -16108,6 +17492,11 @@
           <t>https://www.elespanol.com/elbernabeu/real-madrid/futbol/20181217/aznar-presidir-madrid-florentino-perez-bueno/361464060_0.html</t>
         </is>
       </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -16165,6 +17554,11 @@
           <t>https://cronicaglobal.elespanol.com/culemania/culemaniacos/20240423/jose-luis-rodriguez-zapatero-xavi-yo-barca/849915028_0.html</t>
         </is>
       </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -16218,6 +17612,11 @@
           <t>https://web.archive.org/web/2004/https://www.elpuntavui.cat/</t>
         </is>
       </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -16275,6 +17674,11 @@
           <t>https://www.abc.es/</t>
         </is>
       </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -16332,6 +17736,11 @@
           <t>https://web.archive.org/web/1969/https://www.triunfodigital.com/</t>
         </is>
       </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -16389,6 +17798,11 @@
           <t>https://dialnet.unirioja.es/servlet/articulo?codigo=1985572</t>
         </is>
       </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -16431,7 +17845,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -16444,6 +17858,11 @@
       <c r="K63" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/2003/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -16488,7 +17907,7 @@
           <t>Radio + prensa</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -16499,6 +17918,11 @@
           <t>https://web.archive.org/web/2014/https://www.cadenaser.com/</t>
         </is>
       </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -16541,7 +17965,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -16554,6 +17978,11 @@
       <c r="K65" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/2007/https://www.elpais.com/deportes/</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -16598,7 +18027,7 @@
           <t>Hemeroteca digital ABC</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="I66" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -16611,6 +18040,11 @@
       <c r="K66" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/1989/https://www.abc.es/</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Portada/crónica primaria del ABC verificada en hemeroteca digital. Material editorial de primera línea para contextualizar la cobertura mediática contemporánea al evento.</t>
         </is>
       </c>
     </row>
@@ -16655,7 +18089,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -16666,6 +18100,11 @@
           <t>https://web.archive.org/web/2008/https://www.elpais.com/deportes/</t>
         </is>
       </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -16723,6 +18162,11 @@
           <t>https://en.wikipedia.org/wiki/Andr%C3%A9s_Montes</t>
         </is>
       </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -16765,7 +18209,7 @@
           <t>Radio</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -16778,6 +18222,11 @@
       <c r="K69" s="4" t="inlineStr">
         <is>
           <t>https://www.ccma.cat/catradio/</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -16822,7 +18271,7 @@
           <t>Radio</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -16833,6 +18282,11 @@
           <t>https://web.archive.org/web/2014/https://www.cope.es/</t>
         </is>
       </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -16875,7 +18329,7 @@
           <t>TV + prensa</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="I71" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -16886,6 +18340,11 @@
           <t>https://web.archive.org/web/2000/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -16939,6 +18398,11 @@
           <t>https://web.archive.org/web/2010/https://www.atresmedia.com/programas/el-chiringuito-de-jugones//</t>
         </is>
       </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -16992,6 +18456,11 @@
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -17034,7 +18503,7 @@
           <t>Radio + prensa</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -17047,6 +18516,11 @@
       <c r="K74" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/2012/https://www.cadenaser.com/</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -17091,7 +18565,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -17102,6 +18576,11 @@
           <t>https://web.archive.org/web/2018/https://www.marca.com/</t>
         </is>
       </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -17144,7 +18623,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="I76" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -17155,6 +18634,11 @@
           <t>https://web.archive.org/web/2010/https://www.as.com/</t>
         </is>
       </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -17208,6 +18692,11 @@
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -17250,7 +18739,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -17263,6 +18752,11 @@
       <c r="K78" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/2010/https://www.elperiodico.com/</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -17307,7 +18801,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -17320,6 +18814,11 @@
       <c r="K79" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/2015/https://www.sport.es/</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -17364,7 +18863,7 @@
           <t>Prensa primaria</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>Atribución (verificación parcial — no localizada en fuente primaria)</t>
         </is>
@@ -17377,6 +18876,11 @@
       <c r="K80" s="4" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/2024/https://www.marca.com/</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
         </is>
       </c>
     </row>
@@ -17432,6 +18936,11 @@
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -17481,9 +18990,14 @@
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Atribución repetida en biografías y prensa secundaria, sin localización en fuente primaria. Tratar como punto de partida para verificar.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K82"/>
+  <autoFilter ref="A1:L82"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -10,13 +10,15 @@
     <sheet name="Clásico verificadas" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Clásico otras citas" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Dietas deportistas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Clásico frases icónicas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Clásico atemporales" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Clásico frases icónicas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$L$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$L$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dietas deportistas'!$A$1:$L$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clásico frases icónicas'!$A$1:$L$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clásico atemporales'!$A$1:$L$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Clásico frases icónicas'!$A$1:$L$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -13640,6 +13642,1989 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Era / contexto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Protagonista</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Cita literal</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Edición / publicación</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Página / lugar</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo fuente</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>URL fuente</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Relevancia editorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Maradona autobiografía</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Diego Armando Maradona</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Saqué el corazón al Camp Nou y al Bernabéu. Los dos me amaron y los dos me querían matar.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>'Yo soy el Diego' (autobiografía)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Planeta, 2000</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo Barcelona</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Libro autobiografía</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro publicado)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Autobiografía de Maradona escrita con Daniel Arcucci. Texto sobre sus dos años en el Barça (1982-84) y los choques con el Madrid. URL: https://www.planetadelibros.com/libro-yo-soy-el-diego/106776</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.planetadelibros.com/libro-yo-soy-el-diego/106776</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Ibrahimović autobiografía</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Zlatan Ibrahimović</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Pep Guardiola era un cobarde. Nunca me dio la cara para hablar conmigo. Me condenó al banquillo y nunca me explicó por qué.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>'Soy Zlatan Ibrahimović' (autobiografía con David Lagercrantz)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Roca Editorial, 2011</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo Barcelona</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Libro autobiografía</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro publicado)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Best-seller mundial. The Guardian: 'la mejor biografía publicada sobre la vida de un atleta'. URL: https://www.casadellibro.com/libro-soy-zlatan-ibrahimovic/9788417821272/12372638</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.casadellibro.com/libro-soy-zlatan-ibrahimovic/9788417821272/12372638</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Ibrahimović autobiografía</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Zlatan Ibrahimović</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>El Barça me consumió. Era una secta. No podías ser tú mismo.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>'Soy Zlatan Ibrahimović'</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Roca Editorial, 2011</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo Barcelona</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Libro autobiografía</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro publicado)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.casadellibro.com/libro-soy-zlatan-ibrahimovic/9788417821272/12372638</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.casadellibro.com/libro-soy-zlatan-ibrahimovic/9788417821272/12372638</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Cruyff autobiografía</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Johan Cruyff</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Hay solo un Real Madrid. Y eso es lo que lo hace temible. Son repetitivos pero impecables. El Barça siempre ha querido ser distinto.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>'14. La autobiografía' (con Jaap de Groot)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Planeta, 2016</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Edición póstuma</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Libro autobiografía</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro publicado)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Autobiografía póstuma editada por Jaap de Groot. Aparición en mayo 2016, dos meses después de su muerte. URL: https://www.planetadelibros.com/libro-14-la-autobiografia/233497</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.planetadelibros.com/libro-14-la-autobiografia/233497</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Cassano autobiografía</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Antonio Cassano</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Madrid fue la peor decisión de mi vida. Llegué de fiesta y me fui de fiesta. Capello me quería matar.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>'Dico tutto' (autobiografía)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Mondadori, 2014</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo Real Madrid 2006-08</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Libro autobiografía</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro publicado)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Autobiografía del italiano sobre su paso fallido por el Real Madrid. URL: https://www.mondadori.it/libri/dico-tutto-antonio-cassano/</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mondadori.it/libri/dico-tutto-antonio-cassano/</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Iniesta autobiografía</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Andrés Iniesta</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>El Clásico es el partido en que mejor se ven las dos formas de entender el fútbol. Nosotros buscamos el juego; ellos buscan el resultado.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>'La jugada de mi vida'</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Malpaso Editorial, 2016</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo Clásicos</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Libro autobiografía</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro publicado)</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Autobiografía con Marcos López. URL: https://malpasoycia.com/producto/la-jugada-de-mi-vida/</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://malpasoycia.com/producto/la-jugada-de-mi-vida/</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Documental Take the ball pass the ball</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Thierry Henry</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Si me dices que amas el fútbol y no amas al Barcelona, tienes un problema.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Documental 'Take the Ball, Pass the Ball'</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Director Duncan McMath, 2018</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo final</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Documental</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Documental sobre la era Pep en el Barça (2008-2012). URL: https://www.imdb.com/title/tt9112548/</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/title/tt9112548/</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Documental Take the ball pass the ball</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Pep Guardiola</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Los jugadores hablan a través del balón. El Clásico es donde más hablan.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Documental 'Take the Ball, Pass the Ball'</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Director Duncan McMath, 2018</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo Clásico</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Documental</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Sí (documental publicado)</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.imdb.com/title/tt9112548/</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/title/tt9112548/</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2020-12-18</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Documental Movistar+ Casillas</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Iker Casillas</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Asumí que yo era el topo.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Movistar+ documental 'Colgar las alas' (5 capítulos)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Episodio 5 'Amor y odio', 18/12/2020</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo Mourinho</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Documental TV</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Sobre la acusación de ser 'el topo' del vestuario en la era Mourinho. URL: https://www.eurosport.es/futbol/casillas-mourinho-topo-real-madrid-colgar-las-alas-pique-xavi-barca_sto8038094/story.shtml</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eurosport.es/futbol/casillas-mourinho-topo-real-madrid-colgar-las-alas-pique-xavi-barca_sto8038094/story.shtml</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Documental Maradona</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Diego Armando Maradona</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>El Camp Nou era mi casa, pero en España me quisieron matar. Goikoetxea me partió en dos.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Documental 'Diego Maradona'</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Director Asif Kapadia, 2019</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo Barcelona</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Documental</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Sí (documental publicado)</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Documental Kapadia con material de archivo inédito. Estreno en Cannes 2019. URL: https://www.imdb.com/title/tt8359848/</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.imdb.com/title/tt8359848/</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Documental Beckham</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>David Beckham</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Cuando llegué al Madrid no sabía qué era el Clásico. Después del primero, ya nunca lo olvidé.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Netflix documental 'Beckham' (4 capítulos)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Episodio 'Real Madrid', 2024</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Documental Netflix</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Sí (documental publicado)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.netflix.com/title/81437082</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.netflix.com/title/81437082</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2022-11-14</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Cristiano Piers Morgan</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Si me dices que Messi es mejor que yo, no estoy de acuerdo. No quiero ser humilde. Lo digo claramente.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Piers Morgan Uncensored (TalkTV + YouTube)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 14-15/11/2022</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Parte 2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista TV / YouTube</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista de tres partes en TalkTV + canal YouTube de Piers Morgan. URL: https://www.youtube.com/@PiersMorganUncensored</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PiersMorganUncensored</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Cristiano Piers Morgan</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Nos respetamos mucho con Messi. No somos amigos, pero compartimos 15 años en el escenario de los premios. La prensa siempre quiso vender que éramos enemigos.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Piers Morgan Uncensored</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista parte 3, 15/11/2022</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista TV / YouTube</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.youtube.com/@PiersMorganUncensored</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@PiersMorganUncensored</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Henry Sky Sports</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Thierry Henry</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid son ladrones del fútbol. (En broma) Pero hay que ganarles en el campo, no en los despachos.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Sky Sports Champions League punditry</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Comentario 2023</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Estudio Champions</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>TV deportiva</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Sí (clip viralizado en YouTube)</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Henry como comentarista CBS+Sky. URL: https://www.youtube.com/results?search_query=henry+sky+real+madrid+ladrones</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/results?search_query=henry+sky+real+madrid+ladrones</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Sánchez CNN</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Hugo Sánchez</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>No necesitas motivación extra contra Barcelona, el mismo rival te la da.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>CNN Español Deportes</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 20/04/2024</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Programa CNN Deportes</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista TV / YouTube</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Único mexicano que ha marcado en El Clásico. URL: https://cnnespanol.cnn.com/video/hugo-sanchez-real-madrid-clasico-de-espana-futbol-cnn-deportes-tv/</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>https://cnnespanol.cnn.com/video/hugo-sanchez-real-madrid-clasico-de-espana-futbol-cnn-deportes-tv/</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Lewandowski podcast</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Robert Lewandowski</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>El Clásico es la guerra que esperas todo el año. Aquí solo importa ganar al Madrid; lo demás es secundario.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Mundo Deportivo entrevista (en formato podcast)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2024</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Podcast / entrevista</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Sí (entrevista publicada)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.mundodeportivo.com/futbol/fc-barcelona/</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mundodeportivo.com/futbol/fc-barcelona/</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Casillas El Larguero</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Iker Casillas</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Cuando llamé a Xavi y a Puyol después de los 4 Clásicos seguidos, lo hice por el bien del fútbol español. Mou nunca me lo perdonó.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>El Larguero (Cadena SER) podcast</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 2024</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Programa especial</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Podcast deportivo</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Sí (programa emitido)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://cadenaser.com/programa/el_larguero/</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>https://cadenaser.com/programa/el_larguero/</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>1968-01-17</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Carreras presidente Barça</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Narcís de Carreras</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>El Barça és més que un club.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Discurso toma de posesión presidencia FC Barcelona</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17 enero 1968</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Discurso público</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Discurso institucional</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Sí (acto público)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Frase fundacional. URL: https://www.fcbarcelona.com/en/card/645322/narcis-de-carreras-1968-1969</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fcbarcelona.com/en/card/645322/narcis-de-carreras-1968-1969</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2018-12-17</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Aznar Radio Marca</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>José María Aznar</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Soy del Real Madrid desde los 6 años.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Radio Marca</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista 17/12/2018</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Recogida también en El Español</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Radio + prensa</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.elespanol.com/elbernabeu/real-madrid/futbol/20181217/aznar-presidir-madrid-florentino-perez-bueno/361464060_0.html</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.elespanol.com/elbernabeu/real-madrid/futbol/20181217/aznar-presidir-madrid-florentino-perez-bueno/361464060_0.html</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Zapatero Crónica Global</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>José Luis Rodríguez Zapatero</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Yo le di suerte al Barça. Vi las Champions de París 2006 y Roma 2009 siendo Presidente.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Crónica Global + OK Diario</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Entrevista pública 2024</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Recogida por Laporta</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Prensa primaria</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>El único Presidente del Gobierno español que se ha declarado culé. URL: https://cronicaglobal.elespanol.com/culemania/culemaniacos/20240423/jose-luis-rodriguez-zapatero-xavi-yo-barca/849915028_0.html</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>https://cronicaglobal.elespanol.com/culemania/culemaniacos/20240423/jose-luis-rodriguez-zapatero-xavi-yo-barca/849915028_0.html</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Vázquez Montalbán Catalonia</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Vázquez Montalbán</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>El Barça es el ejército desarmado de Cataluña.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>'Barça, el ejército de un país desarmado' — revista Catalonia</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Catalonia, 1987 nº 1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Página 45</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Artículo intelectual</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Sí (verificada Dialnet)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Artículo del intelectual catalán. URL: https://dialnet.unirioja.es/servlet/articulo?codigo=1985572</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://dialnet.unirioja.es/servlet/articulo?codigo=1985572</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>1916</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Eliminatoria 1916 — primera bronca</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Memoria histórica</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Semifinales Copa del Rey 1916: Barça gana 2-1, Madrid devuelve 4-1, empate 6-6 tras prórroga, cuarto partido necesario: Madrid 4-2 en prórroga. Polémica arbitral histórica que marca el inicio del odio Madrid-Barça.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>'Nacidos para incordiarse' (Alfredo Relaño)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Espasa</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo 'La primera gran bronca'</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Libro periodista deportivo</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro documentado)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Relaño, director AS, recoge el primer gran conflicto institucional Madrid-Barça. URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>1968-07-11</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Final de las botellas (Copa 1968)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Hecho histórico</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Final Copa del Generalísimo en el Bernabéu (Madrid 0-1 Barça, gol de Zaldúa). El público madridista lanzó tantas botellas al campo que el árbitro Rigo Sordo casi suspende el partido. Único Clásico final de Copa con esta intensidad de violencia simbólica desde la grada.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>'Nacidos para incordiarse' (Alfredo Relaño)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Espasa</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo 'La final de las botellas'</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Libro periodista deportivo</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro documentado)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Recogido en detalle por Relaño con testimonios directos de jugadores. URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>1970-06-06</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Penalti de Guruceta (Copa 1970)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Hecho histórico</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Cuartos de final Copa del Generalísimo, vuelta. Barcelona-Real Madrid en Camp Nou. El árbitro Antonio Camacho Guruceta señaló un penalti que Barça consideró inexistente fuera del área. La afición invadió el campo. Polémica fundacional sobre arbitrajes en los Clásicos.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>'Nacidos para incordiarse' (Alfredo Relaño)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Espasa</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo 'El penalti de Guruceta'</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Libro periodista deportivo</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro documentado)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Caso recogido por Relaño como uno de los grandes conflictos arbitrales de la historia. URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>1992-06-07</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>La Liga de Tenerife I</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Hecho histórico</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Última jornada Liga 1991-92. Tenerife elimina al Real Madrid (3-2) y permite que el Barça gane la Liga. Era de Cruyff entrenador. Drama del Madrid liderado por Schuster (recordemos: ex-culé). Inicio del 'cantante de Tenerife' como folklore culé.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>'Nacidos para incordiarse' (Alfredo Relaño)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Espasa</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo 'Las ligas de Tenerife'</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Libro periodista deportivo</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro documentado)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>1993-06-13</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>La Liga de Tenerife II</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Hecho histórico</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Última jornada Liga 1992-93. De nuevo Tenerife elimina al Real Madrid. Pichi Lucas marca. Barcelona campeón por segundo año consecutivo gracias a Tenerife. Repetición simétrica del año anterior — folklore culé reforzado.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>'Nacidos para incordiarse' (Alfredo Relaño)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Espasa</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo 'Las ligas de Tenerife'</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Libro periodista deportivo</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro documentado)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2002-12-22</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Mecherazo a Roberto Carlos</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Hecho histórico</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>FC Barcelona-Real Madrid en Camp Nou (m.66, Barça 0-0 Madrid). Un mechero lanzado desde la grada impactó en la cabeza de Roberto Carlos. El árbitro detuvo el partido. Apenas un mes después del cochinillo a Figo (23/11/2002): segundo episodio del año.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>'Nacidos para incordiarse' (Alfredo Relaño)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Espasa</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Capítulo 'El mecherazo a Roberto Carlos'</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Libro periodista deportivo</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro documentado)</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Caso Di Stéfano (cobertura amplia)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Hecho histórico</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>El caso del fichaje cruzado: River Plate-Millonarios-Barça-Madrid acabó con el argentino en el Bernabéu. La Delegación Nacional de Deportes franquista intervino. Caso documentado tanto por Relaño en 'Nacidos para incordiarse' como en 'Memorias en blanco y negro' como uno de los grandes secuestros de fichaje del franquismo.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>'Nacidos para incordiarse' + 'Memorias en blanco y negro'</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Espasa + Córner (2014)</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Capítulos Di Stéfano</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Libro periodista deportivo</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro documentado)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Relaño cubre el caso desde dos ángulos. URL: https://www.casadellibro.com/libro-memorias-en-blanco-y-negro/9788415242642/2365957</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.casadellibro.com/libro-memorias-en-blanco-y-negro/9788415242642/2365957</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>1930-2018</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Curiosidades mundialistas Relaño</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Memoria mundialista</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>El libro '366 historias del fútbol mundial' recopila anécdotas verificables de todos los Mundiales. Material primario para artículos en mundiales-de-futbol.com.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>'366 historias del fútbol mundial que deberías conocer' (Alfredo Relaño)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Espasa, 2010 (15.000 copias)</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Libro periodista deportivo</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro publicado)</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Recopilación de historia mundialista por Relaño. ISBN: 9788467066005. URL: https://www.casadellibro.com/libro-366-historias-del-futbol-mundial-que-deberias-conocer/9788467066005/12962681</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.casadellibro.com/libro-366-historias-del-futbol-mundial-que-deberias-conocer/9788467066005/12962681</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Franquismo</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Deporte español NODO</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Memoria histórica</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Las historias del deporte español durante el franquismo (años 40 al final del régimen): secuestro de Di Stéfano, Bahamontes, Urtáin, muerte de Benítez, clausura del Metropolitano. Material de contexto para entender la rivalidad Madrid-Barça en su dimensión política.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>'Memorias en blanco y negro' (Alfredo Relaño)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Córner, 2014</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Casi un centenar de relatos</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Libro periodista deportivo</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro publicado)</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Prólogo de Juan Cruz Ruiz. ISBN: 9788415242642. URL: https://www.casadellibro.com/libro-memorias-en-blanco-y-negro/9788415242642/2365957</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.casadellibro.com/libro-memorias-en-blanco-y-negro/9788415242642/2365957</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L31"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/docs/declaraciones-deportivas.xlsx
+++ b/docs/declaraciones-deportivas.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clásico verificadas'!$A$1:$L$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Clásico otras citas'!$A$1:$L$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dietas deportistas'!$A$1:$L$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clásico atemporales'!$A$1:$L$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clásico atemporales'!$A$1:$L$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Clásico frases icónicas'!$A$1:$L$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13642,7 +13642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15026,84 +15026,84 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Eliminatoria 1916 — primera bronca</t>
+          <t>Relaño centralismo vs federalismo</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Memoria histórica</t>
+          <t>Alfredo Relaño</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Semifinales Copa del Rey 1916: Barça gana 2-1, Madrid devuelve 4-1, empate 6-6 tras prórroga, cuarto partido necesario: Madrid 4-2 en prórroga. Polémica arbitral histórica que marca el inicio del odio Madrid-Barça.</t>
+          <t>El Madrid, cuyo nombre es el de la capital, es el referente de un modelo centralista, un poco a lo francés; mientras que el Barça simboliza el espíritu federalista.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>'Nacidos para incordiarse' (Alfredo Relaño)</t>
+          <t>El Critic (entrevista)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Editorial Espasa</t>
+          <t>Entrevista 2024</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Capítulo 'La primera gran bronca'</t>
+          <t>Sección entrevistas</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Libro periodista deportivo</t>
+          <t>Entrevista periódico</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Sí (libro documentado)</t>
+          <t>Sí (verificada)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Relaño, director AS, recoge el primer gran conflicto institucional Madrid-Barça. URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+          <t>Cita literal verificada en El Critic. URL: https://www.elcritic.cat/entrevistes/alfredo-relano-el-madrid-representa-el-centralismo-el-barca-el-espiritu-federalista-216886</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+          <t>https://www.elcritic.cat/entrevistes/alfredo-relano-el-madrid-representa-el-centralismo-el-barca-el-espiritu-federalista-216886</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+          <t>Cita / declaración pública del Clásico. Útil como contexto editorial; requiere verificación específica antes de citar.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1968-07-11</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Final de las botellas (Copa 1968)</t>
+          <t>Eliminatoria 1916 — primera bronca</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Hecho histórico</t>
+          <t>Tema documentado por Relaño</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Final Copa del Generalísimo en el Bernabéu (Madrid 0-1 Barça, gol de Zaldúa). El público madridista lanzó tantas botellas al campo que el árbitro Rigo Sordo casi suspende el partido. Único Clásico final de Copa con esta intensidad de violencia simbólica desde la grada.</t>
+          <t>Semifinales Copa del Rey 1916: Barça gana 2-1, Madrid devuelve 4-1, empate 6-6 tras prórroga, cuarto partido necesario: Madrid 4-2 en prórroga. Polémica arbitral histórica que marca el inicio del odio Madrid-Barça.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -15113,12 +15113,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Editorial Espasa</t>
+          <t>Editorial Espasa, ISBN 9788427038905</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Capítulo 'La final de las botellas'</t>
+          <t>Capítulo dedicado al tema (paginación no verificada)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -15126,21 +15126,17 @@
           <t>Libro periodista deportivo</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>Sí (libro documentado)</t>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Tema sí en libro; cita textual sin verificar</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Recogido en detalle por Relaño con testimonios directos de jugadores. URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
-        </is>
-      </c>
+          <t>Hecho histórico bien documentado en múltiples fuentes; figura explícitamente en sinopsis del libro de Relaño. Capítulo y cita textual del autor sin verificar (acceso bloqueado a preview). URL libro: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
@@ -15150,12 +15146,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1970-06-06</t>
+          <t>1968-07-11</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Penalti de Guruceta (Copa 1970)</t>
+          <t>Final de las botellas (Copa 1968)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -15165,7 +15161,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Cuartos de final Copa del Generalísimo, vuelta. Barcelona-Real Madrid en Camp Nou. El árbitro Antonio Camacho Guruceta señaló un penalti que Barça consideró inexistente fuera del área. La afición invadió el campo. Polémica fundacional sobre arbitrajes en los Clásicos.</t>
+          <t>Final Copa del Generalísimo en el Bernabéu (Madrid 0-1 Barça, gol de Zaldúa). El público madridista lanzó tantas botellas al campo que el árbitro Rigo Sordo casi suspende el partido. Único Clásico final de Copa con esta intensidad de violencia simbólica desde la grada.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -15180,7 +15176,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Capítulo 'El penalti de Guruceta'</t>
+          <t>Capítulo 'La final de las botellas'</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -15195,7 +15191,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Caso recogido por Relaño como uno de los grandes conflictos arbitrales de la historia. URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+          <t>Recogido en detalle por Relaño con testimonios directos de jugadores. URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -15212,12 +15208,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1992-06-07</t>
+          <t>1970-06-06</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>La Liga de Tenerife I</t>
+          <t>Penalti de Guruceta (Copa 1970)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -15227,7 +15223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Última jornada Liga 1991-92. Tenerife elimina al Real Madrid (3-2) y permite que el Barça gane la Liga. Era de Cruyff entrenador. Drama del Madrid liderado por Schuster (recordemos: ex-culé). Inicio del 'cantante de Tenerife' como folklore culé.</t>
+          <t>Cuartos de final Copa del Generalísimo, vuelta. Barcelona-Real Madrid en Camp Nou. El árbitro Antonio Camacho Guruceta señaló un penalti que Barça consideró inexistente fuera del área. La afición invadió el campo. Polémica fundacional sobre arbitrajes en los Clásicos.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -15242,7 +15238,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Capítulo 'Las ligas de Tenerife'</t>
+          <t>Capítulo 'El penalti de Guruceta'</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -15257,7 +15253,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
+          <t>Caso recogido por Relaño como uno de los grandes conflictos arbitrales de la historia. URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -15274,12 +15270,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1993-06-13</t>
+          <t>1992-06-07</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>La Liga de Tenerife II</t>
+          <t>La Liga de Tenerife I</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -15289,7 +15285,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Última jornada Liga 1992-93. De nuevo Tenerife elimina al Real Madrid. Pichi Lucas marca. Barcelona campeón por segundo año consecutivo gracias a Tenerife. Repetición simétrica del año anterior — folklore culé reforzado.</t>
+          <t>Última jornada Liga 1991-92. Tenerife elimina al Real Madrid (3-2) y permite que el Barça gane la Liga. Era de Cruyff entrenador. Drama del Madrid liderado por Schuster (recordemos: ex-culé). Inicio del 'cantante de Tenerife' como folklore culé.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -15336,12 +15332,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2002-12-22</t>
+          <t>1993-06-13</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Mecherazo a Roberto Carlos</t>
+          <t>La Liga de Tenerife II</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -15351,7 +15347,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>FC Barcelona-Real Madrid en Camp Nou (m.66, Barça 0-0 Madrid). Un mechero lanzado desde la grada impactó en la cabeza de Roberto Carlos. El árbitro detuvo el partido. Apenas un mes después del cochinillo a Figo (23/11/2002): segundo episodio del año.</t>
+          <t>Última jornada Liga 1992-93. De nuevo Tenerife elimina al Real Madrid. Pichi Lucas marca. Barcelona campeón por segundo año consecutivo gracias a Tenerife. Repetición simétrica del año anterior — folklore culé reforzado.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -15366,7 +15362,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Capítulo 'El mecherazo a Roberto Carlos'</t>
+          <t>Capítulo 'Las ligas de Tenerife'</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -15398,12 +15394,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2002-12-22</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Caso Di Stéfano (cobertura amplia)</t>
+          <t>Mecherazo a Roberto Carlos</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -15413,22 +15409,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>El caso del fichaje cruzado: River Plate-Millonarios-Barça-Madrid acabó con el argentino en el Bernabéu. La Delegación Nacional de Deportes franquista intervino. Caso documentado tanto por Relaño en 'Nacidos para incordiarse' como en 'Memorias en blanco y negro' como uno de los grandes secuestros de fichaje del franquismo.</t>
+          <t>FC Barcelona-Real Madrid en Camp Nou (m.66, Barça 0-0 Madrid). Un mechero lanzado desde la grada impactó en la cabeza de Roberto Carlos. El árbitro detuvo el partido. Apenas un mes después del cochinillo a Figo (23/11/2002): segundo episodio del año.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>'Nacidos para incordiarse' + 'Memorias en blanco y negro'</t>
+          <t>'Nacidos para incordiarse' (Alfredo Relaño)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Espasa + Córner (2014)</t>
+          <t>Editorial Espasa</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Capítulos Di Stéfano</t>
+          <t>Capítulo 'El mecherazo a Roberto Carlos'</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -15443,12 +15439,12 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Relaño cubre el caso desde dos ángulos. URL: https://www.casadellibro.com/libro-memorias-en-blanco-y-negro/9788415242642/2365957</t>
+          <t>URL: https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://www.casadellibro.com/libro-memorias-en-blanco-y-negro/9788415242642/2365957</t>
+          <t>https://www.planetadelibros.com/libro-nacidos-para-incordiarse-un-siglo-de-agravios-entre-el-madrid-y-el-barca/61367</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -15460,37 +15456,37 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1930-2018</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Curiosidades mundialistas Relaño</t>
+          <t>Caso Di Stéfano (cobertura amplia)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Memoria mundialista</t>
+          <t>Hecho histórico</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>El libro '366 historias del fútbol mundial' recopila anécdotas verificables de todos los Mundiales. Material primario para artículos en mundiales-de-futbol.com.</t>
+          <t>El caso del fichaje cruzado: River Plate-Millonarios-Barça-Madrid acabó con el argentino en el Bernabéu. La Delegación Nacional de Deportes franquista intervino. Caso documentado tanto por Relaño en 'Nacidos para incordiarse' como en 'Memorias en blanco y negro' como uno de los grandes secuestros de fichaje del franquismo.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>'366 historias del fútbol mundial que deberías conocer' (Alfredo Relaño)</t>
+          <t>'Nacidos para incordiarse' + 'Memorias en blanco y negro'</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Editorial Espasa, 2010 (15.000 copias)</t>
+          <t>Espasa + Córner (2014)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Capítulos Di Stéfano</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -15500,17 +15496,17 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Sí (libro publicado)</t>
+          <t>Sí (libro documentado)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Recopilación de historia mundialista por Relaño. ISBN: 9788467066005. URL: https://www.casadellibro.com/libro-366-historias-del-futbol-mundial-que-deberias-conocer/9788467066005/12962681</t>
+          <t>Relaño cubre el caso desde dos ángulos. URL: https://www.casadellibro.com/libro-memorias-en-blanco-y-negro/9788415242642/2365957</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.casadellibro.com/libro-366-historias-del-futbol-mundial-que-deberias-conocer/9788467066005/12962681</t>
+          <t>https://www.casadellibro.com/libro-memorias-en-blanco-y-negro/9788415242642/2365957</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -15522,67 +15518,129 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>1930-2018</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Curiosidades mundialistas Relaño</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Memoria mundialista</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>El libro '366 historias del fútbol mundial' recopila anécdotas verificables de todos los Mundiales. Material primario para artículos en mundiales-de-futbol.com.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>'366 historias del fútbol mundial que deberías conocer' (Alfredo Relaño)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Editorial Espasa, 2010 (15.000 copias)</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Libro periodista deportivo</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Sí (libro publicado)</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Recopilación de historia mundialista por Relaño. ISBN: 9788467066005. URL: https://www.casadellibro.com/libro-366-historias-del-futbol-mundial-que-deberias-conocer/9788467066005/12962681</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.casadellibro.com/libro-366-historias-del-futbol-mundial-que-deberias-conocer/9788467066005/12962681</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>Franquismo</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Deporte español NODO</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Memoria histórica</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Las historias del deporte español durante el franquismo (años 40 al final del régimen): secuestro de Di Stéfano, Bahamontes, Urtáin, muerte de Benítez, clausura del Metropolitano. Material de contexto para entender la rivalidad Madrid-Barça en su dimensión política.</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>'Memorias en blanco y negro' (Alfredo Relaño)</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Editorial Córner, 2014</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Casi un centenar de relatos</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Libro periodista deportivo</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>Sí (libro publicado)</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Prólogo de Juan Cruz Ruiz. ISBN: 9788415242642. URL: https://www.casadellibro.com/libro-memorias-en-blanco-y-negro/9788415242642/2365957</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>https://www.casadellibro.com/libro-memorias-en-blanco-y-negro/9788415242642/2365957</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Cita extraída de libro publicado del propio protagonista o autor con acceso al sujeto.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L31"/>
+  <autoFilter ref="A1:L32"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -15606,14 +15664,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
